--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -5116,65 +5116,205 @@
         <v>1.255</v>
       </c>
     </row>
-    <row r="174" spans="3:6">
-      <c r="C174" s="1"/>
-      <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
-      <c r="F174" s="3"/>
-    </row>
-    <row r="175" spans="3:6">
-      <c r="C175" s="1"/>
-      <c r="D175" s="2"/>
-      <c r="E175" s="2"/>
-      <c r="F175" s="3"/>
-    </row>
-    <row r="176" spans="3:6">
-      <c r="C176" s="1"/>
-      <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
-      <c r="F176" s="3"/>
-    </row>
-    <row r="177" spans="3:6">
-      <c r="C177" s="1"/>
-      <c r="D177" s="2"/>
-      <c r="E177" s="2"/>
-      <c r="F177" s="3"/>
-    </row>
-    <row r="178" spans="3:6">
-      <c r="C178" s="1"/>
-      <c r="D178" s="2"/>
-      <c r="E178" s="2"/>
-      <c r="F178" s="3"/>
-    </row>
-    <row r="179" spans="3:6">
-      <c r="C179" s="1"/>
-      <c r="D179" s="2"/>
-      <c r="E179" s="2"/>
-      <c r="F179" s="3"/>
-    </row>
-    <row r="180" spans="3:6">
-      <c r="C180" s="1"/>
-      <c r="D180" s="2"/>
-      <c r="E180" s="2"/>
-      <c r="F180" s="3"/>
-    </row>
-    <row r="181" spans="3:6">
-      <c r="C181" s="1"/>
-      <c r="D181" s="2"/>
-      <c r="E181" s="2"/>
-      <c r="F181" s="3"/>
-    </row>
-    <row r="182" spans="3:6">
-      <c r="C182" s="1"/>
-      <c r="D182" s="2"/>
-      <c r="E182" s="2"/>
-      <c r="F182" s="3"/>
-    </row>
-    <row r="183" spans="3:6">
-      <c r="C183" s="1"/>
-      <c r="D183" s="2"/>
-      <c r="E183" s="2"/>
-      <c r="F183" s="3"/>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>9</v>
+      </c>
+      <c r="B174">
+        <v>1</v>
+      </c>
+      <c r="C174" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D174" s="2">
+        <v>19.13</v>
+      </c>
+      <c r="E174" s="2">
+        <v>1.63</v>
+      </c>
+      <c r="F174" s="3">
+        <v>5.138</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>9</v>
+      </c>
+      <c r="B175">
+        <v>2</v>
+      </c>
+      <c r="C175" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D175" s="2">
+        <v>19.41</v>
+      </c>
+      <c r="E175" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="F175" s="3">
+        <v>0.788</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>9</v>
+      </c>
+      <c r="B176" t="s">
+        <v>10</v>
+      </c>
+      <c r="C176" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D176" s="2">
+        <v>19.22</v>
+      </c>
+      <c r="E176" s="2">
+        <v>10.38</v>
+      </c>
+      <c r="F176" s="3">
+        <v>3.557</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>9</v>
+      </c>
+      <c r="B177">
+        <v>3</v>
+      </c>
+      <c r="C177" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D177" s="2">
+        <v>19.41</v>
+      </c>
+      <c r="E177" s="2">
+        <v>12.08</v>
+      </c>
+      <c r="F177" s="3">
+        <v>4.726</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>9</v>
+      </c>
+      <c r="B178">
+        <v>4</v>
+      </c>
+      <c r="C178" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D178" s="2">
+        <v>19.74</v>
+      </c>
+      <c r="E178" s="2">
+        <v>70.83</v>
+      </c>
+      <c r="F178" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>9</v>
+      </c>
+      <c r="B179" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D179" s="2">
+        <v>19.75</v>
+      </c>
+      <c r="E179" s="2">
+        <v>21.55</v>
+      </c>
+      <c r="F179" s="3">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>12</v>
+      </c>
+      <c r="B180">
+        <v>1</v>
+      </c>
+      <c r="C180" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D180" s="2">
+        <v>17.6</v>
+      </c>
+      <c r="E180" s="2">
+        <v>0</v>
+      </c>
+      <c r="F180" s="3">
+        <v>0.726</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>12</v>
+      </c>
+      <c r="B181">
+        <v>2</v>
+      </c>
+      <c r="C181" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D181" s="2">
+        <v>17.62</v>
+      </c>
+      <c r="E181" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="F181" s="3">
+        <v>0.752</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182">
+        <v>3</v>
+      </c>
+      <c r="C182" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D182" s="2">
+        <v>17.64</v>
+      </c>
+      <c r="E182" s="2">
+        <v>0</v>
+      </c>
+      <c r="F182" s="3">
+        <v>0.716</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>12</v>
+      </c>
+      <c r="B183">
+        <v>4</v>
+      </c>
+      <c r="C183" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D183" s="2">
+        <v>17.65</v>
+      </c>
+      <c r="E183" s="2">
+        <v>0</v>
+      </c>
+      <c r="F183" s="3">
+        <v>1.031</v>
+      </c>
     </row>
     <row r="184" spans="3:6">
       <c r="C184" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -1235,7 +1235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="6" max="6" width="11.5"/>
@@ -1502,7 +1502,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1522,14 +1522,15 @@
         <v>46103</v>
       </c>
       <c r="G10" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="2">
         <v>18.26</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0.2</v>
       </c>
       <c r="I10" s="3">
         <v>0.581</v>
       </c>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
@@ -1551,10 +1552,10 @@
         <v>46113</v>
       </c>
       <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
         <v>15.69</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
       </c>
       <c r="I11" s="3">
         <v>0.393</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="23775" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -5317,65 +5317,205 @@
         <v>1.031</v>
       </c>
     </row>
-    <row r="184" spans="3:6">
-      <c r="C184" s="1"/>
-      <c r="D184" s="2"/>
-      <c r="E184" s="2"/>
-      <c r="F184" s="3"/>
-    </row>
-    <row r="185" spans="3:6">
-      <c r="C185" s="1"/>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
-      <c r="F185" s="3"/>
-    </row>
-    <row r="186" spans="3:6">
-      <c r="C186" s="1"/>
-      <c r="D186" s="2"/>
-      <c r="E186" s="2"/>
-      <c r="F186" s="3"/>
-    </row>
-    <row r="187" spans="3:6">
-      <c r="C187" s="1"/>
-      <c r="D187" s="2"/>
-      <c r="E187" s="2"/>
-      <c r="F187" s="3"/>
-    </row>
-    <row r="188" spans="3:6">
-      <c r="C188" s="1"/>
-      <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
-      <c r="F188" s="3"/>
-    </row>
-    <row r="189" spans="3:6">
-      <c r="C189" s="1"/>
-      <c r="D189" s="2"/>
-      <c r="E189" s="2"/>
-      <c r="F189" s="3"/>
-    </row>
-    <row r="190" spans="3:6">
-      <c r="C190" s="1"/>
-      <c r="D190" s="2"/>
-      <c r="E190" s="2"/>
-      <c r="F190" s="3"/>
-    </row>
-    <row r="191" spans="3:6">
-      <c r="C191" s="1"/>
-      <c r="D191" s="2"/>
-      <c r="E191" s="2"/>
-      <c r="F191" s="3"/>
-    </row>
-    <row r="192" spans="3:6">
-      <c r="C192" s="1"/>
-      <c r="D192" s="2"/>
-      <c r="E192" s="2"/>
-      <c r="F192" s="3"/>
-    </row>
-    <row r="193" spans="3:6">
-      <c r="C193" s="1"/>
-      <c r="D193" s="2"/>
-      <c r="E193" s="2"/>
-      <c r="F193" s="3"/>
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>9</v>
+      </c>
+      <c r="B184">
+        <v>1</v>
+      </c>
+      <c r="C184" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D184" s="2">
+        <v>19.08</v>
+      </c>
+      <c r="E184" s="2">
+        <v>1.71</v>
+      </c>
+      <c r="F184" s="3">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>9</v>
+      </c>
+      <c r="B185">
+        <v>2</v>
+      </c>
+      <c r="C185" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D185" s="2">
+        <v>19.32</v>
+      </c>
+      <c r="E185" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="F185" s="3">
+        <v>0.206</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>9</v>
+      </c>
+      <c r="B186" t="s">
+        <v>10</v>
+      </c>
+      <c r="C186" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D186" s="2">
+        <v>19.15</v>
+      </c>
+      <c r="E186" s="2">
+        <v>8.8</v>
+      </c>
+      <c r="F186" s="3">
+        <v>3.564</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>9</v>
+      </c>
+      <c r="B187">
+        <v>3</v>
+      </c>
+      <c r="C187" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D187" s="2">
+        <v>19.4</v>
+      </c>
+      <c r="E187" s="2">
+        <v>10.87</v>
+      </c>
+      <c r="F187" s="3">
+        <v>4.281</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>9</v>
+      </c>
+      <c r="B188">
+        <v>4</v>
+      </c>
+      <c r="C188" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D188" s="2">
+        <v>19.67</v>
+      </c>
+      <c r="E188" s="2">
+        <v>66.04</v>
+      </c>
+      <c r="F188" s="3">
+        <v>0.355</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>9</v>
+      </c>
+      <c r="B189" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D189" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="E189" s="2">
+        <v>19.32</v>
+      </c>
+      <c r="F189" s="3">
+        <v>3.263</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>12</v>
+      </c>
+      <c r="B190">
+        <v>1</v>
+      </c>
+      <c r="C190" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D190" s="2">
+        <v>18.59</v>
+      </c>
+      <c r="E190" s="2">
+        <v>0</v>
+      </c>
+      <c r="F190" s="3">
+        <v>0.716</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>12</v>
+      </c>
+      <c r="B191">
+        <v>2</v>
+      </c>
+      <c r="C191" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D191" s="2">
+        <v>18.59</v>
+      </c>
+      <c r="E191" s="2">
+        <v>31</v>
+      </c>
+      <c r="F191" s="3">
+        <v>0.682</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
+        <v>12</v>
+      </c>
+      <c r="B192">
+        <v>3</v>
+      </c>
+      <c r="C192" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D192" s="2">
+        <v>18.6</v>
+      </c>
+      <c r="E192" s="2">
+        <v>0</v>
+      </c>
+      <c r="F192" s="3">
+        <v>0.707</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" t="s">
+        <v>12</v>
+      </c>
+      <c r="B193">
+        <v>4</v>
+      </c>
+      <c r="C193" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D193" s="2">
+        <v>18.52</v>
+      </c>
+      <c r="E193" s="2">
+        <v>0</v>
+      </c>
+      <c r="F193" s="3">
+        <v>1.087</v>
+      </c>
     </row>
     <row r="194" spans="3:6">
       <c r="C194" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23775" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1651,7 +1651,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F281"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -5517,29 +5517,85 @@
         <v>1.087</v>
       </c>
     </row>
-    <row r="194" spans="3:6">
-      <c r="C194" s="1"/>
-      <c r="D194" s="2"/>
-      <c r="E194" s="2"/>
-      <c r="F194" s="3"/>
-    </row>
-    <row r="195" spans="3:6">
-      <c r="C195" s="1"/>
-      <c r="D195" s="2"/>
-      <c r="E195" s="2"/>
-      <c r="F195" s="3"/>
-    </row>
-    <row r="196" spans="3:6">
-      <c r="C196" s="1"/>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
-      <c r="F196" s="3"/>
-    </row>
-    <row r="197" spans="3:6">
-      <c r="C197" s="1"/>
-      <c r="D197" s="2"/>
-      <c r="E197" s="2"/>
-      <c r="F197" s="3"/>
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>12</v>
+      </c>
+      <c r="B194">
+        <v>1</v>
+      </c>
+      <c r="C194" s="1">
+        <v>46120</v>
+      </c>
+      <c r="D194" s="2">
+        <v>17.43</v>
+      </c>
+      <c r="E194" s="2">
+        <v>0</v>
+      </c>
+      <c r="F194" s="3">
+        <v>0.682</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" t="s">
+        <v>12</v>
+      </c>
+      <c r="B195">
+        <v>2</v>
+      </c>
+      <c r="C195" s="1">
+        <v>46120</v>
+      </c>
+      <c r="D195" s="2">
+        <v>17.47</v>
+      </c>
+      <c r="E195" s="2">
+        <v>35</v>
+      </c>
+      <c r="F195" s="3">
+        <v>0.702</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" t="s">
+        <v>12</v>
+      </c>
+      <c r="B196">
+        <v>3</v>
+      </c>
+      <c r="C196" s="1">
+        <v>46120</v>
+      </c>
+      <c r="D196" s="2">
+        <v>17.45</v>
+      </c>
+      <c r="E196" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="F196" s="3">
+        <v>0.716</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" t="s">
+        <v>12</v>
+      </c>
+      <c r="B197">
+        <v>4</v>
+      </c>
+      <c r="C197" s="1">
+        <v>46120</v>
+      </c>
+      <c r="D197" s="2">
+        <v>17.41</v>
+      </c>
+      <c r="E197" s="2">
+        <v>0</v>
+      </c>
+      <c r="F197" s="3">
+        <v>0.099</v>
+      </c>
     </row>
     <row r="198" spans="3:6">
       <c r="C198" s="1"/>
@@ -5829,41 +5885,35 @@
       <c r="E245" s="2"/>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="3:6">
+    <row r="246" spans="3:5">
       <c r="C246" s="1"/>
       <c r="D246" s="2"/>
       <c r="E246" s="2"/>
-      <c r="F246" s="3"/>
-    </row>
-    <row r="247" spans="3:6">
+    </row>
+    <row r="247" spans="3:5">
       <c r="C247" s="1"/>
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
-      <c r="F247" s="3"/>
-    </row>
-    <row r="248" spans="3:6">
+    </row>
+    <row r="248" spans="3:5">
       <c r="C248" s="1"/>
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
-      <c r="F248" s="3"/>
-    </row>
-    <row r="249" spans="3:6">
+    </row>
+    <row r="249" spans="3:5">
       <c r="C249" s="1"/>
       <c r="D249" s="2"/>
       <c r="E249" s="2"/>
-      <c r="F249" s="3"/>
-    </row>
-    <row r="250" spans="3:6">
+    </row>
+    <row r="250" spans="3:5">
       <c r="C250" s="1"/>
       <c r="D250" s="2"/>
       <c r="E250" s="2"/>
-      <c r="F250" s="3"/>
-    </row>
-    <row r="251" spans="3:6">
+    </row>
+    <row r="251" spans="3:5">
       <c r="C251" s="1"/>
       <c r="D251" s="2"/>
       <c r="E251" s="2"/>
-      <c r="F251" s="3"/>
     </row>
     <row r="252" spans="3:5">
       <c r="C252" s="1"/>
@@ -5975,43 +6025,13 @@
       <c r="D273" s="2"/>
       <c r="E273" s="2"/>
     </row>
-    <row r="274" spans="3:5">
-      <c r="C274" s="1"/>
+    <row r="274" spans="4:5">
       <c r="D274" s="2"/>
       <c r="E274" s="2"/>
     </row>
-    <row r="275" spans="3:5">
-      <c r="C275" s="1"/>
+    <row r="275" spans="4:5">
       <c r="D275" s="2"/>
       <c r="E275" s="2"/>
-    </row>
-    <row r="276" spans="3:5">
-      <c r="C276" s="1"/>
-      <c r="D276" s="2"/>
-      <c r="E276" s="2"/>
-    </row>
-    <row r="277" spans="3:5">
-      <c r="C277" s="1"/>
-      <c r="D277" s="2"/>
-      <c r="E277" s="2"/>
-    </row>
-    <row r="278" spans="3:5">
-      <c r="C278" s="1"/>
-      <c r="D278" s="2"/>
-      <c r="E278" s="2"/>
-    </row>
-    <row r="279" spans="3:5">
-      <c r="C279" s="1"/>
-      <c r="D279" s="2"/>
-      <c r="E279" s="2"/>
-    </row>
-    <row r="280" spans="4:5">
-      <c r="D280" s="2"/>
-      <c r="E280" s="2"/>
-    </row>
-    <row r="281" spans="4:5">
-      <c r="D281" s="2"/>
-      <c r="E281" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1561,8 +1561,34 @@
         <v>0.393</v>
       </c>
     </row>
-    <row r="12" spans="6:6">
-      <c r="F12" s="1"/>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>40</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>492</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46122</v>
+      </c>
+      <c r="G12" s="2">
+        <v>17.8</v>
+      </c>
+      <c r="H12" s="2">
+        <v>22.64</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.468</v>
+      </c>
     </row>
     <row r="13" spans="6:6">
       <c r="F13" s="1"/>
@@ -5597,71 +5623,225 @@
         <v>0.099</v>
       </c>
     </row>
-    <row r="198" spans="3:6">
-      <c r="C198" s="1"/>
-      <c r="D198" s="2"/>
-      <c r="E198" s="2"/>
-      <c r="F198" s="3"/>
-    </row>
-    <row r="199" spans="3:6">
-      <c r="C199" s="1"/>
-      <c r="D199" s="2"/>
-      <c r="E199" s="2"/>
-      <c r="F199" s="3"/>
-    </row>
-    <row r="200" spans="3:6">
-      <c r="C200" s="1"/>
-      <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="3"/>
-    </row>
-    <row r="201" spans="3:6">
-      <c r="C201" s="1"/>
-      <c r="D201" s="2"/>
-      <c r="E201" s="2"/>
-      <c r="F201" s="3"/>
-    </row>
-    <row r="202" spans="3:6">
-      <c r="C202" s="1"/>
-      <c r="D202" s="2"/>
-      <c r="E202" s="2"/>
-      <c r="F202" s="3"/>
-    </row>
-    <row r="203" spans="3:6">
-      <c r="C203" s="1"/>
-      <c r="D203" s="2"/>
-      <c r="E203" s="2"/>
-      <c r="F203" s="3"/>
-    </row>
-    <row r="204" spans="3:6">
-      <c r="C204" s="1"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="3"/>
-    </row>
-    <row r="205" spans="3:6">
-      <c r="C205" s="1"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="3"/>
-    </row>
-    <row r="206" spans="3:6">
-      <c r="C206" s="1"/>
-      <c r="D206" s="2"/>
-      <c r="E206" s="2"/>
-      <c r="F206" s="3"/>
-    </row>
-    <row r="207" spans="3:6">
-      <c r="C207" s="1"/>
-      <c r="D207" s="2"/>
-      <c r="E207" s="2"/>
-      <c r="F207" s="3"/>
-    </row>
-    <row r="208" spans="3:6">
-      <c r="C208" s="1"/>
-      <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
-      <c r="F208" s="3"/>
+    <row r="198" spans="1:6">
+      <c r="A198" t="s">
+        <v>9</v>
+      </c>
+      <c r="B198">
+        <v>1</v>
+      </c>
+      <c r="C198" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D198" s="2">
+        <v>20.78</v>
+      </c>
+      <c r="E198" s="2">
+        <v>1.21</v>
+      </c>
+      <c r="F198" s="3">
+        <v>6.649</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>9</v>
+      </c>
+      <c r="B199">
+        <v>2</v>
+      </c>
+      <c r="C199" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D199" s="2">
+        <v>21.2</v>
+      </c>
+      <c r="E199" s="2">
+        <v>3.49</v>
+      </c>
+      <c r="F199" s="3">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>9</v>
+      </c>
+      <c r="B200" t="s">
+        <v>10</v>
+      </c>
+      <c r="C200" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D200" s="2">
+        <v>20.38</v>
+      </c>
+      <c r="E200" s="2">
+        <v>11.16</v>
+      </c>
+      <c r="F200" s="3">
+        <v>4.4692</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>9</v>
+      </c>
+      <c r="B201">
+        <v>3</v>
+      </c>
+      <c r="C201" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D201" s="2">
+        <v>20.68</v>
+      </c>
+      <c r="E201" s="2">
+        <v>11.52</v>
+      </c>
+      <c r="F201" s="3">
+        <v>4.692</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" t="s">
+        <v>9</v>
+      </c>
+      <c r="B202">
+        <v>4</v>
+      </c>
+      <c r="C202" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D202" s="2">
+        <v>20.75</v>
+      </c>
+      <c r="E202" s="2">
+        <v>68.74</v>
+      </c>
+      <c r="F202" s="3">
+        <v>2.089</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>9</v>
+      </c>
+      <c r="B203" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D203" s="2">
+        <v>20.63</v>
+      </c>
+      <c r="E203" s="2">
+        <v>24.85</v>
+      </c>
+      <c r="F203" s="3">
+        <v>2.255</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>12</v>
+      </c>
+      <c r="B204">
+        <v>1</v>
+      </c>
+      <c r="C204" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D204" s="2">
+        <v>22.63</v>
+      </c>
+      <c r="E204" s="2">
+        <v>9</v>
+      </c>
+      <c r="F204" s="3">
+        <v>0.734</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>12</v>
+      </c>
+      <c r="B205">
+        <v>2</v>
+      </c>
+      <c r="C205" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D205" s="2">
+        <v>22.56</v>
+      </c>
+      <c r="E205" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="F205" s="3">
+        <v>0.672</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" t="s">
+        <v>12</v>
+      </c>
+      <c r="B206">
+        <v>3</v>
+      </c>
+      <c r="C206" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D206" s="2">
+        <v>22.61</v>
+      </c>
+      <c r="E206" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="F206" s="3">
+        <v>0.685</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" t="s">
+        <v>12</v>
+      </c>
+      <c r="B207">
+        <v>4</v>
+      </c>
+      <c r="C207" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D207" s="2">
+        <v>22.63</v>
+      </c>
+      <c r="E207" s="2">
+        <v>9.8</v>
+      </c>
+      <c r="F207" s="3">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" t="s">
+        <v>12</v>
+      </c>
+      <c r="B208">
+        <v>5</v>
+      </c>
+      <c r="C208" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D208" s="2">
+        <v>22.64</v>
+      </c>
+      <c r="E208" s="2">
+        <v>17.8</v>
+      </c>
+      <c r="F208" s="3">
+        <v>0.468</v>
+      </c>
     </row>
     <row r="209" spans="3:6">
       <c r="C209" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="13545" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -5843,71 +5843,225 @@
         <v>0.468</v>
       </c>
     </row>
-    <row r="209" spans="3:6">
-      <c r="C209" s="1"/>
-      <c r="D209" s="2"/>
-      <c r="E209" s="2"/>
-      <c r="F209" s="3"/>
-    </row>
-    <row r="210" spans="3:6">
-      <c r="C210" s="1"/>
-      <c r="D210" s="2"/>
-      <c r="E210" s="2"/>
-      <c r="F210" s="3"/>
-    </row>
-    <row r="211" spans="3:6">
-      <c r="C211" s="1"/>
-      <c r="D211" s="2"/>
-      <c r="E211" s="2"/>
-      <c r="F211" s="3"/>
-    </row>
-    <row r="212" spans="3:6">
-      <c r="C212" s="1"/>
-      <c r="D212" s="2"/>
-      <c r="E212" s="2"/>
-      <c r="F212" s="3"/>
-    </row>
-    <row r="213" spans="3:6">
-      <c r="C213" s="1"/>
-      <c r="D213" s="2"/>
-      <c r="E213" s="2"/>
-      <c r="F213" s="3"/>
-    </row>
-    <row r="214" spans="3:6">
-      <c r="C214" s="1"/>
-      <c r="D214" s="2"/>
-      <c r="E214" s="2"/>
-      <c r="F214" s="3"/>
-    </row>
-    <row r="215" spans="3:6">
-      <c r="C215" s="1"/>
-      <c r="D215" s="2"/>
-      <c r="E215" s="2"/>
-      <c r="F215" s="3"/>
-    </row>
-    <row r="216" spans="3:6">
-      <c r="C216" s="1"/>
-      <c r="D216" s="2"/>
-      <c r="E216" s="2"/>
-      <c r="F216" s="3"/>
-    </row>
-    <row r="217" spans="3:6">
-      <c r="C217" s="1"/>
-      <c r="D217" s="2"/>
-      <c r="E217" s="2"/>
-      <c r="F217" s="3"/>
-    </row>
-    <row r="218" spans="3:6">
-      <c r="C218" s="1"/>
-      <c r="D218" s="2"/>
-      <c r="E218" s="2"/>
-      <c r="F218" s="3"/>
-    </row>
-    <row r="219" spans="3:6">
-      <c r="C219" s="1"/>
-      <c r="D219" s="2"/>
-      <c r="E219" s="2"/>
-      <c r="F219" s="3"/>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>9</v>
+      </c>
+      <c r="B209">
+        <v>1</v>
+      </c>
+      <c r="C209" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D209" s="2">
+        <v>20.52</v>
+      </c>
+      <c r="E209" s="2">
+        <v>5.56</v>
+      </c>
+      <c r="F209" s="3">
+        <v>4.824</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>9</v>
+      </c>
+      <c r="B210">
+        <v>2</v>
+      </c>
+      <c r="C210" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D210" s="2">
+        <v>20.71</v>
+      </c>
+      <c r="E210" s="2">
+        <v>2.28</v>
+      </c>
+      <c r="F210" s="3">
+        <v>3.174</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>9</v>
+      </c>
+      <c r="B211" t="s">
+        <v>10</v>
+      </c>
+      <c r="C211" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D211" s="2">
+        <v>20.64</v>
+      </c>
+      <c r="E211" s="2">
+        <v>10.76</v>
+      </c>
+      <c r="F211" s="3">
+        <v>1.575</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>9</v>
+      </c>
+      <c r="B212">
+        <v>3</v>
+      </c>
+      <c r="C212" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D212" s="2">
+        <v>20.81</v>
+      </c>
+      <c r="E212" s="2">
+        <v>15.41</v>
+      </c>
+      <c r="F212" s="3">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" t="s">
+        <v>9</v>
+      </c>
+      <c r="B213">
+        <v>4</v>
+      </c>
+      <c r="C213" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D213" s="2">
+        <v>21.06</v>
+      </c>
+      <c r="E213" s="2">
+        <v>70.62</v>
+      </c>
+      <c r="F213" s="3">
+        <v>3.145</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" t="s">
+        <v>9</v>
+      </c>
+      <c r="B214" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D214" s="2">
+        <v>21.15</v>
+      </c>
+      <c r="E214" s="2">
+        <v>20.79</v>
+      </c>
+      <c r="F214" s="3">
+        <v>2.222</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" t="s">
+        <v>12</v>
+      </c>
+      <c r="B215">
+        <v>1</v>
+      </c>
+      <c r="C215" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D215" s="2">
+        <v>16.23</v>
+      </c>
+      <c r="E215" s="2">
+        <v>0</v>
+      </c>
+      <c r="F215" s="3">
+        <v>0.659</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" t="s">
+        <v>12</v>
+      </c>
+      <c r="B216">
+        <v>2</v>
+      </c>
+      <c r="C216" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D216" s="2">
+        <v>16.26</v>
+      </c>
+      <c r="E216" s="2">
+        <v>34.6</v>
+      </c>
+      <c r="F216" s="3">
+        <v>0.592</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" t="s">
+        <v>12</v>
+      </c>
+      <c r="B217">
+        <v>3</v>
+      </c>
+      <c r="C217" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D217" s="2">
+        <v>16.41</v>
+      </c>
+      <c r="E217" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="F217" s="3">
+        <v>0.841</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" t="s">
+        <v>12</v>
+      </c>
+      <c r="B218">
+        <v>4</v>
+      </c>
+      <c r="C218" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D218" s="2">
+        <v>16.33</v>
+      </c>
+      <c r="E218" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="F218" s="3">
+        <v>0.227</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" t="s">
+        <v>12</v>
+      </c>
+      <c r="B219">
+        <v>5</v>
+      </c>
+      <c r="C219" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D219" s="2">
+        <v>16.24</v>
+      </c>
+      <c r="E219" s="2">
+        <v>27.2</v>
+      </c>
+      <c r="F219" s="3">
+        <v>0.457</v>
+      </c>
     </row>
     <row r="220" spans="3:6">
       <c r="C220" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -6063,35 +6063,105 @@
         <v>0.457</v>
       </c>
     </row>
-    <row r="220" spans="3:6">
-      <c r="C220" s="1"/>
-      <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
-      <c r="F220" s="3"/>
-    </row>
-    <row r="221" spans="3:6">
-      <c r="C221" s="1"/>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
-      <c r="F221" s="3"/>
-    </row>
-    <row r="222" spans="3:6">
-      <c r="C222" s="1"/>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-      <c r="F222" s="3"/>
-    </row>
-    <row r="223" spans="3:6">
-      <c r="C223" s="1"/>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
-      <c r="F223" s="3"/>
-    </row>
-    <row r="224" spans="3:6">
-      <c r="C224" s="1"/>
-      <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
-      <c r="F224" s="3"/>
+    <row r="220" spans="1:6">
+      <c r="A220" t="s">
+        <v>12</v>
+      </c>
+      <c r="B220">
+        <v>1</v>
+      </c>
+      <c r="C220" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D220" s="2">
+        <v>19.87</v>
+      </c>
+      <c r="E220" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="F220" s="3">
+        <v>0.668</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" t="s">
+        <v>12</v>
+      </c>
+      <c r="B221">
+        <v>2</v>
+      </c>
+      <c r="C221" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D221" s="2">
+        <v>19.82</v>
+      </c>
+      <c r="E221" s="2">
+        <v>30</v>
+      </c>
+      <c r="F221" s="3">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" t="s">
+        <v>12</v>
+      </c>
+      <c r="B222">
+        <v>3</v>
+      </c>
+      <c r="C222" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D222" s="2">
+        <v>19.77</v>
+      </c>
+      <c r="E222" s="2">
+        <v>3</v>
+      </c>
+      <c r="F222" s="3">
+        <v>0.783</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" t="s">
+        <v>12</v>
+      </c>
+      <c r="B223">
+        <v>4</v>
+      </c>
+      <c r="C223" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D223" s="2">
+        <v>19.79</v>
+      </c>
+      <c r="E223" s="2">
+        <v>6</v>
+      </c>
+      <c r="F223" s="3">
+        <v>0.271</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" t="s">
+        <v>12</v>
+      </c>
+      <c r="B224">
+        <v>5</v>
+      </c>
+      <c r="C224" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D224" s="2">
+        <v>19.81</v>
+      </c>
+      <c r="E224" s="2">
+        <v>26</v>
+      </c>
+      <c r="F224" s="3">
+        <v>0.491</v>
+      </c>
     </row>
     <row r="225" spans="3:6">
       <c r="C225" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -6163,35 +6163,105 @@
         <v>0.491</v>
       </c>
     </row>
-    <row r="225" spans="3:6">
-      <c r="C225" s="1"/>
-      <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
-      <c r="F225" s="3"/>
-    </row>
-    <row r="226" spans="3:6">
-      <c r="C226" s="1"/>
-      <c r="D226" s="2"/>
-      <c r="E226" s="2"/>
-      <c r="F226" s="3"/>
-    </row>
-    <row r="227" spans="3:6">
-      <c r="C227" s="1"/>
-      <c r="D227" s="2"/>
-      <c r="E227" s="2"/>
-      <c r="F227" s="3"/>
-    </row>
-    <row r="228" spans="3:6">
-      <c r="C228" s="1"/>
-      <c r="D228" s="2"/>
-      <c r="E228" s="2"/>
-      <c r="F228" s="3"/>
-    </row>
-    <row r="229" spans="3:6">
-      <c r="C229" s="1"/>
-      <c r="D229" s="2"/>
-      <c r="E229" s="2"/>
-      <c r="F229" s="3"/>
+    <row r="225" spans="1:6">
+      <c r="A225" t="s">
+        <v>12</v>
+      </c>
+      <c r="B225">
+        <v>1</v>
+      </c>
+      <c r="C225" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D225" s="2">
+        <v>19.87</v>
+      </c>
+      <c r="E225" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="F225" s="3">
+        <v>0.668</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" t="s">
+        <v>12</v>
+      </c>
+      <c r="B226">
+        <v>2</v>
+      </c>
+      <c r="C226" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D226" s="2">
+        <v>19.82</v>
+      </c>
+      <c r="E226" s="2">
+        <v>30</v>
+      </c>
+      <c r="F226" s="3">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227">
+        <v>3</v>
+      </c>
+      <c r="C227" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D227" s="2">
+        <v>19.77</v>
+      </c>
+      <c r="E227" s="2">
+        <v>3</v>
+      </c>
+      <c r="F227" s="3">
+        <v>0.783</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" t="s">
+        <v>12</v>
+      </c>
+      <c r="B228">
+        <v>4</v>
+      </c>
+      <c r="C228" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D228" s="2">
+        <v>19.79</v>
+      </c>
+      <c r="E228" s="2">
+        <v>6</v>
+      </c>
+      <c r="F228" s="3">
+        <v>0.271</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" t="s">
+        <v>12</v>
+      </c>
+      <c r="B229">
+        <v>5</v>
+      </c>
+      <c r="C229" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D229" s="2">
+        <v>19.81</v>
+      </c>
+      <c r="E229" s="2">
+        <v>26</v>
+      </c>
+      <c r="F229" s="3">
+        <v>0.491</v>
+      </c>
     </row>
     <row r="230" spans="3:6">
       <c r="C230" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -6263,41 +6263,125 @@
         <v>0.491</v>
       </c>
     </row>
-    <row r="230" spans="3:6">
-      <c r="C230" s="1"/>
-      <c r="D230" s="2"/>
-      <c r="E230" s="2"/>
-      <c r="F230" s="3"/>
-    </row>
-    <row r="231" spans="3:6">
-      <c r="C231" s="1"/>
-      <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-      <c r="F231" s="3"/>
-    </row>
-    <row r="232" spans="3:6">
-      <c r="C232" s="1"/>
-      <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
-      <c r="F232" s="3"/>
-    </row>
-    <row r="233" spans="3:6">
-      <c r="C233" s="1"/>
-      <c r="D233" s="2"/>
-      <c r="E233" s="2"/>
-      <c r="F233" s="3"/>
-    </row>
-    <row r="234" spans="3:6">
-      <c r="C234" s="1"/>
-      <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
-      <c r="F234" s="3"/>
-    </row>
-    <row r="235" spans="3:6">
-      <c r="C235" s="1"/>
-      <c r="D235" s="2"/>
-      <c r="E235" s="2"/>
-      <c r="F235" s="3"/>
+    <row r="230" spans="1:6">
+      <c r="A230" t="s">
+        <v>9</v>
+      </c>
+      <c r="B230">
+        <v>1</v>
+      </c>
+      <c r="C230" s="1">
+        <v>46132</v>
+      </c>
+      <c r="D230" s="2">
+        <v>21.24</v>
+      </c>
+      <c r="E230" s="2">
+        <v>2.54</v>
+      </c>
+      <c r="F230" s="3">
+        <v>5.208</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" t="s">
+        <v>9</v>
+      </c>
+      <c r="B231">
+        <v>2</v>
+      </c>
+      <c r="C231" s="1">
+        <v>46132</v>
+      </c>
+      <c r="D231" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="E231" s="2">
+        <v>4.78</v>
+      </c>
+      <c r="F231" s="3">
+        <v>2.735</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" t="s">
+        <v>9</v>
+      </c>
+      <c r="B232" t="s">
+        <v>10</v>
+      </c>
+      <c r="C232" s="1">
+        <v>46132</v>
+      </c>
+      <c r="D232" s="2">
+        <v>21.01</v>
+      </c>
+      <c r="E232" s="2">
+        <v>8.78</v>
+      </c>
+      <c r="F232" s="3">
+        <v>2.331</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" t="s">
+        <v>9</v>
+      </c>
+      <c r="B233">
+        <v>3</v>
+      </c>
+      <c r="C233" s="1">
+        <v>46132</v>
+      </c>
+      <c r="D233" s="2">
+        <v>21.36</v>
+      </c>
+      <c r="E233" s="2">
+        <v>13.28</v>
+      </c>
+      <c r="F233" s="3">
+        <v>4.321</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" t="s">
+        <v>9</v>
+      </c>
+      <c r="B234">
+        <v>4</v>
+      </c>
+      <c r="C234" s="1">
+        <v>46132</v>
+      </c>
+      <c r="D234" s="2">
+        <v>21.56</v>
+      </c>
+      <c r="E234" s="2">
+        <v>59.68</v>
+      </c>
+      <c r="F234" s="3">
+        <v>3.022</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" t="s">
+        <v>9</v>
+      </c>
+      <c r="B235" t="s">
+        <v>11</v>
+      </c>
+      <c r="C235" s="1">
+        <v>46132</v>
+      </c>
+      <c r="D235" s="2">
+        <v>21.97</v>
+      </c>
+      <c r="E235" s="2">
+        <v>0.59</v>
+      </c>
+      <c r="F235" s="3">
+        <v>1.76</v>
+      </c>
     </row>
     <row r="236" spans="3:6">
       <c r="C236" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -6383,70 +6383,225 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="236" spans="3:6">
-      <c r="C236" s="1"/>
-      <c r="D236" s="2"/>
-      <c r="E236" s="2"/>
-      <c r="F236" s="3"/>
-    </row>
-    <row r="237" spans="3:6">
-      <c r="C237" s="1"/>
-      <c r="D237" s="2"/>
-      <c r="E237" s="2"/>
-      <c r="F237" s="3"/>
-    </row>
-    <row r="238" spans="3:6">
-      <c r="C238" s="1"/>
-      <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
-      <c r="F238" s="3"/>
-    </row>
-    <row r="239" spans="3:6">
-      <c r="C239" s="1"/>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
-      <c r="F239" s="3"/>
-    </row>
-    <row r="240" spans="3:6">
-      <c r="C240" s="1"/>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-      <c r="F240" s="3"/>
-    </row>
-    <row r="241" spans="3:6">
-      <c r="C241" s="1"/>
-      <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
-      <c r="F241" s="3"/>
-    </row>
-    <row r="242" spans="3:6">
-      <c r="C242" s="1"/>
-      <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
-      <c r="F242" s="3"/>
-    </row>
-    <row r="243" spans="3:6">
-      <c r="C243" s="1"/>
-      <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
-      <c r="F243" s="3"/>
-    </row>
-    <row r="244" spans="3:6">
-      <c r="C244" s="1"/>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
-      <c r="F244" s="3"/>
-    </row>
-    <row r="245" spans="3:6">
-      <c r="C245" s="1"/>
-      <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
-      <c r="F245" s="3"/>
-    </row>
-    <row r="246" spans="3:5">
-      <c r="C246" s="1"/>
-      <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
+    <row r="236" spans="1:6">
+      <c r="A236" t="s">
+        <v>9</v>
+      </c>
+      <c r="B236">
+        <v>1</v>
+      </c>
+      <c r="C236" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D236" s="2">
+        <v>21.52</v>
+      </c>
+      <c r="E236" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="F236" s="3">
+        <v>5.125</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" t="s">
+        <v>9</v>
+      </c>
+      <c r="B237">
+        <v>2</v>
+      </c>
+      <c r="C237" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D237" s="2">
+        <v>21.43</v>
+      </c>
+      <c r="E237" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="F237" s="3">
+        <v>2.674</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" t="s">
+        <v>9</v>
+      </c>
+      <c r="B238" t="s">
+        <v>10</v>
+      </c>
+      <c r="C238" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D238" s="2">
+        <v>21.55</v>
+      </c>
+      <c r="E238" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="F238" s="3">
+        <v>1.716</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" t="s">
+        <v>9</v>
+      </c>
+      <c r="B239">
+        <v>3</v>
+      </c>
+      <c r="C239" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D239" s="2">
+        <v>21.39</v>
+      </c>
+      <c r="E239" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="F239" s="3">
+        <v>4.972</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" t="s">
+        <v>9</v>
+      </c>
+      <c r="B240">
+        <v>4</v>
+      </c>
+      <c r="C240" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D240" s="2">
+        <v>21.44</v>
+      </c>
+      <c r="E240" s="2">
+        <v>54.4</v>
+      </c>
+      <c r="F240" s="3">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" t="s">
+        <v>9</v>
+      </c>
+      <c r="B241" t="s">
+        <v>11</v>
+      </c>
+      <c r="C241" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D241" s="2">
+        <v>21.54</v>
+      </c>
+      <c r="E241" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="F241" s="3">
+        <v>1.118</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" t="s">
+        <v>12</v>
+      </c>
+      <c r="B242">
+        <v>1</v>
+      </c>
+      <c r="C242" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D242" s="2">
+        <v>21.46</v>
+      </c>
+      <c r="E242" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="F242" s="3">
+        <v>0.592</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" t="s">
+        <v>12</v>
+      </c>
+      <c r="B243">
+        <v>2</v>
+      </c>
+      <c r="C243" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D243" s="2">
+        <v>21.54</v>
+      </c>
+      <c r="E243" s="2">
+        <v>42.8</v>
+      </c>
+      <c r="F243" s="3">
+        <v>0.618</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" t="s">
+        <v>12</v>
+      </c>
+      <c r="B244">
+        <v>3</v>
+      </c>
+      <c r="C244" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D244" s="2">
+        <v>21.42</v>
+      </c>
+      <c r="E244" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="F244" s="3">
+        <v>1.233</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" t="s">
+        <v>12</v>
+      </c>
+      <c r="B245">
+        <v>4</v>
+      </c>
+      <c r="C245" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D245" s="2">
+        <v>21.39</v>
+      </c>
+      <c r="E245" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="F245" s="3">
+        <v>0.481</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" t="s">
+        <v>12</v>
+      </c>
+      <c r="B246">
+        <v>5</v>
+      </c>
+      <c r="C246" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D246" s="2">
+        <v>21.44</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45</v>
+      </c>
+      <c r="F246" s="3">
+        <v>0.568</v>
+      </c>
     </row>
     <row r="247" spans="3:5">
       <c r="C247" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -6603,30 +6603,105 @@
         <v>0.568</v>
       </c>
     </row>
-    <row r="247" spans="3:5">
-      <c r="C247" s="1"/>
-      <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
-    </row>
-    <row r="248" spans="3:5">
-      <c r="C248" s="1"/>
-      <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
-    </row>
-    <row r="249" spans="3:5">
-      <c r="C249" s="1"/>
-      <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
-    </row>
-    <row r="250" spans="3:5">
-      <c r="C250" s="1"/>
-      <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
-    </row>
-    <row r="251" spans="3:5">
-      <c r="C251" s="1"/>
-      <c r="D251" s="2"/>
-      <c r="E251" s="2"/>
+    <row r="247" spans="1:6">
+      <c r="A247" t="s">
+        <v>12</v>
+      </c>
+      <c r="B247">
+        <v>1</v>
+      </c>
+      <c r="C247" s="1">
+        <v>46134</v>
+      </c>
+      <c r="D247" s="2">
+        <v>19.96</v>
+      </c>
+      <c r="E247" s="2">
+        <v>0.31</v>
+      </c>
+      <c r="F247" s="3">
+        <v>0.564</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" t="s">
+        <v>12</v>
+      </c>
+      <c r="B248">
+        <v>2</v>
+      </c>
+      <c r="C248" s="1">
+        <v>46134</v>
+      </c>
+      <c r="D248" s="2">
+        <v>19.95</v>
+      </c>
+      <c r="E248" s="2">
+        <v>29.25</v>
+      </c>
+      <c r="F248" s="3">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" t="s">
+        <v>12</v>
+      </c>
+      <c r="B249">
+        <v>3</v>
+      </c>
+      <c r="C249" s="1">
+        <v>46134</v>
+      </c>
+      <c r="D249" s="2">
+        <v>19.92</v>
+      </c>
+      <c r="E249" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="F249" s="3">
+        <v>0.619</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" t="s">
+        <v>12</v>
+      </c>
+      <c r="B250">
+        <v>4</v>
+      </c>
+      <c r="C250" s="1">
+        <v>46134</v>
+      </c>
+      <c r="D250" s="2">
+        <v>19.95</v>
+      </c>
+      <c r="E250" s="2">
+        <v>7.03</v>
+      </c>
+      <c r="F250" s="3">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" t="s">
+        <v>12</v>
+      </c>
+      <c r="B251">
+        <v>5</v>
+      </c>
+      <c r="C251" s="1">
+        <v>46134</v>
+      </c>
+      <c r="D251" s="2">
+        <v>19.89</v>
+      </c>
+      <c r="E251" s="2">
+        <v>34.09</v>
+      </c>
+      <c r="F251" s="3">
+        <v>1.803</v>
+      </c>
     </row>
     <row r="252" spans="3:5">
       <c r="C252" s="1"/>
@@ -6748,6 +6823,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -6703,35 +6703,125 @@
         <v>1.803</v>
       </c>
     </row>
-    <row r="252" spans="3:5">
-      <c r="C252" s="1"/>
-      <c r="D252" s="2"/>
-      <c r="E252" s="2"/>
-    </row>
-    <row r="253" spans="3:5">
-      <c r="C253" s="1"/>
-      <c r="D253" s="2"/>
-      <c r="E253" s="2"/>
-    </row>
-    <row r="254" spans="3:5">
-      <c r="C254" s="1"/>
-      <c r="D254" s="2"/>
-      <c r="E254" s="2"/>
-    </row>
-    <row r="255" spans="3:5">
-      <c r="C255" s="1"/>
-      <c r="D255" s="2"/>
-      <c r="E255" s="2"/>
-    </row>
-    <row r="256" spans="3:5">
-      <c r="C256" s="1"/>
-      <c r="D256" s="2"/>
-      <c r="E256" s="2"/>
-    </row>
-    <row r="257" spans="3:5">
-      <c r="C257" s="1"/>
-      <c r="D257" s="2"/>
-      <c r="E257" s="2"/>
+    <row r="252" spans="1:6">
+      <c r="A252" t="s">
+        <v>9</v>
+      </c>
+      <c r="B252">
+        <v>1</v>
+      </c>
+      <c r="C252" s="1">
+        <v>46136</v>
+      </c>
+      <c r="D252" s="2">
+        <v>29.33</v>
+      </c>
+      <c r="E252" s="2">
+        <v>1.73</v>
+      </c>
+      <c r="F252" s="3">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" t="s">
+        <v>9</v>
+      </c>
+      <c r="B253">
+        <v>2</v>
+      </c>
+      <c r="C253" s="1">
+        <v>46136</v>
+      </c>
+      <c r="D253" s="2">
+        <v>29.28</v>
+      </c>
+      <c r="E253" s="2">
+        <v>3.64</v>
+      </c>
+      <c r="F253" s="3">
+        <v>1.541</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" t="s">
+        <v>9</v>
+      </c>
+      <c r="B254" t="s">
+        <v>10</v>
+      </c>
+      <c r="C254" s="1">
+        <v>46136</v>
+      </c>
+      <c r="D254" s="2">
+        <v>29.27</v>
+      </c>
+      <c r="E254" s="2">
+        <v>6.21</v>
+      </c>
+      <c r="F254" s="3">
+        <v>2.278</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" t="s">
+        <v>9</v>
+      </c>
+      <c r="B255">
+        <v>3</v>
+      </c>
+      <c r="C255" s="1">
+        <v>46136</v>
+      </c>
+      <c r="D255" s="2">
+        <v>29.32</v>
+      </c>
+      <c r="E255" s="2">
+        <v>12.37</v>
+      </c>
+      <c r="F255" s="3">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" t="s">
+        <v>9</v>
+      </c>
+      <c r="B256">
+        <v>4</v>
+      </c>
+      <c r="C256" s="1">
+        <v>46136</v>
+      </c>
+      <c r="D256" s="2">
+        <v>29.38</v>
+      </c>
+      <c r="E256" s="2">
+        <v>47.29</v>
+      </c>
+      <c r="F256" s="3">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" t="s">
+        <v>9</v>
+      </c>
+      <c r="B257" t="s">
+        <v>11</v>
+      </c>
+      <c r="C257" s="1">
+        <v>46136</v>
+      </c>
+      <c r="D257" s="2">
+        <v>29.27</v>
+      </c>
+      <c r="E257" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="F257" s="3">
+        <v>2.318</v>
+      </c>
     </row>
     <row r="258" spans="3:5">
       <c r="C258" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -6823,30 +6823,105 @@
         <v>2.318</v>
       </c>
     </row>
-    <row r="258" spans="3:5">
-      <c r="C258" s="1"/>
-      <c r="D258" s="2"/>
-      <c r="E258" s="2"/>
-    </row>
-    <row r="259" spans="3:5">
-      <c r="C259" s="1"/>
-      <c r="D259" s="2"/>
-      <c r="E259" s="2"/>
-    </row>
-    <row r="260" spans="3:5">
-      <c r="C260" s="1"/>
-      <c r="D260" s="2"/>
-      <c r="E260" s="2"/>
-    </row>
-    <row r="261" spans="3:5">
-      <c r="C261" s="1"/>
-      <c r="D261" s="2"/>
-      <c r="E261" s="2"/>
-    </row>
-    <row r="262" spans="3:5">
-      <c r="C262" s="1"/>
-      <c r="D262" s="2"/>
-      <c r="E262" s="2"/>
+    <row r="258" spans="1:6">
+      <c r="A258" t="s">
+        <v>12</v>
+      </c>
+      <c r="B258">
+        <v>1</v>
+      </c>
+      <c r="C258" s="1">
+        <v>46137</v>
+      </c>
+      <c r="D258" s="2">
+        <v>33.18</v>
+      </c>
+      <c r="E258" s="2">
+        <v>0</v>
+      </c>
+      <c r="F258" s="3">
+        <v>3.347</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" t="s">
+        <v>12</v>
+      </c>
+      <c r="B259">
+        <v>2</v>
+      </c>
+      <c r="C259" s="1">
+        <v>46137</v>
+      </c>
+      <c r="D259" s="2">
+        <v>33.24</v>
+      </c>
+      <c r="E259" s="2">
+        <v>25.59</v>
+      </c>
+      <c r="F259" s="3">
+        <v>3.531</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" t="s">
+        <v>12</v>
+      </c>
+      <c r="B260">
+        <v>3</v>
+      </c>
+      <c r="C260" s="1">
+        <v>46137</v>
+      </c>
+      <c r="D260" s="2">
+        <v>33.08</v>
+      </c>
+      <c r="E260" s="2">
+        <v>2.45</v>
+      </c>
+      <c r="F260" s="3">
+        <v>3.333</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" t="s">
+        <v>12</v>
+      </c>
+      <c r="B261">
+        <v>4</v>
+      </c>
+      <c r="C261" s="1">
+        <v>46137</v>
+      </c>
+      <c r="D261" s="2">
+        <v>33.26</v>
+      </c>
+      <c r="E261" s="2">
+        <v>7.22</v>
+      </c>
+      <c r="F261" s="3">
+        <v>3.283</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" t="s">
+        <v>12</v>
+      </c>
+      <c r="B262">
+        <v>5</v>
+      </c>
+      <c r="C262" s="1">
+        <v>46137</v>
+      </c>
+      <c r="D262" s="2">
+        <v>33.28</v>
+      </c>
+      <c r="E262" s="2">
+        <v>29.88</v>
+      </c>
+      <c r="F262" s="3">
+        <v>2.298</v>
+      </c>
     </row>
     <row r="263" spans="3:5">
       <c r="C263" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -6923,30 +6923,105 @@
         <v>2.298</v>
       </c>
     </row>
-    <row r="263" spans="3:5">
-      <c r="C263" s="1"/>
-      <c r="D263" s="2"/>
-      <c r="E263" s="2"/>
-    </row>
-    <row r="264" spans="3:5">
-      <c r="C264" s="1"/>
-      <c r="D264" s="2"/>
-      <c r="E264" s="2"/>
-    </row>
-    <row r="265" spans="3:5">
-      <c r="C265" s="1"/>
-      <c r="D265" s="2"/>
-      <c r="E265" s="2"/>
-    </row>
-    <row r="266" spans="3:5">
-      <c r="C266" s="1"/>
-      <c r="D266" s="2"/>
-      <c r="E266" s="2"/>
-    </row>
-    <row r="267" spans="3:5">
-      <c r="C267" s="1"/>
-      <c r="D267" s="2"/>
-      <c r="E267" s="2"/>
+    <row r="263" spans="1:6">
+      <c r="A263" t="s">
+        <v>12</v>
+      </c>
+      <c r="B263">
+        <v>1</v>
+      </c>
+      <c r="C263" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D263" s="2">
+        <v>28.66</v>
+      </c>
+      <c r="E263" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="F263" s="3">
+        <v>2.974</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" t="s">
+        <v>12</v>
+      </c>
+      <c r="B264">
+        <v>2</v>
+      </c>
+      <c r="C264" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D264" s="2">
+        <v>28.63</v>
+      </c>
+      <c r="E264" s="2">
+        <v>22.6</v>
+      </c>
+      <c r="F264" s="3">
+        <v>1.868</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" t="s">
+        <v>12</v>
+      </c>
+      <c r="B265">
+        <v>3</v>
+      </c>
+      <c r="C265" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D265" s="2">
+        <v>28.64</v>
+      </c>
+      <c r="E265" s="2">
+        <v>5</v>
+      </c>
+      <c r="F265" s="3">
+        <v>3.217</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" t="s">
+        <v>12</v>
+      </c>
+      <c r="B266">
+        <v>4</v>
+      </c>
+      <c r="C266" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D266" s="2">
+        <v>28.62</v>
+      </c>
+      <c r="E266" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="F266" s="3">
+        <v>2.633</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" t="s">
+        <v>12</v>
+      </c>
+      <c r="B267">
+        <v>5</v>
+      </c>
+      <c r="C267" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D267" s="2">
+        <v>28.62</v>
+      </c>
+      <c r="E267" s="2">
+        <v>29.6</v>
+      </c>
+      <c r="F267" s="3">
+        <v>1.462</v>
+      </c>
     </row>
     <row r="268" spans="3:5">
       <c r="C268" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -7023,43 +7023,225 @@
         <v>1.462</v>
       </c>
     </row>
-    <row r="268" spans="3:5">
-      <c r="C268" s="1"/>
-      <c r="D268" s="2"/>
-      <c r="E268" s="2"/>
-    </row>
-    <row r="269" spans="3:5">
-      <c r="C269" s="1"/>
-      <c r="D269" s="2"/>
-      <c r="E269" s="2"/>
-    </row>
-    <row r="270" spans="3:5">
-      <c r="C270" s="1"/>
-      <c r="D270" s="2"/>
-      <c r="E270" s="2"/>
-    </row>
-    <row r="271" spans="3:5">
-      <c r="C271" s="1"/>
-      <c r="D271" s="2"/>
-      <c r="E271" s="2"/>
-    </row>
-    <row r="272" spans="3:5">
-      <c r="C272" s="1"/>
-      <c r="D272" s="2"/>
-      <c r="E272" s="2"/>
-    </row>
-    <row r="273" spans="3:5">
-      <c r="C273" s="1"/>
-      <c r="D273" s="2"/>
-      <c r="E273" s="2"/>
-    </row>
-    <row r="274" spans="4:5">
-      <c r="D274" s="2"/>
-      <c r="E274" s="2"/>
-    </row>
-    <row r="275" spans="4:5">
-      <c r="D275" s="2"/>
-      <c r="E275" s="2"/>
+    <row r="268" spans="1:6">
+      <c r="A268" t="s">
+        <v>9</v>
+      </c>
+      <c r="B268">
+        <v>1</v>
+      </c>
+      <c r="C268" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D268" s="2">
+        <v>23.28</v>
+      </c>
+      <c r="E268" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="F268" s="3">
+        <v>5.523</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" t="s">
+        <v>9</v>
+      </c>
+      <c r="B269">
+        <v>2</v>
+      </c>
+      <c r="C269" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D269" s="2">
+        <v>23.74</v>
+      </c>
+      <c r="E269" s="2">
+        <v>2.13</v>
+      </c>
+      <c r="F269" s="3">
+        <v>2.559</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" t="s">
+        <v>9</v>
+      </c>
+      <c r="B270" t="s">
+        <v>10</v>
+      </c>
+      <c r="C270" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D270" s="2">
+        <v>23.36</v>
+      </c>
+      <c r="E270" s="2">
+        <v>2.16</v>
+      </c>
+      <c r="F270" s="3">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" t="s">
+        <v>9</v>
+      </c>
+      <c r="B271">
+        <v>3</v>
+      </c>
+      <c r="C271" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D271" s="2">
+        <v>23.75</v>
+      </c>
+      <c r="E271" s="2">
+        <v>6.02</v>
+      </c>
+      <c r="F271" s="3">
+        <v>4.076</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" t="s">
+        <v>9</v>
+      </c>
+      <c r="B272">
+        <v>4</v>
+      </c>
+      <c r="C272" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D272" s="2">
+        <v>24.07</v>
+      </c>
+      <c r="E272" s="2">
+        <v>36.34</v>
+      </c>
+      <c r="F272" s="3">
+        <v>3.312</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" t="s">
+        <v>9</v>
+      </c>
+      <c r="B273" t="s">
+        <v>11</v>
+      </c>
+      <c r="C273" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D273" s="2">
+        <v>24.19</v>
+      </c>
+      <c r="E273" s="2">
+        <v>2.48</v>
+      </c>
+      <c r="F273" s="3">
+        <v>4.558</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" t="s">
+        <v>12</v>
+      </c>
+      <c r="B274">
+        <v>1</v>
+      </c>
+      <c r="C274" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D274" s="2">
+        <v>28.24</v>
+      </c>
+      <c r="E274" s="2">
+        <v>0</v>
+      </c>
+      <c r="F274" s="3">
+        <v>2.773</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" t="s">
+        <v>12</v>
+      </c>
+      <c r="B275">
+        <v>2</v>
+      </c>
+      <c r="C275" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D275" s="2">
+        <v>28.22</v>
+      </c>
+      <c r="E275" s="2">
+        <v>19.28</v>
+      </c>
+      <c r="F275" s="3">
+        <v>2.989</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" t="s">
+        <v>12</v>
+      </c>
+      <c r="B276">
+        <v>3</v>
+      </c>
+      <c r="C276" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D276" s="2">
+        <v>28.26</v>
+      </c>
+      <c r="E276" s="2">
+        <v>1.97</v>
+      </c>
+      <c r="F276" s="3">
+        <v>2.828</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" t="s">
+        <v>12</v>
+      </c>
+      <c r="B277">
+        <v>4</v>
+      </c>
+      <c r="C277" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D277" s="2">
+        <v>28.27</v>
+      </c>
+      <c r="E277" s="2">
+        <v>4.83</v>
+      </c>
+      <c r="F277" s="3">
+        <v>2.804</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" t="s">
+        <v>12</v>
+      </c>
+      <c r="B278">
+        <v>5</v>
+      </c>
+      <c r="C278" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D278" s="2">
+        <v>28.24</v>
+      </c>
+      <c r="E278" s="2">
+        <v>26.47</v>
+      </c>
+      <c r="F278" s="3">
+        <v>3.02</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F288"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -7243,6 +7243,206 @@
         <v>3.02</v>
       </c>
     </row>
+    <row r="279" spans="1:6">
+      <c r="A279" t="s">
+        <v>12</v>
+      </c>
+      <c r="B279">
+        <v>1</v>
+      </c>
+      <c r="C279" s="1">
+        <v>46144</v>
+      </c>
+      <c r="D279" s="2">
+        <v>27.74</v>
+      </c>
+      <c r="E279" s="2">
+        <v>0</v>
+      </c>
+      <c r="F279" s="3">
+        <v>2.145</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" t="s">
+        <v>12</v>
+      </c>
+      <c r="B280">
+        <v>2</v>
+      </c>
+      <c r="C280" s="1">
+        <v>46144</v>
+      </c>
+      <c r="D280" s="2">
+        <v>27.68</v>
+      </c>
+      <c r="E280" s="2">
+        <v>28.69</v>
+      </c>
+      <c r="F280" s="3">
+        <v>2.433</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" t="s">
+        <v>12</v>
+      </c>
+      <c r="B281">
+        <v>3</v>
+      </c>
+      <c r="C281" s="1">
+        <v>46144</v>
+      </c>
+      <c r="D281" s="2">
+        <v>27.7</v>
+      </c>
+      <c r="E281" s="2">
+        <v>3.25</v>
+      </c>
+      <c r="F281" s="3">
+        <v>2.285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" t="s">
+        <v>12</v>
+      </c>
+      <c r="B282">
+        <v>4</v>
+      </c>
+      <c r="C282" s="1">
+        <v>46144</v>
+      </c>
+      <c r="D282" s="2">
+        <v>27.7</v>
+      </c>
+      <c r="E282" s="2">
+        <v>7.05</v>
+      </c>
+      <c r="F282" s="3">
+        <v>2.192</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" t="s">
+        <v>12</v>
+      </c>
+      <c r="B283">
+        <v>5</v>
+      </c>
+      <c r="C283" s="1">
+        <v>46144</v>
+      </c>
+      <c r="D283" s="2">
+        <v>27.7</v>
+      </c>
+      <c r="E283" s="2">
+        <v>31.39</v>
+      </c>
+      <c r="F283" s="3">
+        <v>2.567</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" t="s">
+        <v>12</v>
+      </c>
+      <c r="B284">
+        <v>1</v>
+      </c>
+      <c r="C284" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D284" s="2">
+        <v>24.23</v>
+      </c>
+      <c r="E284" s="2">
+        <v>0</v>
+      </c>
+      <c r="F284" s="3">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" t="s">
+        <v>12</v>
+      </c>
+      <c r="B285">
+        <v>2</v>
+      </c>
+      <c r="C285" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D285" s="2">
+        <v>24.21</v>
+      </c>
+      <c r="E285" s="2">
+        <v>3.88</v>
+      </c>
+      <c r="F285" s="3">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" t="s">
+        <v>12</v>
+      </c>
+      <c r="B286">
+        <v>3</v>
+      </c>
+      <c r="C286" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D286" s="2">
+        <v>24.24</v>
+      </c>
+      <c r="E286" s="2">
+        <v>0</v>
+      </c>
+      <c r="F286" s="3">
+        <v>1.926</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" t="s">
+        <v>12</v>
+      </c>
+      <c r="B287">
+        <v>4</v>
+      </c>
+      <c r="C287" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D287" s="2">
+        <v>24.14</v>
+      </c>
+      <c r="E287" s="2">
+        <v>0</v>
+      </c>
+      <c r="F287" s="3">
+        <v>1.941</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" t="s">
+        <v>12</v>
+      </c>
+      <c r="B288">
+        <v>5</v>
+      </c>
+      <c r="C288" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D288" s="2">
+        <v>24.22</v>
+      </c>
+      <c r="E288" s="2">
+        <v>0</v>
+      </c>
+      <c r="F288" s="3">
+        <v>2.181</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F288"/>
+  <dimension ref="A1:F299"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -7443,6 +7443,226 @@
         <v>2.181</v>
       </c>
     </row>
+    <row r="289" spans="1:6">
+      <c r="A289" t="s">
+        <v>9</v>
+      </c>
+      <c r="B289">
+        <v>1</v>
+      </c>
+      <c r="C289" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D289" s="2">
+        <v>21.87</v>
+      </c>
+      <c r="E289" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="F289" s="3">
+        <v>4.773</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" t="s">
+        <v>9</v>
+      </c>
+      <c r="B290">
+        <v>2</v>
+      </c>
+      <c r="C290" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D290" s="2">
+        <v>21.93</v>
+      </c>
+      <c r="E290" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="F290" s="3">
+        <v>3.164</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" t="s">
+        <v>9</v>
+      </c>
+      <c r="B291" t="s">
+        <v>10</v>
+      </c>
+      <c r="C291" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D291" s="2">
+        <v>21.96</v>
+      </c>
+      <c r="E291" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="F291" s="3">
+        <v>2.869</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" t="s">
+        <v>9</v>
+      </c>
+      <c r="B292">
+        <v>3</v>
+      </c>
+      <c r="C292" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D292" s="2">
+        <v>21.92</v>
+      </c>
+      <c r="E292" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="F292" s="3">
+        <v>4.728</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" t="s">
+        <v>9</v>
+      </c>
+      <c r="B293">
+        <v>4</v>
+      </c>
+      <c r="C293" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D293" s="2">
+        <v>21.95</v>
+      </c>
+      <c r="E293" s="2">
+        <v>42.4</v>
+      </c>
+      <c r="F293" s="3">
+        <v>3.715</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" t="s">
+        <v>9</v>
+      </c>
+      <c r="B294" t="s">
+        <v>11</v>
+      </c>
+      <c r="C294" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D294" s="2">
+        <v>21.93</v>
+      </c>
+      <c r="E294" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="F294" s="3">
+        <v>4.281</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" t="s">
+        <v>12</v>
+      </c>
+      <c r="B295">
+        <v>1</v>
+      </c>
+      <c r="C295" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D295" s="2">
+        <v>26.78</v>
+      </c>
+      <c r="E295" s="2">
+        <v>0</v>
+      </c>
+      <c r="F295" s="3">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" t="s">
+        <v>12</v>
+      </c>
+      <c r="B296">
+        <v>2</v>
+      </c>
+      <c r="C296" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D296" s="2">
+        <v>26.9</v>
+      </c>
+      <c r="E296" s="2">
+        <v>32.53</v>
+      </c>
+      <c r="F296" s="3">
+        <v>0.489</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" t="s">
+        <v>12</v>
+      </c>
+      <c r="B297">
+        <v>3</v>
+      </c>
+      <c r="C297" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D297" s="2">
+        <v>26.96</v>
+      </c>
+      <c r="E297" s="2">
+        <v>2.99</v>
+      </c>
+      <c r="F297" s="3">
+        <v>0.517</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" t="s">
+        <v>12</v>
+      </c>
+      <c r="B298">
+        <v>4</v>
+      </c>
+      <c r="C298" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D298" s="2">
+        <v>26.76</v>
+      </c>
+      <c r="E298" s="2">
+        <v>6.11</v>
+      </c>
+      <c r="F298" s="3">
+        <v>0.693</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" t="s">
+        <v>12</v>
+      </c>
+      <c r="B299">
+        <v>5</v>
+      </c>
+      <c r="C299" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D299" s="2">
+        <v>26.46</v>
+      </c>
+      <c r="E299" s="2">
+        <v>25</v>
+      </c>
+      <c r="F299" s="3">
+        <v>0.902</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F299"/>
+  <dimension ref="A1:F310"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -7663,6 +7663,226 @@
         <v>0.902</v>
       </c>
     </row>
+    <row r="300" spans="1:6">
+      <c r="A300" t="s">
+        <v>9</v>
+      </c>
+      <c r="B300">
+        <v>1</v>
+      </c>
+      <c r="C300" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D300" s="2">
+        <v>22.28</v>
+      </c>
+      <c r="E300" s="2">
+        <v>0.55</v>
+      </c>
+      <c r="F300" s="3">
+        <v>8.345</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" t="s">
+        <v>9</v>
+      </c>
+      <c r="B301">
+        <v>2</v>
+      </c>
+      <c r="C301" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D301" s="2">
+        <v>22.56</v>
+      </c>
+      <c r="E301" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="F301" s="3">
+        <v>1.499</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" t="s">
+        <v>9</v>
+      </c>
+      <c r="B302" t="s">
+        <v>10</v>
+      </c>
+      <c r="C302" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D302" s="2">
+        <v>22.4</v>
+      </c>
+      <c r="E302" s="2">
+        <v>8.15</v>
+      </c>
+      <c r="F302" s="3">
+        <v>3.481</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" t="s">
+        <v>9</v>
+      </c>
+      <c r="B303">
+        <v>3</v>
+      </c>
+      <c r="C303" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D303" s="2">
+        <v>22.61</v>
+      </c>
+      <c r="E303" s="2">
+        <v>13.81</v>
+      </c>
+      <c r="F303" s="3">
+        <v>7.611</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" t="s">
+        <v>9</v>
+      </c>
+      <c r="B304">
+        <v>4</v>
+      </c>
+      <c r="C304" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D304" s="2">
+        <v>23.77</v>
+      </c>
+      <c r="E304" s="2">
+        <v>4.79</v>
+      </c>
+      <c r="F304" s="3">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" t="s">
+        <v>9</v>
+      </c>
+      <c r="B305" t="s">
+        <v>11</v>
+      </c>
+      <c r="C305" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D305" s="2">
+        <v>23.86</v>
+      </c>
+      <c r="E305" s="2">
+        <v>1.76</v>
+      </c>
+      <c r="F305" s="3">
+        <v>5.625</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" t="s">
+        <v>12</v>
+      </c>
+      <c r="B306">
+        <v>1</v>
+      </c>
+      <c r="C306" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D306" s="2">
+        <v>29.88</v>
+      </c>
+      <c r="E306" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="F306" s="3">
+        <v>2.951</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" t="s">
+        <v>12</v>
+      </c>
+      <c r="B307">
+        <v>2</v>
+      </c>
+      <c r="C307" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D307" s="2">
+        <v>29.82</v>
+      </c>
+      <c r="E307" s="2">
+        <v>9.62</v>
+      </c>
+      <c r="F307" s="3">
+        <v>3.018</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" t="s">
+        <v>12</v>
+      </c>
+      <c r="B308">
+        <v>3</v>
+      </c>
+      <c r="C308" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D308" s="2">
+        <v>29.85</v>
+      </c>
+      <c r="E308" s="2">
+        <v>1.27</v>
+      </c>
+      <c r="F308" s="3">
+        <v>3.117</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" t="s">
+        <v>12</v>
+      </c>
+      <c r="B309">
+        <v>4</v>
+      </c>
+      <c r="C309" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D309" s="2">
+        <v>29.83</v>
+      </c>
+      <c r="E309" s="2">
+        <v>4.02</v>
+      </c>
+      <c r="F309" s="3">
+        <v>3.058</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" t="s">
+        <v>12</v>
+      </c>
+      <c r="B310">
+        <v>5</v>
+      </c>
+      <c r="C310" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D310" s="2">
+        <v>29.82</v>
+      </c>
+      <c r="E310" s="2">
+        <v>23.22</v>
+      </c>
+      <c r="F310" s="3">
+        <v>3.153</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F310"/>
+  <dimension ref="A1:F321"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -7883,6 +7883,226 @@
         <v>3.153</v>
       </c>
     </row>
+    <row r="311" spans="1:6">
+      <c r="A311" t="s">
+        <v>9</v>
+      </c>
+      <c r="B311">
+        <v>1</v>
+      </c>
+      <c r="C311" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D311" s="2">
+        <v>21.76</v>
+      </c>
+      <c r="E311" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="F311" s="3">
+        <v>10.196</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" t="s">
+        <v>9</v>
+      </c>
+      <c r="B312">
+        <v>2</v>
+      </c>
+      <c r="C312" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D312" s="2">
+        <v>22.13</v>
+      </c>
+      <c r="E312" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="F312" s="3">
+        <v>1.366</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" t="s">
+        <v>9</v>
+      </c>
+      <c r="B313" t="s">
+        <v>10</v>
+      </c>
+      <c r="C313" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D313" s="2">
+        <v>21.87</v>
+      </c>
+      <c r="E313" s="2">
+        <v>7.46</v>
+      </c>
+      <c r="F313" s="3">
+        <v>3.079</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" t="s">
+        <v>9</v>
+      </c>
+      <c r="B314">
+        <v>3</v>
+      </c>
+      <c r="C314" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D314" s="2">
+        <v>22.31</v>
+      </c>
+      <c r="E314" s="2">
+        <v>13.19</v>
+      </c>
+      <c r="F314" s="3">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" t="s">
+        <v>9</v>
+      </c>
+      <c r="B315">
+        <v>4</v>
+      </c>
+      <c r="C315" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D315" s="2">
+        <v>23.25</v>
+      </c>
+      <c r="E315" s="2">
+        <v>5.04</v>
+      </c>
+      <c r="F315" s="3">
+        <v>5.63</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" t="s">
+        <v>9</v>
+      </c>
+      <c r="B316" t="s">
+        <v>11</v>
+      </c>
+      <c r="C316" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D316" s="2">
+        <v>23.47</v>
+      </c>
+      <c r="E316" s="2">
+        <v>1.66</v>
+      </c>
+      <c r="F316" s="3">
+        <v>4.461</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" t="s">
+        <v>12</v>
+      </c>
+      <c r="B317">
+        <v>1</v>
+      </c>
+      <c r="C317" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D317" s="2">
+        <v>29.74</v>
+      </c>
+      <c r="E317" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="F317" s="3">
+        <v>2.859</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" t="s">
+        <v>12</v>
+      </c>
+      <c r="B318">
+        <v>2</v>
+      </c>
+      <c r="C318" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D318" s="2">
+        <v>29.7</v>
+      </c>
+      <c r="E318" s="2">
+        <v>9.11</v>
+      </c>
+      <c r="F318" s="3">
+        <v>2.979</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" t="s">
+        <v>12</v>
+      </c>
+      <c r="B319">
+        <v>3</v>
+      </c>
+      <c r="C319" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D319" s="2">
+        <v>29.75</v>
+      </c>
+      <c r="E319" s="2">
+        <v>1.32</v>
+      </c>
+      <c r="F319" s="3">
+        <v>2.912</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" t="s">
+        <v>12</v>
+      </c>
+      <c r="B320">
+        <v>4</v>
+      </c>
+      <c r="C320" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D320" s="2">
+        <v>29.71</v>
+      </c>
+      <c r="E320" s="2">
+        <v>3.61</v>
+      </c>
+      <c r="F320" s="3">
+        <v>2.812</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" t="s">
+        <v>12</v>
+      </c>
+      <c r="B321">
+        <v>5</v>
+      </c>
+      <c r="C321" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D321" s="2">
+        <v>29.74</v>
+      </c>
+      <c r="E321" s="2">
+        <v>22.47</v>
+      </c>
+      <c r="F321" s="3">
+        <v>3.225</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F321"/>
+  <dimension ref="A1:F332"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -8103,6 +8103,226 @@
         <v>3.225</v>
       </c>
     </row>
+    <row r="322" spans="1:6">
+      <c r="A322" t="s">
+        <v>9</v>
+      </c>
+      <c r="B322">
+        <v>1</v>
+      </c>
+      <c r="C322" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D322" s="2">
+        <v>20.25</v>
+      </c>
+      <c r="E322" s="2">
+        <v>0.14</v>
+      </c>
+      <c r="F322" s="3">
+        <v>9.491</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" t="s">
+        <v>9</v>
+      </c>
+      <c r="B323">
+        <v>2</v>
+      </c>
+      <c r="C323" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D323" s="2">
+        <v>20.76</v>
+      </c>
+      <c r="E323" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="F323" s="3">
+        <v>2.862</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" t="s">
+        <v>9</v>
+      </c>
+      <c r="B324" t="s">
+        <v>10</v>
+      </c>
+      <c r="C324" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D324" s="2">
+        <v>20.54</v>
+      </c>
+      <c r="E324" s="2">
+        <v>7.76</v>
+      </c>
+      <c r="F324" s="3">
+        <v>3.955</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" t="s">
+        <v>9</v>
+      </c>
+      <c r="B325">
+        <v>3</v>
+      </c>
+      <c r="C325" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D325" s="2">
+        <v>20.89</v>
+      </c>
+      <c r="E325" s="2">
+        <v>12.44</v>
+      </c>
+      <c r="F325" s="3">
+        <v>7.515</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" t="s">
+        <v>9</v>
+      </c>
+      <c r="B326">
+        <v>4</v>
+      </c>
+      <c r="C326" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D326" s="2">
+        <v>21.78</v>
+      </c>
+      <c r="E326" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="F326" s="3">
+        <v>5.356</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" t="s">
+        <v>9</v>
+      </c>
+      <c r="B327" t="s">
+        <v>11</v>
+      </c>
+      <c r="C327" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D327" s="2">
+        <v>21.89</v>
+      </c>
+      <c r="E327" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="F327" s="3">
+        <v>3.676</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" t="s">
+        <v>12</v>
+      </c>
+      <c r="B328">
+        <v>1</v>
+      </c>
+      <c r="C328" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D328" s="2">
+        <v>28.46</v>
+      </c>
+      <c r="E328" s="2">
+        <v>0</v>
+      </c>
+      <c r="F328" s="3">
+        <v>0.895</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" t="s">
+        <v>12</v>
+      </c>
+      <c r="B329">
+        <v>2</v>
+      </c>
+      <c r="C329" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D329" s="2">
+        <v>28.53</v>
+      </c>
+      <c r="E329" s="2">
+        <v>9.27</v>
+      </c>
+      <c r="F329" s="3">
+        <v>0.468</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" t="s">
+        <v>12</v>
+      </c>
+      <c r="B330">
+        <v>3</v>
+      </c>
+      <c r="C330" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D330" s="2">
+        <v>28.52</v>
+      </c>
+      <c r="E330" s="2">
+        <v>1.17</v>
+      </c>
+      <c r="F330" s="3">
+        <v>0.531</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" t="s">
+        <v>12</v>
+      </c>
+      <c r="B331">
+        <v>4</v>
+      </c>
+      <c r="C331" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D331" s="2">
+        <v>28.52</v>
+      </c>
+      <c r="E331" s="2">
+        <v>3.29</v>
+      </c>
+      <c r="F331" s="3">
+        <v>0.691</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" t="s">
+        <v>12</v>
+      </c>
+      <c r="B332">
+        <v>5</v>
+      </c>
+      <c r="C332" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D332" s="2">
+        <v>28.51</v>
+      </c>
+      <c r="E332" s="2">
+        <v>23.72</v>
+      </c>
+      <c r="F332" s="3">
+        <v>0.577</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F332"/>
+  <dimension ref="A1:F343"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -8323,6 +8323,226 @@
         <v>0.577</v>
       </c>
     </row>
+    <row r="333" spans="1:6">
+      <c r="A333" t="s">
+        <v>9</v>
+      </c>
+      <c r="B333">
+        <v>1</v>
+      </c>
+      <c r="C333" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D333" s="2">
+        <v>19.41</v>
+      </c>
+      <c r="E333" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="F333" s="3">
+        <v>8.751</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" t="s">
+        <v>9</v>
+      </c>
+      <c r="B334">
+        <v>2</v>
+      </c>
+      <c r="C334" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D334" s="2">
+        <v>19.76</v>
+      </c>
+      <c r="E334" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="F334" s="3">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" t="s">
+        <v>9</v>
+      </c>
+      <c r="B335" t="s">
+        <v>10</v>
+      </c>
+      <c r="C335" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D335" s="2">
+        <v>19.58</v>
+      </c>
+      <c r="E335" s="2">
+        <v>8.7</v>
+      </c>
+      <c r="F335" s="3">
+        <v>4.029</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" t="s">
+        <v>9</v>
+      </c>
+      <c r="B336">
+        <v>3</v>
+      </c>
+      <c r="C336" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D336" s="2">
+        <v>19.95</v>
+      </c>
+      <c r="E336" s="2">
+        <v>16.36</v>
+      </c>
+      <c r="F336" s="3">
+        <v>7.316</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" t="s">
+        <v>9</v>
+      </c>
+      <c r="B337">
+        <v>4</v>
+      </c>
+      <c r="C337" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D337" s="2">
+        <v>20.78</v>
+      </c>
+      <c r="E337" s="2">
+        <v>5.15</v>
+      </c>
+      <c r="F337" s="3">
+        <v>6.251</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" t="s">
+        <v>9</v>
+      </c>
+      <c r="B338" t="s">
+        <v>11</v>
+      </c>
+      <c r="C338" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D338" s="2">
+        <v>20.99</v>
+      </c>
+      <c r="E338" s="2">
+        <v>0.76</v>
+      </c>
+      <c r="F338" s="3">
+        <v>3.395</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" t="s">
+        <v>12</v>
+      </c>
+      <c r="B339">
+        <v>1</v>
+      </c>
+      <c r="C339" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D339" s="2">
+        <v>29.06</v>
+      </c>
+      <c r="E339" s="2">
+        <v>0</v>
+      </c>
+      <c r="F339" s="3">
+        <v>0.888</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" t="s">
+        <v>12</v>
+      </c>
+      <c r="B340">
+        <v>2</v>
+      </c>
+      <c r="C340" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D340" s="2">
+        <v>29.11</v>
+      </c>
+      <c r="E340" s="2">
+        <v>9.59</v>
+      </c>
+      <c r="F340" s="3">
+        <v>0.472</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" t="s">
+        <v>12</v>
+      </c>
+      <c r="B341">
+        <v>3</v>
+      </c>
+      <c r="C341" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D341" s="2">
+        <v>29.07</v>
+      </c>
+      <c r="E341" s="2">
+        <v>1.02</v>
+      </c>
+      <c r="F341" s="3">
+        <v>0.508</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" t="s">
+        <v>12</v>
+      </c>
+      <c r="B342">
+        <v>4</v>
+      </c>
+      <c r="C342" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D342" s="2">
+        <v>29.08</v>
+      </c>
+      <c r="E342" s="2">
+        <v>3.31</v>
+      </c>
+      <c r="F342" s="3">
+        <v>0.612</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" t="s">
+        <v>12</v>
+      </c>
+      <c r="B343">
+        <v>5</v>
+      </c>
+      <c r="C343" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D343" s="2">
+        <v>29.09</v>
+      </c>
+      <c r="E343" s="2">
+        <v>21.29</v>
+      </c>
+      <c r="F343" s="3">
+        <v>0.554</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -697,7 +697,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -708,6 +708,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1677,7 +1680,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F343"/>
+  <dimension ref="A1:F355"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -8543,6 +8546,229 @@
         <v>0.554</v>
       </c>
     </row>
+    <row r="344" spans="1:6">
+      <c r="A344" t="s">
+        <v>9</v>
+      </c>
+      <c r="B344">
+        <v>1</v>
+      </c>
+      <c r="C344" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D344" s="2">
+        <v>19.01</v>
+      </c>
+      <c r="E344" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="F344" s="3">
+        <v>8.55</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" t="s">
+        <v>9</v>
+      </c>
+      <c r="B345">
+        <v>2</v>
+      </c>
+      <c r="C345" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D345" s="2">
+        <v>19.4</v>
+      </c>
+      <c r="E345" s="2">
+        <v>0.42</v>
+      </c>
+      <c r="F345" s="3">
+        <v>3.032</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" t="s">
+        <v>9</v>
+      </c>
+      <c r="B346" t="s">
+        <v>10</v>
+      </c>
+      <c r="C346" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D346" s="2">
+        <v>19.25</v>
+      </c>
+      <c r="E346" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="F346" s="3">
+        <v>3.882</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" t="s">
+        <v>9</v>
+      </c>
+      <c r="B347">
+        <v>3</v>
+      </c>
+      <c r="C347" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D347" s="2">
+        <v>19.74</v>
+      </c>
+      <c r="E347" s="2">
+        <v>15.67</v>
+      </c>
+      <c r="F347" s="3">
+        <v>7.639</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" t="s">
+        <v>9</v>
+      </c>
+      <c r="B348">
+        <v>4</v>
+      </c>
+      <c r="C348" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D348" s="2">
+        <v>20.64</v>
+      </c>
+      <c r="E348" s="2">
+        <v>5.09</v>
+      </c>
+      <c r="F348" s="3">
+        <v>6.081</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" t="s">
+        <v>9</v>
+      </c>
+      <c r="B349" t="s">
+        <v>11</v>
+      </c>
+      <c r="C349" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D349" s="2">
+        <v>20.74</v>
+      </c>
+      <c r="E349" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F349" s="3">
+        <v>1.331</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" t="s">
+        <v>12</v>
+      </c>
+      <c r="B350">
+        <v>1</v>
+      </c>
+      <c r="C350" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D350" s="2">
+        <v>28.77</v>
+      </c>
+      <c r="E350" s="2">
+        <v>0</v>
+      </c>
+      <c r="F350" s="3">
+        <v>0.907</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" t="s">
+        <v>12</v>
+      </c>
+      <c r="B351">
+        <v>2</v>
+      </c>
+      <c r="C351" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D351" s="2">
+        <v>28.76</v>
+      </c>
+      <c r="E351" s="2">
+        <v>12.85</v>
+      </c>
+      <c r="F351" s="3">
+        <v>0.492</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" t="s">
+        <v>12</v>
+      </c>
+      <c r="B352">
+        <v>3</v>
+      </c>
+      <c r="C352" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D352" s="2">
+        <v>28.69</v>
+      </c>
+      <c r="E352" s="2">
+        <v>1.16</v>
+      </c>
+      <c r="F352" s="3">
+        <v>0.536</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" t="s">
+        <v>12</v>
+      </c>
+      <c r="B353">
+        <v>4</v>
+      </c>
+      <c r="C353" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D353" s="2">
+        <v>28.73</v>
+      </c>
+      <c r="E353" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="F353" s="3">
+        <v>0.725</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" t="s">
+        <v>12</v>
+      </c>
+      <c r="B354">
+        <v>5</v>
+      </c>
+      <c r="C354" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D354" s="2">
+        <v>28.76</v>
+      </c>
+      <c r="E354" s="2">
+        <v>21.65</v>
+      </c>
+      <c r="F354" s="3">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="355" spans="5:5">
+      <c r="E355" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -697,7 +697,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -708,9 +708,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1680,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F355"/>
+  <dimension ref="A1:F365"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -8766,8 +8763,225 @@
         <v>0.485</v>
       </c>
     </row>
-    <row r="355" spans="5:5">
-      <c r="E355" s="4"/>
+    <row r="355" spans="1:6">
+      <c r="A355" t="s">
+        <v>9</v>
+      </c>
+      <c r="B355">
+        <v>1</v>
+      </c>
+      <c r="C355" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D355" s="2">
+        <v>22.34</v>
+      </c>
+      <c r="E355" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F355" s="3">
+        <v>7.962</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" t="s">
+        <v>9</v>
+      </c>
+      <c r="B356">
+        <v>2</v>
+      </c>
+      <c r="C356" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D356" s="2">
+        <v>22.41</v>
+      </c>
+      <c r="E356" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F356" s="3">
+        <v>2.885</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" t="s">
+        <v>9</v>
+      </c>
+      <c r="B357" t="s">
+        <v>10</v>
+      </c>
+      <c r="C357" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D357" s="2">
+        <v>22.46</v>
+      </c>
+      <c r="E357" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="F357" s="3">
+        <v>3.916</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358" t="s">
+        <v>9</v>
+      </c>
+      <c r="B358">
+        <v>3</v>
+      </c>
+      <c r="C358" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D358" s="2">
+        <v>22.43</v>
+      </c>
+      <c r="E358" s="2">
+        <v>18.2</v>
+      </c>
+      <c r="F358" s="3">
+        <v>8.242</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" t="s">
+        <v>9</v>
+      </c>
+      <c r="B359">
+        <v>4</v>
+      </c>
+      <c r="C359" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D359" s="2">
+        <v>22.39</v>
+      </c>
+      <c r="E359" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="F359" s="3">
+        <v>5.971</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" t="s">
+        <v>9</v>
+      </c>
+      <c r="B360" t="s">
+        <v>11</v>
+      </c>
+      <c r="C360" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D360" s="2">
+        <v>22.44</v>
+      </c>
+      <c r="E360" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F360" s="3">
+        <v>1.524</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" t="s">
+        <v>12</v>
+      </c>
+      <c r="B361">
+        <v>1</v>
+      </c>
+      <c r="C361" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D361" s="2">
+        <v>28.8</v>
+      </c>
+      <c r="E361" s="2">
+        <v>0</v>
+      </c>
+      <c r="F361" s="3">
+        <v>0.886</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" t="s">
+        <v>12</v>
+      </c>
+      <c r="B362">
+        <v>2</v>
+      </c>
+      <c r="C362" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D362" s="2">
+        <v>28.79</v>
+      </c>
+      <c r="E362" s="2">
+        <v>16.98</v>
+      </c>
+      <c r="F362" s="3">
+        <v>0.479</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" t="s">
+        <v>12</v>
+      </c>
+      <c r="B363">
+        <v>3</v>
+      </c>
+      <c r="C363" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D363" s="2">
+        <v>28.77</v>
+      </c>
+      <c r="E363" s="2">
+        <v>1.66</v>
+      </c>
+      <c r="F363" s="3">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" t="s">
+        <v>12</v>
+      </c>
+      <c r="B364">
+        <v>4</v>
+      </c>
+      <c r="C364" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D364" s="2">
+        <v>28.91</v>
+      </c>
+      <c r="E364" s="2">
+        <v>3.71</v>
+      </c>
+      <c r="F364" s="3">
+        <v>0.557</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" t="s">
+        <v>12</v>
+      </c>
+      <c r="B365">
+        <v>5</v>
+      </c>
+      <c r="C365" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D365" s="2">
+        <v>28.83</v>
+      </c>
+      <c r="E365" s="2">
+        <v>22.91</v>
+      </c>
+      <c r="F365" s="3">
+        <v>0.552</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F365"/>
+  <dimension ref="A1:F387"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -8983,6 +8983,446 @@
         <v>0.552</v>
       </c>
     </row>
+    <row r="366" spans="1:6">
+      <c r="A366" t="s">
+        <v>9</v>
+      </c>
+      <c r="B366">
+        <v>1</v>
+      </c>
+      <c r="C366" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D366" s="2">
+        <v>18.69</v>
+      </c>
+      <c r="E366" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="F366" s="3">
+        <v>9.57</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" t="s">
+        <v>9</v>
+      </c>
+      <c r="B367">
+        <v>2</v>
+      </c>
+      <c r="C367" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D367" s="2">
+        <v>19.15</v>
+      </c>
+      <c r="E367" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="F367" s="3">
+        <v>3.191</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" t="s">
+        <v>9</v>
+      </c>
+      <c r="B368" t="s">
+        <v>10</v>
+      </c>
+      <c r="C368" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D368" s="2">
+        <v>19.07</v>
+      </c>
+      <c r="E368" s="2">
+        <v>8.36</v>
+      </c>
+      <c r="F368" s="3">
+        <v>3.707</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" t="s">
+        <v>9</v>
+      </c>
+      <c r="B369">
+        <v>3</v>
+      </c>
+      <c r="C369" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D369" s="2">
+        <v>19.26</v>
+      </c>
+      <c r="E369" s="2">
+        <v>15.24</v>
+      </c>
+      <c r="F369" s="3">
+        <v>7.442</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" t="s">
+        <v>9</v>
+      </c>
+      <c r="B370">
+        <v>4</v>
+      </c>
+      <c r="C370" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D370" s="2">
+        <v>19.67</v>
+      </c>
+      <c r="E370" s="2">
+        <v>5.06</v>
+      </c>
+      <c r="F370" s="3">
+        <v>1.971</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" t="s">
+        <v>9</v>
+      </c>
+      <c r="B371" t="s">
+        <v>11</v>
+      </c>
+      <c r="C371" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D371" s="2">
+        <v>20.24</v>
+      </c>
+      <c r="E371" s="2">
+        <v>0.22</v>
+      </c>
+      <c r="F371" s="3">
+        <v>0.957</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" t="s">
+        <v>12</v>
+      </c>
+      <c r="B372">
+        <v>1</v>
+      </c>
+      <c r="C372" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D372" s="2">
+        <v>28.27</v>
+      </c>
+      <c r="E372" s="2">
+        <v>0</v>
+      </c>
+      <c r="F372" s="3">
+        <v>0.711</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" t="s">
+        <v>12</v>
+      </c>
+      <c r="B373">
+        <v>2</v>
+      </c>
+      <c r="C373" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D373" s="2">
+        <v>28.28</v>
+      </c>
+      <c r="E373" s="2">
+        <v>16.94</v>
+      </c>
+      <c r="F373" s="3">
+        <v>0.405</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" t="s">
+        <v>12</v>
+      </c>
+      <c r="B374">
+        <v>3</v>
+      </c>
+      <c r="C374" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D374" s="2">
+        <v>28.29</v>
+      </c>
+      <c r="E374" s="2">
+        <v>1.95</v>
+      </c>
+      <c r="F374" s="3">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" t="s">
+        <v>12</v>
+      </c>
+      <c r="B375">
+        <v>4</v>
+      </c>
+      <c r="C375" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D375" s="2">
+        <v>28.28</v>
+      </c>
+      <c r="E375" s="2">
+        <v>4.39</v>
+      </c>
+      <c r="F375" s="3">
+        <v>0.684</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" t="s">
+        <v>12</v>
+      </c>
+      <c r="B376">
+        <v>5</v>
+      </c>
+      <c r="C376" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D376" s="2">
+        <v>28.27</v>
+      </c>
+      <c r="E376" s="2">
+        <v>26.43</v>
+      </c>
+      <c r="F376" s="3">
+        <v>0.549</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" t="s">
+        <v>9</v>
+      </c>
+      <c r="B377">
+        <v>1</v>
+      </c>
+      <c r="C377" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D377" s="2">
+        <v>22.1</v>
+      </c>
+      <c r="E377" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="F377" s="3">
+        <v>10.362</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" t="s">
+        <v>9</v>
+      </c>
+      <c r="B378">
+        <v>2</v>
+      </c>
+      <c r="C378" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D378" s="2">
+        <v>22.05</v>
+      </c>
+      <c r="E378" s="2">
+        <v>0.67</v>
+      </c>
+      <c r="F378" s="3">
+        <v>1.071</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" t="s">
+        <v>9</v>
+      </c>
+      <c r="B379" t="s">
+        <v>10</v>
+      </c>
+      <c r="C379" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D379" s="2">
+        <v>21.74</v>
+      </c>
+      <c r="E379" s="2">
+        <v>9.23</v>
+      </c>
+      <c r="F379" s="3">
+        <v>3.882</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" t="s">
+        <v>9</v>
+      </c>
+      <c r="B380">
+        <v>3</v>
+      </c>
+      <c r="C380" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D380" s="2">
+        <v>22.04</v>
+      </c>
+      <c r="E380" s="2">
+        <v>18.29</v>
+      </c>
+      <c r="F380" s="3">
+        <v>7.377</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" t="s">
+        <v>9</v>
+      </c>
+      <c r="B381">
+        <v>4</v>
+      </c>
+      <c r="C381" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D381" s="2">
+        <v>22.21</v>
+      </c>
+      <c r="E381" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="F381" s="3">
+        <v>2.423</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" t="s">
+        <v>9</v>
+      </c>
+      <c r="B382" t="s">
+        <v>11</v>
+      </c>
+      <c r="C382" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D382" s="2">
+        <v>22.64</v>
+      </c>
+      <c r="E382" s="2">
+        <v>0</v>
+      </c>
+      <c r="F382" s="3">
+        <v>0.678</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" t="s">
+        <v>12</v>
+      </c>
+      <c r="B383">
+        <v>1</v>
+      </c>
+      <c r="C383" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D383" s="2">
+        <v>25.45</v>
+      </c>
+      <c r="E383" s="2">
+        <v>0</v>
+      </c>
+      <c r="F383" s="3">
+        <v>0.582</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" t="s">
+        <v>12</v>
+      </c>
+      <c r="B384">
+        <v>2</v>
+      </c>
+      <c r="C384" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D384" s="2">
+        <v>25.49</v>
+      </c>
+      <c r="E384" s="2">
+        <v>20.39</v>
+      </c>
+      <c r="F384" s="3">
+        <v>0.265</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" t="s">
+        <v>12</v>
+      </c>
+      <c r="B385">
+        <v>3</v>
+      </c>
+      <c r="C385" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D385" s="2">
+        <v>25.51</v>
+      </c>
+      <c r="E385" s="2">
+        <v>2.12</v>
+      </c>
+      <c r="F385" s="3">
+        <v>0.338</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6">
+      <c r="A386" t="s">
+        <v>12</v>
+      </c>
+      <c r="B386">
+        <v>4</v>
+      </c>
+      <c r="C386" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D386" s="2">
+        <v>25.51</v>
+      </c>
+      <c r="E386" s="2">
+        <v>4.74</v>
+      </c>
+      <c r="F386" s="3">
+        <v>0.443</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6">
+      <c r="A387" t="s">
+        <v>12</v>
+      </c>
+      <c r="B387">
+        <v>5</v>
+      </c>
+      <c r="C387" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D387" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="E387" s="2">
+        <v>30.19</v>
+      </c>
+      <c r="F387" s="3">
+        <v>0.488</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F387"/>
+  <dimension ref="A1:F398"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -9423,6 +9423,226 @@
         <v>0.488</v>
       </c>
     </row>
+    <row r="388" spans="1:6">
+      <c r="A388" t="s">
+        <v>9</v>
+      </c>
+      <c r="B388">
+        <v>1</v>
+      </c>
+      <c r="C388" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D388" s="2">
+        <v>22.96</v>
+      </c>
+      <c r="E388" s="2">
+        <v>0.31</v>
+      </c>
+      <c r="F388" s="3">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6">
+      <c r="A389" t="s">
+        <v>9</v>
+      </c>
+      <c r="B389">
+        <v>2</v>
+      </c>
+      <c r="C389" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D389" s="2">
+        <v>26.56</v>
+      </c>
+      <c r="E389" s="2">
+        <v>1.34</v>
+      </c>
+      <c r="F389" s="3">
+        <v>3.924</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6">
+      <c r="A390" t="s">
+        <v>9</v>
+      </c>
+      <c r="B390" t="s">
+        <v>10</v>
+      </c>
+      <c r="C390" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D390" s="2">
+        <v>25.72</v>
+      </c>
+      <c r="E390" s="2">
+        <v>6.79</v>
+      </c>
+      <c r="F390" s="3">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6">
+      <c r="A391" t="s">
+        <v>9</v>
+      </c>
+      <c r="B391">
+        <v>3</v>
+      </c>
+      <c r="C391" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D391" s="2">
+        <v>25.64</v>
+      </c>
+      <c r="E391" s="2">
+        <v>9.67</v>
+      </c>
+      <c r="F391" s="3">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6">
+      <c r="A392" t="s">
+        <v>9</v>
+      </c>
+      <c r="B392">
+        <v>4</v>
+      </c>
+      <c r="C392" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D392" s="2">
+        <v>26.69</v>
+      </c>
+      <c r="E392" s="2">
+        <v>4.55</v>
+      </c>
+      <c r="F392" s="3">
+        <v>5.992</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6">
+      <c r="A393" t="s">
+        <v>9</v>
+      </c>
+      <c r="B393" t="s">
+        <v>11</v>
+      </c>
+      <c r="C393" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D393" s="2">
+        <v>26.81</v>
+      </c>
+      <c r="E393" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F393" s="3">
+        <v>3.136</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6">
+      <c r="A394" t="s">
+        <v>12</v>
+      </c>
+      <c r="B394">
+        <v>1</v>
+      </c>
+      <c r="C394" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D394" s="2">
+        <v>33.93</v>
+      </c>
+      <c r="E394" s="2">
+        <v>0</v>
+      </c>
+      <c r="F394" s="3">
+        <v>1.812</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6">
+      <c r="A395" t="s">
+        <v>12</v>
+      </c>
+      <c r="B395">
+        <v>2</v>
+      </c>
+      <c r="C395" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D395" s="2">
+        <v>33.87</v>
+      </c>
+      <c r="E395" s="2">
+        <v>13.6</v>
+      </c>
+      <c r="F395" s="3">
+        <v>0.549</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6">
+      <c r="A396" t="s">
+        <v>12</v>
+      </c>
+      <c r="B396">
+        <v>3</v>
+      </c>
+      <c r="C396" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D396" s="2">
+        <v>33.85</v>
+      </c>
+      <c r="E396" s="2">
+        <v>1.97</v>
+      </c>
+      <c r="F396" s="3">
+        <v>0.608</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6">
+      <c r="A397" t="s">
+        <v>12</v>
+      </c>
+      <c r="B397">
+        <v>4</v>
+      </c>
+      <c r="C397" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D397" s="2">
+        <v>33.86</v>
+      </c>
+      <c r="E397" s="2">
+        <v>5.58</v>
+      </c>
+      <c r="F397" s="3">
+        <v>0.701</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6">
+      <c r="A398" t="s">
+        <v>12</v>
+      </c>
+      <c r="B398">
+        <v>5</v>
+      </c>
+      <c r="C398" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D398" s="2">
+        <v>33.77</v>
+      </c>
+      <c r="E398" s="2">
+        <v>29.22</v>
+      </c>
+      <c r="F398" s="3">
+        <v>0.556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F398"/>
+  <dimension ref="A1:F409"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -9643,6 +9643,226 @@
         <v>0.556</v>
       </c>
     </row>
+    <row r="399" spans="1:6">
+      <c r="A399" t="s">
+        <v>9</v>
+      </c>
+      <c r="B399">
+        <v>1</v>
+      </c>
+      <c r="C399" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D399" s="2">
+        <v>23.78</v>
+      </c>
+      <c r="E399" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="F399" s="3">
+        <v>14.491</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6">
+      <c r="A400" t="s">
+        <v>9</v>
+      </c>
+      <c r="B400">
+        <v>2</v>
+      </c>
+      <c r="C400" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D400" s="2">
+        <v>26.84</v>
+      </c>
+      <c r="E400" s="2">
+        <v>1.45</v>
+      </c>
+      <c r="F400" s="3">
+        <v>3.862</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6">
+      <c r="A401" t="s">
+        <v>9</v>
+      </c>
+      <c r="B401" t="s">
+        <v>10</v>
+      </c>
+      <c r="C401" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D401" s="2">
+        <v>26.79</v>
+      </c>
+      <c r="E401" s="2">
+        <v>5.86</v>
+      </c>
+      <c r="F401" s="3">
+        <v>3.955</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6">
+      <c r="A402" t="s">
+        <v>9</v>
+      </c>
+      <c r="B402">
+        <v>3</v>
+      </c>
+      <c r="C402" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D402" s="2">
+        <v>26.55</v>
+      </c>
+      <c r="E402" s="2">
+        <v>13.52</v>
+      </c>
+      <c r="F402" s="3">
+        <v>7.515</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6">
+      <c r="A403" t="s">
+        <v>9</v>
+      </c>
+      <c r="B403">
+        <v>4</v>
+      </c>
+      <c r="C403" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D403" s="2">
+        <v>26.91</v>
+      </c>
+      <c r="E403" s="2">
+        <v>6.27</v>
+      </c>
+      <c r="F403" s="3">
+        <v>5.356</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6">
+      <c r="A404" t="s">
+        <v>9</v>
+      </c>
+      <c r="B404" t="s">
+        <v>11</v>
+      </c>
+      <c r="C404" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D404" s="2">
+        <v>25.42</v>
+      </c>
+      <c r="E404" s="2">
+        <v>0.14</v>
+      </c>
+      <c r="F404" s="3">
+        <v>3.676</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6">
+      <c r="A405" t="s">
+        <v>12</v>
+      </c>
+      <c r="B405">
+        <v>1</v>
+      </c>
+      <c r="C405" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D405" s="2">
+        <v>33.81</v>
+      </c>
+      <c r="E405" s="2">
+        <v>0</v>
+      </c>
+      <c r="F405" s="3">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6">
+      <c r="A406" t="s">
+        <v>12</v>
+      </c>
+      <c r="B406">
+        <v>2</v>
+      </c>
+      <c r="C406" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D406" s="2">
+        <v>33.67</v>
+      </c>
+      <c r="E406" s="2">
+        <v>12.57</v>
+      </c>
+      <c r="F406" s="3">
+        <v>0.478</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6">
+      <c r="A407" t="s">
+        <v>12</v>
+      </c>
+      <c r="B407">
+        <v>3</v>
+      </c>
+      <c r="C407" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D407" s="2">
+        <v>33.85</v>
+      </c>
+      <c r="E407" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="F407" s="3">
+        <v>0.591</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6">
+      <c r="A408" t="s">
+        <v>12</v>
+      </c>
+      <c r="B408">
+        <v>4</v>
+      </c>
+      <c r="C408" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D408" s="2">
+        <v>33.79</v>
+      </c>
+      <c r="E408" s="2">
+        <v>7.91</v>
+      </c>
+      <c r="F408" s="3">
+        <v>0.891</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6">
+      <c r="A409" t="s">
+        <v>12</v>
+      </c>
+      <c r="B409">
+        <v>5</v>
+      </c>
+      <c r="C409" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D409" s="2">
+        <v>33.74</v>
+      </c>
+      <c r="E409" s="2">
+        <v>31.26</v>
+      </c>
+      <c r="F409" s="3">
+        <v>0.572</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F409"/>
+  <dimension ref="A1:F431"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -9863,6 +9863,446 @@
         <v>0.572</v>
       </c>
     </row>
+    <row r="410" spans="1:6">
+      <c r="A410" t="s">
+        <v>9</v>
+      </c>
+      <c r="B410">
+        <v>1</v>
+      </c>
+      <c r="C410" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D410" s="2">
+        <v>29.78</v>
+      </c>
+      <c r="E410" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="F410" s="3">
+        <v>5.514</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6">
+      <c r="A411" t="s">
+        <v>9</v>
+      </c>
+      <c r="B411">
+        <v>2</v>
+      </c>
+      <c r="C411" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D411" s="2">
+        <v>29.74</v>
+      </c>
+      <c r="E411" s="2">
+        <v>2.36</v>
+      </c>
+      <c r="F411" s="3">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6">
+      <c r="A412" t="s">
+        <v>9</v>
+      </c>
+      <c r="B412" t="s">
+        <v>10</v>
+      </c>
+      <c r="C412" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D412" s="2">
+        <v>29.82</v>
+      </c>
+      <c r="E412" s="2">
+        <v>5.86</v>
+      </c>
+      <c r="F412" s="3">
+        <v>3.955</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6">
+      <c r="A413" t="s">
+        <v>9</v>
+      </c>
+      <c r="B413">
+        <v>3</v>
+      </c>
+      <c r="C413" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D413" s="2">
+        <v>29.85</v>
+      </c>
+      <c r="E413" s="2">
+        <v>10.79</v>
+      </c>
+      <c r="F413" s="3">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6">
+      <c r="A414" t="s">
+        <v>9</v>
+      </c>
+      <c r="B414">
+        <v>4</v>
+      </c>
+      <c r="C414" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D414" s="2">
+        <v>29.91</v>
+      </c>
+      <c r="E414" s="2">
+        <v>1.51</v>
+      </c>
+      <c r="F414" s="3">
+        <v>5.356</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6">
+      <c r="A415" t="s">
+        <v>9</v>
+      </c>
+      <c r="B415" t="s">
+        <v>11</v>
+      </c>
+      <c r="C415" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D415" s="2">
+        <v>29.72</v>
+      </c>
+      <c r="E415" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F415" s="3">
+        <v>0.586</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6">
+      <c r="A416" t="s">
+        <v>12</v>
+      </c>
+      <c r="B416">
+        <v>1</v>
+      </c>
+      <c r="C416" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D416" s="2">
+        <v>33.84</v>
+      </c>
+      <c r="E416" s="2">
+        <v>0</v>
+      </c>
+      <c r="F416" s="3">
+        <v>3.116</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6">
+      <c r="A417" t="s">
+        <v>12</v>
+      </c>
+      <c r="B417">
+        <v>2</v>
+      </c>
+      <c r="C417" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D417" s="2">
+        <v>33.85</v>
+      </c>
+      <c r="E417" s="2">
+        <v>2.09</v>
+      </c>
+      <c r="F417" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6">
+      <c r="A418" t="s">
+        <v>12</v>
+      </c>
+      <c r="B418">
+        <v>3</v>
+      </c>
+      <c r="C418" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D418" s="2">
+        <v>33.8</v>
+      </c>
+      <c r="E418" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="F418" s="3">
+        <v>0.512</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6">
+      <c r="A419" t="s">
+        <v>12</v>
+      </c>
+      <c r="B419">
+        <v>4</v>
+      </c>
+      <c r="C419" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D419" s="2">
+        <v>34</v>
+      </c>
+      <c r="E419" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="F419" s="3">
+        <v>2.214</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6">
+      <c r="A420" t="s">
+        <v>12</v>
+      </c>
+      <c r="B420">
+        <v>5</v>
+      </c>
+      <c r="C420" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D420" s="2">
+        <v>33.81</v>
+      </c>
+      <c r="E420" s="2">
+        <v>6.56</v>
+      </c>
+      <c r="F420" s="3">
+        <v>0.279</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6">
+      <c r="A421" t="s">
+        <v>9</v>
+      </c>
+      <c r="B421">
+        <v>1</v>
+      </c>
+      <c r="C421" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D421" s="2">
+        <v>30.52</v>
+      </c>
+      <c r="E421" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="F421" s="3">
+        <v>4.769</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6">
+      <c r="A422" t="s">
+        <v>9</v>
+      </c>
+      <c r="B422">
+        <v>2</v>
+      </c>
+      <c r="C422" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D422" s="2">
+        <v>30.7</v>
+      </c>
+      <c r="E422" s="2">
+        <v>1.13</v>
+      </c>
+      <c r="F422" s="3">
+        <v>0.463</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6">
+      <c r="A423" t="s">
+        <v>9</v>
+      </c>
+      <c r="B423" t="s">
+        <v>10</v>
+      </c>
+      <c r="C423" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D423" s="2">
+        <v>29.75</v>
+      </c>
+      <c r="E423" s="2">
+        <v>2.55</v>
+      </c>
+      <c r="F423" s="3">
+        <v>3.712</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6">
+      <c r="A424" t="s">
+        <v>9</v>
+      </c>
+      <c r="B424">
+        <v>3</v>
+      </c>
+      <c r="C424" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D424" s="2">
+        <v>30.28</v>
+      </c>
+      <c r="E424" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="F424" s="3">
+        <v>2.032</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6">
+      <c r="A425" t="s">
+        <v>9</v>
+      </c>
+      <c r="B425">
+        <v>4</v>
+      </c>
+      <c r="C425" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D425" s="2">
+        <v>31.2</v>
+      </c>
+      <c r="E425" s="2">
+        <v>1.67</v>
+      </c>
+      <c r="F425" s="3">
+        <v>4.132</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6">
+      <c r="A426" t="s">
+        <v>9</v>
+      </c>
+      <c r="B426" t="s">
+        <v>11</v>
+      </c>
+      <c r="C426" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D426" s="2">
+        <v>25.64</v>
+      </c>
+      <c r="E426" s="2">
+        <v>0</v>
+      </c>
+      <c r="F426" s="3">
+        <v>0.931</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6">
+      <c r="A427" t="s">
+        <v>12</v>
+      </c>
+      <c r="B427">
+        <v>1</v>
+      </c>
+      <c r="C427" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D427" s="2">
+        <v>35.78</v>
+      </c>
+      <c r="E427" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="F427" s="3">
+        <v>0.634</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6">
+      <c r="A428" t="s">
+        <v>12</v>
+      </c>
+      <c r="B428">
+        <v>2</v>
+      </c>
+      <c r="C428" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D428" s="2">
+        <v>35.81</v>
+      </c>
+      <c r="E428" s="2">
+        <v>7.66</v>
+      </c>
+      <c r="F428" s="3">
+        <v>1.765</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6">
+      <c r="A429" t="s">
+        <v>12</v>
+      </c>
+      <c r="B429">
+        <v>3</v>
+      </c>
+      <c r="C429" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D429" s="2">
+        <v>35.85</v>
+      </c>
+      <c r="E429" s="2">
+        <v>2.25</v>
+      </c>
+      <c r="F429" s="3">
+        <v>0.534</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6">
+      <c r="A430" t="s">
+        <v>12</v>
+      </c>
+      <c r="B430">
+        <v>4</v>
+      </c>
+      <c r="C430" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D430" s="2">
+        <v>35.92</v>
+      </c>
+      <c r="E430" s="2">
+        <v>2.88</v>
+      </c>
+      <c r="F430" s="3">
+        <v>0.538</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6">
+      <c r="A431" t="s">
+        <v>12</v>
+      </c>
+      <c r="B431">
+        <v>5</v>
+      </c>
+      <c r="C431" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D431" s="2">
+        <v>35.81</v>
+      </c>
+      <c r="E431" s="2">
+        <v>19.62</v>
+      </c>
+      <c r="F431" s="3">
+        <v>1.994</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="13545" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F431"/>
+  <dimension ref="A1:F442"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -10303,6 +10303,226 @@
         <v>1.994</v>
       </c>
     </row>
+    <row r="432" spans="1:6">
+      <c r="A432" t="s">
+        <v>9</v>
+      </c>
+      <c r="B432">
+        <v>1</v>
+      </c>
+      <c r="C432" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D432" s="2">
+        <v>29.69</v>
+      </c>
+      <c r="E432" s="2">
+        <v>0.57</v>
+      </c>
+      <c r="F432" s="3">
+        <v>5.145</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6">
+      <c r="A433" t="s">
+        <v>9</v>
+      </c>
+      <c r="B433">
+        <v>2</v>
+      </c>
+      <c r="C433" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D433" s="2">
+        <v>30.14</v>
+      </c>
+      <c r="E433" s="2">
+        <v>1.06</v>
+      </c>
+      <c r="F433" s="3">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6">
+      <c r="A434" t="s">
+        <v>9</v>
+      </c>
+      <c r="B434" t="s">
+        <v>10</v>
+      </c>
+      <c r="C434" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D434" s="2">
+        <v>29.88</v>
+      </c>
+      <c r="E434" s="2">
+        <v>3.62</v>
+      </c>
+      <c r="F434" s="3">
+        <v>3.298</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6">
+      <c r="A435" t="s">
+        <v>9</v>
+      </c>
+      <c r="B435">
+        <v>3</v>
+      </c>
+      <c r="C435" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D435" s="2">
+        <v>29.98</v>
+      </c>
+      <c r="E435" s="2">
+        <v>5.96</v>
+      </c>
+      <c r="F435" s="3">
+        <v>1.987</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6">
+      <c r="A436" t="s">
+        <v>9</v>
+      </c>
+      <c r="B436">
+        <v>4</v>
+      </c>
+      <c r="C436" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D436" s="2">
+        <v>30.1</v>
+      </c>
+      <c r="E436" s="2">
+        <v>8.11</v>
+      </c>
+      <c r="F436" s="3">
+        <v>2.982</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6">
+      <c r="A437" t="s">
+        <v>9</v>
+      </c>
+      <c r="B437" t="s">
+        <v>11</v>
+      </c>
+      <c r="C437" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D437" s="2">
+        <v>29.61</v>
+      </c>
+      <c r="E437" s="2">
+        <v>0.47</v>
+      </c>
+      <c r="F437" s="3">
+        <v>0.878</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6">
+      <c r="A438" t="s">
+        <v>12</v>
+      </c>
+      <c r="B438">
+        <v>1</v>
+      </c>
+      <c r="C438" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D438" s="2">
+        <v>35.88</v>
+      </c>
+      <c r="E438" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="F438" s="3">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6">
+      <c r="A439" t="s">
+        <v>12</v>
+      </c>
+      <c r="B439">
+        <v>2</v>
+      </c>
+      <c r="C439" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D439" s="2">
+        <v>35.91</v>
+      </c>
+      <c r="E439" s="2">
+        <v>8.23</v>
+      </c>
+      <c r="F439" s="3">
+        <v>1.846</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6">
+      <c r="A440" t="s">
+        <v>12</v>
+      </c>
+      <c r="B440">
+        <v>3</v>
+      </c>
+      <c r="C440" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D440" s="2">
+        <v>35.88</v>
+      </c>
+      <c r="E440" s="2">
+        <v>3.54</v>
+      </c>
+      <c r="F440" s="3">
+        <v>0.618</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6">
+      <c r="A441" t="s">
+        <v>12</v>
+      </c>
+      <c r="B441">
+        <v>4</v>
+      </c>
+      <c r="C441" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D441" s="2">
+        <v>35.92</v>
+      </c>
+      <c r="E441" s="2">
+        <v>1.96</v>
+      </c>
+      <c r="F441" s="3">
+        <v>0.495</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6">
+      <c r="A442" t="s">
+        <v>12</v>
+      </c>
+      <c r="B442">
+        <v>5</v>
+      </c>
+      <c r="C442" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D442" s="2">
+        <v>35.87</v>
+      </c>
+      <c r="E442" s="2">
+        <v>17.86</v>
+      </c>
+      <c r="F442" s="3">
+        <v>2.621</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="13545" windowHeight="11730" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F442"/>
+  <dimension ref="A1:F464"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -10523,6 +10523,446 @@
         <v>2.621</v>
       </c>
     </row>
+    <row r="443" spans="1:6">
+      <c r="A443" t="s">
+        <v>9</v>
+      </c>
+      <c r="B443">
+        <v>1</v>
+      </c>
+      <c r="C443" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D443" s="2">
+        <v>30.33</v>
+      </c>
+      <c r="E443" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="F443" s="3">
+        <v>4.951</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6">
+      <c r="A444" t="s">
+        <v>9</v>
+      </c>
+      <c r="B444">
+        <v>2</v>
+      </c>
+      <c r="C444" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D444" s="2">
+        <v>31.16</v>
+      </c>
+      <c r="E444" s="2">
+        <v>1.45</v>
+      </c>
+      <c r="F444" s="3">
+        <v>0.137</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6">
+      <c r="A445" t="s">
+        <v>9</v>
+      </c>
+      <c r="B445" t="s">
+        <v>10</v>
+      </c>
+      <c r="C445" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D445" s="2">
+        <v>30.38</v>
+      </c>
+      <c r="E445" s="2">
+        <v>2.43</v>
+      </c>
+      <c r="F445" s="3">
+        <v>4.834</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6">
+      <c r="A446" t="s">
+        <v>9</v>
+      </c>
+      <c r="B446">
+        <v>3</v>
+      </c>
+      <c r="C446" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D446" s="2">
+        <v>31.12</v>
+      </c>
+      <c r="E446" s="2">
+        <v>2.35</v>
+      </c>
+      <c r="F446" s="3">
+        <v>5.536</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6">
+      <c r="A447" t="s">
+        <v>9</v>
+      </c>
+      <c r="B447">
+        <v>4</v>
+      </c>
+      <c r="C447" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D447" s="2">
+        <v>31.67</v>
+      </c>
+      <c r="E447" s="2">
+        <v>1.92</v>
+      </c>
+      <c r="F447" s="3">
+        <v>4.148</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6">
+      <c r="A448" t="s">
+        <v>9</v>
+      </c>
+      <c r="B448" t="s">
+        <v>11</v>
+      </c>
+      <c r="C448" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D448" s="2">
+        <v>31.62</v>
+      </c>
+      <c r="E448" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="F448" s="3">
+        <v>3.121</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6">
+      <c r="A449" t="s">
+        <v>12</v>
+      </c>
+      <c r="B449">
+        <v>1</v>
+      </c>
+      <c r="C449" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D449" s="2">
+        <v>35.37</v>
+      </c>
+      <c r="E449" s="2">
+        <v>0</v>
+      </c>
+      <c r="F449" s="3">
+        <v>1.064</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6">
+      <c r="A450" t="s">
+        <v>12</v>
+      </c>
+      <c r="B450">
+        <v>2</v>
+      </c>
+      <c r="C450" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D450" s="2">
+        <v>34.91</v>
+      </c>
+      <c r="E450" s="2">
+        <v>2.98</v>
+      </c>
+      <c r="F450" s="3">
+        <v>0.685</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6">
+      <c r="A451" t="s">
+        <v>12</v>
+      </c>
+      <c r="B451">
+        <v>3</v>
+      </c>
+      <c r="C451" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D451" s="2">
+        <v>35.06</v>
+      </c>
+      <c r="E451" s="2">
+        <v>1.87</v>
+      </c>
+      <c r="F451" s="3">
+        <v>0.522</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6">
+      <c r="A452" t="s">
+        <v>12</v>
+      </c>
+      <c r="B452">
+        <v>4</v>
+      </c>
+      <c r="C452" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D452" s="2">
+        <v>35.19</v>
+      </c>
+      <c r="E452" s="2">
+        <v>0.71</v>
+      </c>
+      <c r="F452" s="3">
+        <v>1.321</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6">
+      <c r="A453" t="s">
+        <v>12</v>
+      </c>
+      <c r="B453">
+        <v>5</v>
+      </c>
+      <c r="C453" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D453" s="2">
+        <v>34.96</v>
+      </c>
+      <c r="E453" s="2">
+        <v>8.03</v>
+      </c>
+      <c r="F453" s="3">
+        <v>0.666</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6">
+      <c r="A454" t="s">
+        <v>9</v>
+      </c>
+      <c r="B454">
+        <v>1</v>
+      </c>
+      <c r="C454" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D454" s="2">
+        <v>29.96</v>
+      </c>
+      <c r="E454" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F454" s="3">
+        <v>6.725</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6">
+      <c r="A455" t="s">
+        <v>9</v>
+      </c>
+      <c r="B455">
+        <v>2</v>
+      </c>
+      <c r="C455" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D455" s="2">
+        <v>30.56</v>
+      </c>
+      <c r="E455" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="F455" s="3">
+        <v>2.521</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6">
+      <c r="A456" t="s">
+        <v>9</v>
+      </c>
+      <c r="B456" t="s">
+        <v>10</v>
+      </c>
+      <c r="C456" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D456" s="2">
+        <v>29.72</v>
+      </c>
+      <c r="E456" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="F456" s="3">
+        <v>3.186</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6">
+      <c r="A457" t="s">
+        <v>9</v>
+      </c>
+      <c r="B457">
+        <v>3</v>
+      </c>
+      <c r="C457" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D457" s="2">
+        <v>29.64</v>
+      </c>
+      <c r="E457" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="F457" s="3">
+        <v>7.186</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6">
+      <c r="A458" t="s">
+        <v>9</v>
+      </c>
+      <c r="B458">
+        <v>4</v>
+      </c>
+      <c r="C458" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D458" s="2">
+        <v>29.69</v>
+      </c>
+      <c r="E458" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="F458" s="3">
+        <v>4.683</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6">
+      <c r="A459" t="s">
+        <v>9</v>
+      </c>
+      <c r="B459" t="s">
+        <v>11</v>
+      </c>
+      <c r="C459" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D459" s="2">
+        <v>29.81</v>
+      </c>
+      <c r="E459" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F459" s="3">
+        <v>2.936</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6">
+      <c r="A460" t="s">
+        <v>12</v>
+      </c>
+      <c r="B460">
+        <v>1</v>
+      </c>
+      <c r="C460" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D460" s="2">
+        <v>35.93</v>
+      </c>
+      <c r="E460" s="2">
+        <v>0</v>
+      </c>
+      <c r="F460" s="3">
+        <v>1.442</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6">
+      <c r="A461" t="s">
+        <v>12</v>
+      </c>
+      <c r="B461">
+        <v>2</v>
+      </c>
+      <c r="C461" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D461" s="2">
+        <v>35.87</v>
+      </c>
+      <c r="E461" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="F461" s="3">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6">
+      <c r="A462" t="s">
+        <v>12</v>
+      </c>
+      <c r="B462">
+        <v>3</v>
+      </c>
+      <c r="C462" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D462" s="2">
+        <v>35.85</v>
+      </c>
+      <c r="E462" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="F462" s="3">
+        <v>0.497</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6">
+      <c r="A463" t="s">
+        <v>12</v>
+      </c>
+      <c r="B463">
+        <v>4</v>
+      </c>
+      <c r="C463" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D463" s="2">
+        <v>35.86</v>
+      </c>
+      <c r="E463" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F463" s="3">
+        <v>0.864</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6">
+      <c r="A464" t="s">
+        <v>12</v>
+      </c>
+      <c r="B464">
+        <v>5</v>
+      </c>
+      <c r="C464" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D464" s="2">
+        <v>35.77</v>
+      </c>
+      <c r="E464" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="F464" s="3">
+        <v>0.518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="11730" activeTab="1"/>
+    <workbookView windowWidth="13545" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F464"/>
+  <dimension ref="A1:F475"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -10963,6 +10963,226 @@
         <v>0.518</v>
       </c>
     </row>
+    <row r="465" spans="1:6">
+      <c r="A465" t="s">
+        <v>9</v>
+      </c>
+      <c r="B465">
+        <v>1</v>
+      </c>
+      <c r="C465" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D465" s="2">
+        <v>31.26</v>
+      </c>
+      <c r="E465" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="F465" s="3">
+        <v>4.514</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6">
+      <c r="A466" t="s">
+        <v>9</v>
+      </c>
+      <c r="B466">
+        <v>2</v>
+      </c>
+      <c r="C466" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D466" s="2">
+        <v>31.44</v>
+      </c>
+      <c r="E466" s="2">
+        <v>2.14</v>
+      </c>
+      <c r="F466" s="3">
+        <v>0.562</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6">
+      <c r="A467" t="s">
+        <v>9</v>
+      </c>
+      <c r="B467" t="s">
+        <v>10</v>
+      </c>
+      <c r="C467" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D467" s="2">
+        <v>31.46</v>
+      </c>
+      <c r="E467" s="2">
+        <v>2.98</v>
+      </c>
+      <c r="F467" s="3">
+        <v>3.259</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6">
+      <c r="A468" t="s">
+        <v>9</v>
+      </c>
+      <c r="B468">
+        <v>3</v>
+      </c>
+      <c r="C468" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D468" s="2">
+        <v>31.36</v>
+      </c>
+      <c r="E468" s="2">
+        <v>7.21</v>
+      </c>
+      <c r="F468" s="3">
+        <v>1.872</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6">
+      <c r="A469" t="s">
+        <v>9</v>
+      </c>
+      <c r="B469">
+        <v>4</v>
+      </c>
+      <c r="C469" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D469" s="2">
+        <v>31.42</v>
+      </c>
+      <c r="E469" s="2">
+        <v>2.33</v>
+      </c>
+      <c r="F469" s="3">
+        <v>3.891</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6">
+      <c r="A470" t="s">
+        <v>9</v>
+      </c>
+      <c r="B470" t="s">
+        <v>11</v>
+      </c>
+      <c r="C470" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D470" s="2">
+        <v>31.39</v>
+      </c>
+      <c r="E470" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="F470" s="3">
+        <v>0.764</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6">
+      <c r="A471" t="s">
+        <v>12</v>
+      </c>
+      <c r="B471">
+        <v>1</v>
+      </c>
+      <c r="C471" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D471" s="2">
+        <v>35.32</v>
+      </c>
+      <c r="E471" s="2">
+        <v>0</v>
+      </c>
+      <c r="F471" s="3">
+        <v>1.359</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6">
+      <c r="A472" t="s">
+        <v>12</v>
+      </c>
+      <c r="B472">
+        <v>2</v>
+      </c>
+      <c r="C472" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D472" s="2">
+        <v>34.25</v>
+      </c>
+      <c r="E472" s="2">
+        <v>3.04</v>
+      </c>
+      <c r="F472" s="3">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6">
+      <c r="A473" t="s">
+        <v>12</v>
+      </c>
+      <c r="B473">
+        <v>3</v>
+      </c>
+      <c r="C473" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D473" s="2">
+        <v>35.41</v>
+      </c>
+      <c r="E473" s="2">
+        <v>1.36</v>
+      </c>
+      <c r="F473" s="3">
+        <v>0.592</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6">
+      <c r="A474" t="s">
+        <v>12</v>
+      </c>
+      <c r="B474">
+        <v>4</v>
+      </c>
+      <c r="C474" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D474" s="2">
+        <v>35.43</v>
+      </c>
+      <c r="E474" s="2">
+        <v>0.83</v>
+      </c>
+      <c r="F474" s="3">
+        <v>1.283</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6">
+      <c r="A475" t="s">
+        <v>12</v>
+      </c>
+      <c r="B475">
+        <v>5</v>
+      </c>
+      <c r="C475" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D475" s="2">
+        <v>34.98</v>
+      </c>
+      <c r="E475" s="2">
+        <v>6.85</v>
+      </c>
+      <c r="F475" s="3">
+        <v>0.704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F475"/>
+  <dimension ref="A1:F486"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -11183,6 +11183,226 @@
         <v>0.704</v>
       </c>
     </row>
+    <row r="476" spans="1:6">
+      <c r="A476" t="s">
+        <v>9</v>
+      </c>
+      <c r="B476">
+        <v>1</v>
+      </c>
+      <c r="C476" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D476" s="2">
+        <v>31.04</v>
+      </c>
+      <c r="E476" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="F476" s="3">
+        <v>4.248</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6">
+      <c r="A477" t="s">
+        <v>9</v>
+      </c>
+      <c r="B477">
+        <v>2</v>
+      </c>
+      <c r="C477" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D477" s="2">
+        <v>31.09</v>
+      </c>
+      <c r="E477" s="2">
+        <v>2.46</v>
+      </c>
+      <c r="F477" s="3">
+        <v>0.471</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6">
+      <c r="A478" t="s">
+        <v>9</v>
+      </c>
+      <c r="B478" t="s">
+        <v>10</v>
+      </c>
+      <c r="C478" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D478" s="2">
+        <v>30.85</v>
+      </c>
+      <c r="E478" s="2">
+        <v>2.55</v>
+      </c>
+      <c r="F478" s="3">
+        <v>2.975</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6">
+      <c r="A479" t="s">
+        <v>9</v>
+      </c>
+      <c r="B479">
+        <v>3</v>
+      </c>
+      <c r="C479" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D479" s="2">
+        <v>31.05</v>
+      </c>
+      <c r="E479" s="2">
+        <v>6.41</v>
+      </c>
+      <c r="F479" s="3">
+        <v>0.764</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6">
+      <c r="A480" t="s">
+        <v>9</v>
+      </c>
+      <c r="B480">
+        <v>4</v>
+      </c>
+      <c r="C480" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D480" s="2">
+        <v>31.08</v>
+      </c>
+      <c r="E480" s="2">
+        <v>2.02</v>
+      </c>
+      <c r="F480" s="3">
+        <v>3.247</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6">
+      <c r="A481" t="s">
+        <v>9</v>
+      </c>
+      <c r="B481" t="s">
+        <v>11</v>
+      </c>
+      <c r="C481" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D481" s="2">
+        <v>30.94</v>
+      </c>
+      <c r="E481" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="F481" s="3">
+        <v>0.684</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6">
+      <c r="A482" t="s">
+        <v>12</v>
+      </c>
+      <c r="B482">
+        <v>1</v>
+      </c>
+      <c r="C482" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D482" s="2">
+        <v>34.71</v>
+      </c>
+      <c r="E482" s="2">
+        <v>0</v>
+      </c>
+      <c r="F482" s="3">
+        <v>1.261</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6">
+      <c r="A483" t="s">
+        <v>12</v>
+      </c>
+      <c r="B483">
+        <v>2</v>
+      </c>
+      <c r="C483" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D483" s="2">
+        <v>34.62</v>
+      </c>
+      <c r="E483" s="2">
+        <v>3.27</v>
+      </c>
+      <c r="F483" s="3">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6">
+      <c r="A484" t="s">
+        <v>12</v>
+      </c>
+      <c r="B484">
+        <v>3</v>
+      </c>
+      <c r="C484" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D484" s="2">
+        <v>34.7</v>
+      </c>
+      <c r="E484" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="F484" s="3">
+        <v>0.648</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6">
+      <c r="A485" t="s">
+        <v>12</v>
+      </c>
+      <c r="B485">
+        <v>4</v>
+      </c>
+      <c r="C485" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D485" s="2">
+        <v>34.52</v>
+      </c>
+      <c r="E485" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="F485" s="3">
+        <v>1.597</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6">
+      <c r="A486" t="s">
+        <v>12</v>
+      </c>
+      <c r="B486">
+        <v>5</v>
+      </c>
+      <c r="C486" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D486" s="2">
+        <v>34.75</v>
+      </c>
+      <c r="E486" s="2">
+        <v>4.91</v>
+      </c>
+      <c r="F486" s="3">
+        <v>0.517</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F486"/>
+  <dimension ref="A1:F519"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -11403,6 +11403,666 @@
         <v>0.517</v>
       </c>
     </row>
+    <row r="487" spans="1:6">
+      <c r="A487" t="s">
+        <v>9</v>
+      </c>
+      <c r="B487">
+        <v>1</v>
+      </c>
+      <c r="C487" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D487" s="2">
+        <v>30.33</v>
+      </c>
+      <c r="E487" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="F487" s="3">
+        <v>4.756</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6">
+      <c r="A488" t="s">
+        <v>9</v>
+      </c>
+      <c r="B488">
+        <v>2</v>
+      </c>
+      <c r="C488" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D488" s="2">
+        <v>30.16</v>
+      </c>
+      <c r="E488" s="2">
+        <v>1.86</v>
+      </c>
+      <c r="F488" s="3">
+        <v>0.347</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6">
+      <c r="A489" t="s">
+        <v>9</v>
+      </c>
+      <c r="B489" t="s">
+        <v>10</v>
+      </c>
+      <c r="C489" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D489" s="2">
+        <v>30.38</v>
+      </c>
+      <c r="E489" s="2">
+        <v>3.48</v>
+      </c>
+      <c r="F489" s="3">
+        <v>3.751</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6">
+      <c r="A490" t="s">
+        <v>9</v>
+      </c>
+      <c r="B490">
+        <v>3</v>
+      </c>
+      <c r="C490" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D490" s="2">
+        <v>29.82</v>
+      </c>
+      <c r="E490" s="2">
+        <v>4.27</v>
+      </c>
+      <c r="F490" s="3">
+        <v>4.673</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6">
+      <c r="A491" t="s">
+        <v>9</v>
+      </c>
+      <c r="B491">
+        <v>4</v>
+      </c>
+      <c r="C491" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D491" s="2">
+        <v>29.67</v>
+      </c>
+      <c r="E491" s="2">
+        <v>2.06</v>
+      </c>
+      <c r="F491" s="3">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6">
+      <c r="A492" t="s">
+        <v>9</v>
+      </c>
+      <c r="B492" t="s">
+        <v>11</v>
+      </c>
+      <c r="C492" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D492" s="2">
+        <v>29.62</v>
+      </c>
+      <c r="E492" s="2">
+        <v>0</v>
+      </c>
+      <c r="F492" s="3">
+        <v>2.714</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6">
+      <c r="A493" t="s">
+        <v>12</v>
+      </c>
+      <c r="B493">
+        <v>1</v>
+      </c>
+      <c r="C493" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D493" s="2">
+        <v>31.43</v>
+      </c>
+      <c r="E493" s="2">
+        <v>0</v>
+      </c>
+      <c r="F493" s="3">
+        <v>1.282</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6">
+      <c r="A494" t="s">
+        <v>12</v>
+      </c>
+      <c r="B494">
+        <v>2</v>
+      </c>
+      <c r="C494" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D494" s="2">
+        <v>30.97</v>
+      </c>
+      <c r="E494" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="F494" s="3">
+        <v>0.546</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6">
+      <c r="A495" t="s">
+        <v>12</v>
+      </c>
+      <c r="B495">
+        <v>3</v>
+      </c>
+      <c r="C495" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D495" s="2">
+        <v>31.06</v>
+      </c>
+      <c r="E495" s="2">
+        <v>0.69</v>
+      </c>
+      <c r="F495" s="3">
+        <v>0.681</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6">
+      <c r="A496" t="s">
+        <v>12</v>
+      </c>
+      <c r="B496">
+        <v>4</v>
+      </c>
+      <c r="C496" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D496" s="2">
+        <v>31.14</v>
+      </c>
+      <c r="E496" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F496" s="3">
+        <v>1.451</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6">
+      <c r="A497" t="s">
+        <v>12</v>
+      </c>
+      <c r="B497">
+        <v>5</v>
+      </c>
+      <c r="C497" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D497" s="2">
+        <v>30.93</v>
+      </c>
+      <c r="E497" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="F497" s="3">
+        <v>0.549</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6">
+      <c r="A498" t="s">
+        <v>9</v>
+      </c>
+      <c r="B498">
+        <v>1</v>
+      </c>
+      <c r="C498" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D498" s="2">
+        <v>30.56</v>
+      </c>
+      <c r="E498" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="F498" s="3">
+        <v>4.829</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6">
+      <c r="A499" t="s">
+        <v>9</v>
+      </c>
+      <c r="B499">
+        <v>2</v>
+      </c>
+      <c r="C499" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D499" s="2">
+        <v>29.86</v>
+      </c>
+      <c r="E499" s="2">
+        <v>3.98</v>
+      </c>
+      <c r="F499" s="3">
+        <v>0.391</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6">
+      <c r="A500" t="s">
+        <v>9</v>
+      </c>
+      <c r="B500" t="s">
+        <v>10</v>
+      </c>
+      <c r="C500" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D500" s="2">
+        <v>30.42</v>
+      </c>
+      <c r="E500" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="F500" s="3">
+        <v>3.582</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6">
+      <c r="A501" t="s">
+        <v>9</v>
+      </c>
+      <c r="B501">
+        <v>3</v>
+      </c>
+      <c r="C501" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D501" s="2">
+        <v>30.25</v>
+      </c>
+      <c r="E501" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="F501" s="3">
+        <v>4.476</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6">
+      <c r="A502" t="s">
+        <v>9</v>
+      </c>
+      <c r="B502">
+        <v>4</v>
+      </c>
+      <c r="C502" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D502" s="2">
+        <v>29.24</v>
+      </c>
+      <c r="E502" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="F502" s="3">
+        <v>3.021</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6">
+      <c r="A503" t="s">
+        <v>9</v>
+      </c>
+      <c r="B503" t="s">
+        <v>11</v>
+      </c>
+      <c r="C503" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D503" s="2">
+        <v>29.98</v>
+      </c>
+      <c r="E503" s="2">
+        <v>0.69</v>
+      </c>
+      <c r="F503" s="3">
+        <v>2.983</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6">
+      <c r="A504" t="s">
+        <v>12</v>
+      </c>
+      <c r="B504">
+        <v>1</v>
+      </c>
+      <c r="C504" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D504" s="2">
+        <v>30.85</v>
+      </c>
+      <c r="E504" s="2">
+        <v>0</v>
+      </c>
+      <c r="F504" s="3">
+        <v>1.256</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6">
+      <c r="A505" t="s">
+        <v>12</v>
+      </c>
+      <c r="B505">
+        <v>2</v>
+      </c>
+      <c r="C505" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D505" s="2">
+        <v>30.15</v>
+      </c>
+      <c r="E505" s="2">
+        <v>9.95</v>
+      </c>
+      <c r="F505" s="3">
+        <v>0.589</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6">
+      <c r="A506" t="s">
+        <v>12</v>
+      </c>
+      <c r="B506">
+        <v>3</v>
+      </c>
+      <c r="C506" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D506" s="2">
+        <v>30.21</v>
+      </c>
+      <c r="E506" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="F506" s="3">
+        <v>0.618</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6">
+      <c r="A507" t="s">
+        <v>12</v>
+      </c>
+      <c r="B507">
+        <v>4</v>
+      </c>
+      <c r="C507" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D507" s="2">
+        <v>30.25</v>
+      </c>
+      <c r="E507" s="2">
+        <v>0</v>
+      </c>
+      <c r="F507" s="3">
+        <v>1.428</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6">
+      <c r="A508" t="s">
+        <v>12</v>
+      </c>
+      <c r="B508">
+        <v>5</v>
+      </c>
+      <c r="C508" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D508" s="2">
+        <v>31.12</v>
+      </c>
+      <c r="E508" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="F508" s="3">
+        <v>0.538</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6">
+      <c r="A509" t="s">
+        <v>9</v>
+      </c>
+      <c r="B509">
+        <v>1</v>
+      </c>
+      <c r="C509" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D509" s="2">
+        <v>29.61</v>
+      </c>
+      <c r="E509" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="F509" s="3">
+        <v>3.815</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6">
+      <c r="A510" t="s">
+        <v>9</v>
+      </c>
+      <c r="B510">
+        <v>2</v>
+      </c>
+      <c r="C510" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D510" s="2">
+        <v>29.56</v>
+      </c>
+      <c r="E510" s="2">
+        <v>4.34</v>
+      </c>
+      <c r="F510" s="3">
+        <v>1.068</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6">
+      <c r="A511" t="s">
+        <v>9</v>
+      </c>
+      <c r="B511" t="s">
+        <v>10</v>
+      </c>
+      <c r="C511" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D511" s="2">
+        <v>28.79</v>
+      </c>
+      <c r="E511" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="F511" s="3">
+        <v>3.589</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6">
+      <c r="A512" t="s">
+        <v>9</v>
+      </c>
+      <c r="B512">
+        <v>3</v>
+      </c>
+      <c r="C512" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D512" s="2">
+        <v>29.92</v>
+      </c>
+      <c r="E512" s="2">
+        <v>10.47</v>
+      </c>
+      <c r="F512" s="3">
+        <v>9.476</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6">
+      <c r="A513" t="s">
+        <v>9</v>
+      </c>
+      <c r="B513">
+        <v>4</v>
+      </c>
+      <c r="C513" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D513" s="2">
+        <v>29.78</v>
+      </c>
+      <c r="E513" s="2">
+        <v>4.99</v>
+      </c>
+      <c r="F513" s="3">
+        <v>2.121</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6">
+      <c r="A514" t="s">
+        <v>9</v>
+      </c>
+      <c r="B514" t="s">
+        <v>11</v>
+      </c>
+      <c r="C514" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D514" s="2">
+        <v>29.97</v>
+      </c>
+      <c r="E514" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F514" s="3">
+        <v>1.412</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6">
+      <c r="A515" t="s">
+        <v>12</v>
+      </c>
+      <c r="B515">
+        <v>1</v>
+      </c>
+      <c r="C515" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D515" s="2">
+        <v>33.85</v>
+      </c>
+      <c r="E515" s="2">
+        <v>0</v>
+      </c>
+      <c r="F515" s="3">
+        <v>0.986</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6">
+      <c r="A516" t="s">
+        <v>12</v>
+      </c>
+      <c r="B516">
+        <v>2</v>
+      </c>
+      <c r="C516" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D516" s="2">
+        <v>34.12</v>
+      </c>
+      <c r="E516" s="2">
+        <v>2.51</v>
+      </c>
+      <c r="F516" s="3">
+        <v>0.574</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6">
+      <c r="A517" t="s">
+        <v>12</v>
+      </c>
+      <c r="B517">
+        <v>3</v>
+      </c>
+      <c r="C517" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D517" s="2">
+        <v>34.06</v>
+      </c>
+      <c r="E517" s="2">
+        <v>2.03</v>
+      </c>
+      <c r="F517" s="3">
+        <v>0.613</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6">
+      <c r="A518" t="s">
+        <v>12</v>
+      </c>
+      <c r="B518">
+        <v>4</v>
+      </c>
+      <c r="C518" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D518" s="2">
+        <v>33.95</v>
+      </c>
+      <c r="E518" s="2">
+        <v>0.61</v>
+      </c>
+      <c r="F518" s="3">
+        <v>1.321</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6">
+      <c r="A519" t="s">
+        <v>12</v>
+      </c>
+      <c r="B519">
+        <v>5</v>
+      </c>
+      <c r="C519" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D519" s="2">
+        <v>33.82</v>
+      </c>
+      <c r="E519" s="2">
+        <v>11.26</v>
+      </c>
+      <c r="F519" s="3">
+        <v>0.666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F519"/>
+  <dimension ref="A1:F541"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -12063,6 +12063,446 @@
         <v>0.666</v>
       </c>
     </row>
+    <row r="520" spans="1:6">
+      <c r="A520" t="s">
+        <v>9</v>
+      </c>
+      <c r="B520">
+        <v>1</v>
+      </c>
+      <c r="C520" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D520" s="2">
+        <v>28.38</v>
+      </c>
+      <c r="E520" s="2">
+        <v>0</v>
+      </c>
+      <c r="F520" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6">
+      <c r="A521" t="s">
+        <v>9</v>
+      </c>
+      <c r="B521">
+        <v>2</v>
+      </c>
+      <c r="C521" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D521" s="2">
+        <v>28.75</v>
+      </c>
+      <c r="E521" s="2">
+        <v>2.98</v>
+      </c>
+      <c r="F521" s="3">
+        <v>0.908</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6">
+      <c r="A522" t="s">
+        <v>9</v>
+      </c>
+      <c r="B522" t="s">
+        <v>10</v>
+      </c>
+      <c r="C522" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D522" s="2">
+        <v>28.18</v>
+      </c>
+      <c r="E522" s="2">
+        <v>5.57</v>
+      </c>
+      <c r="F522" s="3">
+        <v>1.922</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6">
+      <c r="A523" t="s">
+        <v>9</v>
+      </c>
+      <c r="B523">
+        <v>3</v>
+      </c>
+      <c r="C523" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D523" s="2">
+        <v>28.55</v>
+      </c>
+      <c r="E523" s="2">
+        <v>9.04</v>
+      </c>
+      <c r="F523" s="3">
+        <v>0.412</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6">
+      <c r="A524" t="s">
+        <v>9</v>
+      </c>
+      <c r="B524">
+        <v>4</v>
+      </c>
+      <c r="C524" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D524" s="2">
+        <v>29.39</v>
+      </c>
+      <c r="E524" s="2">
+        <v>3.52</v>
+      </c>
+      <c r="F524" s="3">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6">
+      <c r="A525" t="s">
+        <v>9</v>
+      </c>
+      <c r="B525" t="s">
+        <v>11</v>
+      </c>
+      <c r="C525" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D525" s="2">
+        <v>29.3</v>
+      </c>
+      <c r="E525" s="2">
+        <v>0</v>
+      </c>
+      <c r="F525" s="3">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6">
+      <c r="A526" t="s">
+        <v>12</v>
+      </c>
+      <c r="B526">
+        <v>1</v>
+      </c>
+      <c r="C526" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D526" s="2">
+        <v>31.89</v>
+      </c>
+      <c r="E526" s="2">
+        <v>0</v>
+      </c>
+      <c r="F526" s="3">
+        <v>0.628</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6">
+      <c r="A527" t="s">
+        <v>12</v>
+      </c>
+      <c r="B527">
+        <v>2</v>
+      </c>
+      <c r="C527" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D527" s="2">
+        <v>32.13</v>
+      </c>
+      <c r="E527" s="2">
+        <v>10.49</v>
+      </c>
+      <c r="F527" s="3">
+        <v>1.113</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6">
+      <c r="A528" t="s">
+        <v>12</v>
+      </c>
+      <c r="B528">
+        <v>3</v>
+      </c>
+      <c r="C528" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D528" s="2">
+        <v>32.16</v>
+      </c>
+      <c r="E528" s="2">
+        <v>5.47</v>
+      </c>
+      <c r="F528" s="3">
+        <v>2.356</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6">
+      <c r="A529" t="s">
+        <v>12</v>
+      </c>
+      <c r="B529">
+        <v>4</v>
+      </c>
+      <c r="C529" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D529" s="2">
+        <v>32.45</v>
+      </c>
+      <c r="E529" s="2">
+        <v>2.33</v>
+      </c>
+      <c r="F529" s="3">
+        <v>2.333</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6">
+      <c r="A530" t="s">
+        <v>12</v>
+      </c>
+      <c r="B530">
+        <v>5</v>
+      </c>
+      <c r="C530" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D530" s="2">
+        <v>32.14</v>
+      </c>
+      <c r="E530" s="2">
+        <v>24.68</v>
+      </c>
+      <c r="F530" s="3">
+        <v>2.468</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6">
+      <c r="A531" t="s">
+        <v>9</v>
+      </c>
+      <c r="B531">
+        <v>1</v>
+      </c>
+      <c r="C531" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D531" s="2">
+        <v>28.08</v>
+      </c>
+      <c r="E531" s="2">
+        <v>0</v>
+      </c>
+      <c r="F531" s="3">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6">
+      <c r="A532" t="s">
+        <v>9</v>
+      </c>
+      <c r="B532">
+        <v>2</v>
+      </c>
+      <c r="C532" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D532" s="2">
+        <v>28.11</v>
+      </c>
+      <c r="E532" s="2">
+        <v>4.07</v>
+      </c>
+      <c r="F532" s="3">
+        <v>1.318</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6">
+      <c r="A533" t="s">
+        <v>9</v>
+      </c>
+      <c r="B533" t="s">
+        <v>10</v>
+      </c>
+      <c r="C533" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D533" s="2">
+        <v>29</v>
+      </c>
+      <c r="E533" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="F533" s="3">
+        <v>0.708</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6">
+      <c r="A534" t="s">
+        <v>9</v>
+      </c>
+      <c r="B534">
+        <v>3</v>
+      </c>
+      <c r="C534" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D534" s="2">
+        <v>28.61</v>
+      </c>
+      <c r="E534" s="2">
+        <v>6.84</v>
+      </c>
+      <c r="F534" s="3">
+        <v>1.422</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6">
+      <c r="A535" t="s">
+        <v>9</v>
+      </c>
+      <c r="B535">
+        <v>4</v>
+      </c>
+      <c r="C535" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D535" s="2">
+        <v>29.26</v>
+      </c>
+      <c r="E535" s="2">
+        <v>0</v>
+      </c>
+      <c r="F535" s="3">
+        <v>1.613</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6">
+      <c r="A536" t="s">
+        <v>9</v>
+      </c>
+      <c r="B536" t="s">
+        <v>11</v>
+      </c>
+      <c r="C536" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D536" s="2">
+        <v>29.33</v>
+      </c>
+      <c r="E536" s="2">
+        <v>3.15</v>
+      </c>
+      <c r="F536" s="3">
+        <v>1.623</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6">
+      <c r="A537" t="s">
+        <v>12</v>
+      </c>
+      <c r="B537">
+        <v>1</v>
+      </c>
+      <c r="C537" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D537" s="2">
+        <v>31.52</v>
+      </c>
+      <c r="E537" s="2">
+        <v>0</v>
+      </c>
+      <c r="F537" s="3">
+        <v>3.184</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6">
+      <c r="A538" t="s">
+        <v>12</v>
+      </c>
+      <c r="B538">
+        <v>2</v>
+      </c>
+      <c r="C538" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D538" s="2">
+        <v>31.65</v>
+      </c>
+      <c r="E538" s="2">
+        <v>6.41</v>
+      </c>
+      <c r="F538" s="3">
+        <v>1.741</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6">
+      <c r="A539" t="s">
+        <v>12</v>
+      </c>
+      <c r="B539">
+        <v>3</v>
+      </c>
+      <c r="C539" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D539" s="2">
+        <v>31.69</v>
+      </c>
+      <c r="E539" s="2">
+        <v>4</v>
+      </c>
+      <c r="F539" s="3">
+        <v>2.044</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6">
+      <c r="A540" t="s">
+        <v>12</v>
+      </c>
+      <c r="B540">
+        <v>4</v>
+      </c>
+      <c r="C540" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D540" s="2">
+        <v>31.91</v>
+      </c>
+      <c r="E540" s="2">
+        <v>1.54</v>
+      </c>
+      <c r="F540" s="3">
+        <v>2.458</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6">
+      <c r="A541" t="s">
+        <v>12</v>
+      </c>
+      <c r="B541">
+        <v>5</v>
+      </c>
+      <c r="C541" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D541" s="2">
+        <v>31.63</v>
+      </c>
+      <c r="E541" s="2">
+        <v>22.43</v>
+      </c>
+      <c r="F541" s="3">
+        <v>2.191</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12960" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F541"/>
+  <dimension ref="A1:F557"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -12503,6 +12503,326 @@
         <v>2.191</v>
       </c>
     </row>
+    <row r="542" spans="1:6">
+      <c r="A542" t="s">
+        <v>9</v>
+      </c>
+      <c r="B542">
+        <v>1</v>
+      </c>
+      <c r="C542" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D542" s="2">
+        <v>29.82</v>
+      </c>
+      <c r="E542" s="2">
+        <v>1.07</v>
+      </c>
+      <c r="F542" s="3">
+        <v>4.623</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6">
+      <c r="A543" t="s">
+        <v>9</v>
+      </c>
+      <c r="B543">
+        <v>2</v>
+      </c>
+      <c r="C543" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D543" s="2">
+        <v>29.69</v>
+      </c>
+      <c r="E543" s="2">
+        <v>2.307</v>
+      </c>
+      <c r="F543" s="3">
+        <v>0.142</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6">
+      <c r="A544" t="s">
+        <v>9</v>
+      </c>
+      <c r="B544" t="s">
+        <v>10</v>
+      </c>
+      <c r="C544" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D544" s="2">
+        <v>29.91</v>
+      </c>
+      <c r="E544" s="2">
+        <v>2.583</v>
+      </c>
+      <c r="F544" s="3">
+        <v>4.782</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6">
+      <c r="A545" t="s">
+        <v>9</v>
+      </c>
+      <c r="B545">
+        <v>3</v>
+      </c>
+      <c r="C545" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D545" s="2">
+        <v>30.84</v>
+      </c>
+      <c r="E545" s="2">
+        <v>9.23</v>
+      </c>
+      <c r="F545" s="3">
+        <v>5.449</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6">
+      <c r="A546" t="s">
+        <v>9</v>
+      </c>
+      <c r="B546">
+        <v>4</v>
+      </c>
+      <c r="C546" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D546" s="2">
+        <v>30.96</v>
+      </c>
+      <c r="E546" s="2">
+        <v>4.57</v>
+      </c>
+      <c r="F546" s="3">
+        <v>3.985</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6">
+      <c r="A547" t="s">
+        <v>9</v>
+      </c>
+      <c r="B547" t="s">
+        <v>11</v>
+      </c>
+      <c r="C547" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D547" s="2">
+        <v>31.42</v>
+      </c>
+      <c r="E547" s="2">
+        <v>0.55</v>
+      </c>
+      <c r="F547" s="3">
+        <v>2.996</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6">
+      <c r="A548" t="s">
+        <v>12</v>
+      </c>
+      <c r="B548">
+        <v>1</v>
+      </c>
+      <c r="C548" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D548" s="2">
+        <v>34.89</v>
+      </c>
+      <c r="E548" s="2">
+        <v>1.31</v>
+      </c>
+      <c r="F548" s="3">
+        <v>0.968</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6">
+      <c r="A549" t="s">
+        <v>12</v>
+      </c>
+      <c r="B549">
+        <v>2</v>
+      </c>
+      <c r="C549" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D549" s="2">
+        <v>34.72</v>
+      </c>
+      <c r="E549" s="2">
+        <v>1.74</v>
+      </c>
+      <c r="F549" s="3">
+        <v>0.721</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6">
+      <c r="A550" t="s">
+        <v>12</v>
+      </c>
+      <c r="B550">
+        <v>3</v>
+      </c>
+      <c r="C550" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D550" s="2">
+        <v>34.92</v>
+      </c>
+      <c r="E550" s="2">
+        <v>8.73</v>
+      </c>
+      <c r="F550" s="3">
+        <v>0.492</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6">
+      <c r="A551" t="s">
+        <v>12</v>
+      </c>
+      <c r="B551">
+        <v>4</v>
+      </c>
+      <c r="C551" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D551" s="2">
+        <v>35.02</v>
+      </c>
+      <c r="E551" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="F551" s="3">
+        <v>1.112</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6">
+      <c r="A552" t="s">
+        <v>12</v>
+      </c>
+      <c r="B552">
+        <v>5</v>
+      </c>
+      <c r="C552" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D552" s="2">
+        <v>35.16</v>
+      </c>
+      <c r="E552" s="2">
+        <v>22.8</v>
+      </c>
+      <c r="F552" s="3">
+        <v>0.624</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6">
+      <c r="A553" t="s">
+        <v>12</v>
+      </c>
+      <c r="B553">
+        <v>1</v>
+      </c>
+      <c r="C553" s="1">
+        <v>46183</v>
+      </c>
+      <c r="D553" s="2">
+        <v>31.52</v>
+      </c>
+      <c r="E553" s="2">
+        <v>0</v>
+      </c>
+      <c r="F553" s="2">
+        <v>0.598</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6">
+      <c r="A554" t="s">
+        <v>12</v>
+      </c>
+      <c r="B554">
+        <v>2</v>
+      </c>
+      <c r="C554" s="1">
+        <v>46183</v>
+      </c>
+      <c r="D554" s="2">
+        <v>31.85</v>
+      </c>
+      <c r="E554" s="2">
+        <v>8.19</v>
+      </c>
+      <c r="F554" s="2">
+        <v>1.072</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6">
+      <c r="A555" t="s">
+        <v>12</v>
+      </c>
+      <c r="B555">
+        <v>3</v>
+      </c>
+      <c r="C555" s="1">
+        <v>46183</v>
+      </c>
+      <c r="D555" s="2">
+        <v>31.94</v>
+      </c>
+      <c r="E555" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="F555" s="2">
+        <v>2.132</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6">
+      <c r="A556" t="s">
+        <v>12</v>
+      </c>
+      <c r="B556">
+        <v>4</v>
+      </c>
+      <c r="C556" s="1">
+        <v>46183</v>
+      </c>
+      <c r="D556" s="2">
+        <v>32.38</v>
+      </c>
+      <c r="E556" s="2">
+        <v>2.12</v>
+      </c>
+      <c r="F556" s="2">
+        <v>2.244</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6">
+      <c r="A557" t="s">
+        <v>12</v>
+      </c>
+      <c r="B557">
+        <v>5</v>
+      </c>
+      <c r="C557" s="1">
+        <v>46183</v>
+      </c>
+      <c r="D557" s="2">
+        <v>31.92</v>
+      </c>
+      <c r="E557" s="2">
+        <v>23.92</v>
+      </c>
+      <c r="F557" s="2">
+        <v>2.268</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960" activeTab="1"/>
+    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F557"/>
+  <dimension ref="A1:F562"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -12823,6 +12823,106 @@
         <v>2.268</v>
       </c>
     </row>
+    <row r="558" spans="1:6">
+      <c r="A558" t="s">
+        <v>12</v>
+      </c>
+      <c r="B558">
+        <v>1</v>
+      </c>
+      <c r="C558" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D558" s="2">
+        <v>30.24</v>
+      </c>
+      <c r="E558" s="2">
+        <v>0</v>
+      </c>
+      <c r="F558" s="2">
+        <v>0.295</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6">
+      <c r="A559" t="s">
+        <v>12</v>
+      </c>
+      <c r="B559">
+        <v>2</v>
+      </c>
+      <c r="C559" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D559" s="2">
+        <v>30.76</v>
+      </c>
+      <c r="E559" s="2">
+        <v>2.17</v>
+      </c>
+      <c r="F559" s="2">
+        <v>0.514</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6">
+      <c r="A560" t="s">
+        <v>12</v>
+      </c>
+      <c r="B560">
+        <v>3</v>
+      </c>
+      <c r="C560" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D560" s="2">
+        <v>32.41</v>
+      </c>
+      <c r="E560" s="2">
+        <v>24.03</v>
+      </c>
+      <c r="F560" s="2">
+        <v>0.446</v>
+      </c>
+    </row>
+    <row r="561" spans="1:6">
+      <c r="A561" t="s">
+        <v>12</v>
+      </c>
+      <c r="B561">
+        <v>4</v>
+      </c>
+      <c r="C561" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D561" s="2">
+        <v>29.07</v>
+      </c>
+      <c r="E561" s="2">
+        <v>1.08</v>
+      </c>
+      <c r="F561" s="2">
+        <v>0.461</v>
+      </c>
+    </row>
+    <row r="562" spans="1:6">
+      <c r="A562" t="s">
+        <v>12</v>
+      </c>
+      <c r="B562">
+        <v>5</v>
+      </c>
+      <c r="C562" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D562" s="2">
+        <v>32.38</v>
+      </c>
+      <c r="E562" s="2">
+        <v>36.83</v>
+      </c>
+      <c r="F562" s="2">
+        <v>0.553</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12960" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F562"/>
+  <dimension ref="A1:F567"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -12739,7 +12739,7 @@
       <c r="E553" s="2">
         <v>0</v>
       </c>
-      <c r="F553" s="2">
+      <c r="F553" s="3">
         <v>0.598</v>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       <c r="E554" s="2">
         <v>8.19</v>
       </c>
-      <c r="F554" s="2">
+      <c r="F554" s="3">
         <v>1.072</v>
       </c>
     </row>
@@ -12779,7 +12779,7 @@
       <c r="E555" s="2">
         <v>6.25</v>
       </c>
-      <c r="F555" s="2">
+      <c r="F555" s="3">
         <v>2.132</v>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       <c r="E556" s="2">
         <v>2.12</v>
       </c>
-      <c r="F556" s="2">
+      <c r="F556" s="3">
         <v>2.244</v>
       </c>
     </row>
@@ -12819,7 +12819,7 @@
       <c r="E557" s="2">
         <v>23.92</v>
       </c>
-      <c r="F557" s="2">
+      <c r="F557" s="3">
         <v>2.268</v>
       </c>
     </row>
@@ -12839,7 +12839,7 @@
       <c r="E558" s="2">
         <v>0</v>
       </c>
-      <c r="F558" s="2">
+      <c r="F558" s="3">
         <v>0.295</v>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       <c r="E559" s="2">
         <v>2.17</v>
       </c>
-      <c r="F559" s="2">
+      <c r="F559" s="3">
         <v>0.514</v>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       <c r="E560" s="2">
         <v>24.03</v>
       </c>
-      <c r="F560" s="2">
+      <c r="F560" s="3">
         <v>0.446</v>
       </c>
     </row>
@@ -12899,7 +12899,7 @@
       <c r="E561" s="2">
         <v>1.08</v>
       </c>
-      <c r="F561" s="2">
+      <c r="F561" s="3">
         <v>0.461</v>
       </c>
     </row>
@@ -12919,8 +12919,108 @@
       <c r="E562" s="2">
         <v>36.83</v>
       </c>
-      <c r="F562" s="2">
+      <c r="F562" s="3">
         <v>0.553</v>
+      </c>
+    </row>
+    <row r="563" spans="1:6">
+      <c r="A563" t="s">
+        <v>12</v>
+      </c>
+      <c r="B563">
+        <v>1</v>
+      </c>
+      <c r="C563" s="1">
+        <v>46187</v>
+      </c>
+      <c r="D563" s="2">
+        <v>29.26</v>
+      </c>
+      <c r="E563" s="2">
+        <v>3.36</v>
+      </c>
+      <c r="F563" s="3">
+        <v>0.594</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6">
+      <c r="A564" t="s">
+        <v>12</v>
+      </c>
+      <c r="B564">
+        <v>2</v>
+      </c>
+      <c r="C564" s="1">
+        <v>46187</v>
+      </c>
+      <c r="D564" s="2">
+        <v>29.08</v>
+      </c>
+      <c r="E564" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="F564" s="3">
+        <v>1.127</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6">
+      <c r="A565" t="s">
+        <v>12</v>
+      </c>
+      <c r="B565">
+        <v>3</v>
+      </c>
+      <c r="C565" s="1">
+        <v>46187</v>
+      </c>
+      <c r="D565" s="2">
+        <v>31.58</v>
+      </c>
+      <c r="E565" s="2">
+        <v>27.99</v>
+      </c>
+      <c r="F565" s="3">
+        <v>2.246</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6">
+      <c r="A566" t="s">
+        <v>12</v>
+      </c>
+      <c r="B566">
+        <v>4</v>
+      </c>
+      <c r="C566" s="1">
+        <v>46187</v>
+      </c>
+      <c r="D566" s="2">
+        <v>27.76</v>
+      </c>
+      <c r="E566" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="F566" s="3">
+        <v>2.491</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6">
+      <c r="A567" t="s">
+        <v>12</v>
+      </c>
+      <c r="B567">
+        <v>5</v>
+      </c>
+      <c r="C567" s="1">
+        <v>46187</v>
+      </c>
+      <c r="D567" s="2">
+        <v>31.56</v>
+      </c>
+      <c r="E567" s="2">
+        <v>41.37</v>
+      </c>
+      <c r="F567" s="3">
+        <v>2.538</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960" activeTab="1"/>
+    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F567"/>
+  <dimension ref="A1:F606"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -13023,6 +13023,786 @@
         <v>2.538</v>
       </c>
     </row>
+    <row r="568" spans="1:6">
+      <c r="A568" t="s">
+        <v>9</v>
+      </c>
+      <c r="B568">
+        <v>1</v>
+      </c>
+      <c r="C568" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D568" s="2">
+        <v>28.42</v>
+      </c>
+      <c r="E568" s="2">
+        <v>8.09</v>
+      </c>
+      <c r="F568" s="3">
+        <v>0.902</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6">
+      <c r="A569" t="s">
+        <v>9</v>
+      </c>
+      <c r="B569">
+        <v>2</v>
+      </c>
+      <c r="C569" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D569" s="2">
+        <v>29.33</v>
+      </c>
+      <c r="E569" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="F569" s="3">
+        <v>0.986</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6">
+      <c r="A570" t="s">
+        <v>9</v>
+      </c>
+      <c r="B570" t="s">
+        <v>10</v>
+      </c>
+      <c r="C570" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D570" s="2">
+        <v>28.85</v>
+      </c>
+      <c r="E570" s="2">
+        <v>9.38</v>
+      </c>
+      <c r="F570" s="3">
+        <v>1.305</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6">
+      <c r="A571" t="s">
+        <v>9</v>
+      </c>
+      <c r="B571">
+        <v>3</v>
+      </c>
+      <c r="C571" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D571" s="2">
+        <v>29.35</v>
+      </c>
+      <c r="E571" s="2">
+        <v>12.43</v>
+      </c>
+      <c r="F571" s="3">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6">
+      <c r="A572" t="s">
+        <v>9</v>
+      </c>
+      <c r="B572">
+        <v>4</v>
+      </c>
+      <c r="C572" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D572" s="2">
+        <v>30.02</v>
+      </c>
+      <c r="E572" s="2">
+        <v>5.1</v>
+      </c>
+      <c r="F572" s="3">
+        <v>1.981</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6">
+      <c r="A573" t="s">
+        <v>9</v>
+      </c>
+      <c r="B573" t="s">
+        <v>11</v>
+      </c>
+      <c r="C573" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D573" s="2">
+        <v>24.8</v>
+      </c>
+      <c r="E573" s="2">
+        <v>0</v>
+      </c>
+      <c r="F573" s="3">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6">
+      <c r="A574" t="s">
+        <v>12</v>
+      </c>
+      <c r="B574">
+        <v>1</v>
+      </c>
+      <c r="C574" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D574" s="2">
+        <v>29.59</v>
+      </c>
+      <c r="E574" s="2">
+        <v>0</v>
+      </c>
+      <c r="F574" s="3">
+        <v>4.831</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6">
+      <c r="A575" t="s">
+        <v>12</v>
+      </c>
+      <c r="B575">
+        <v>2</v>
+      </c>
+      <c r="C575" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D575" s="2">
+        <v>31.03</v>
+      </c>
+      <c r="E575" s="2">
+        <v>3.54</v>
+      </c>
+      <c r="F575" s="3">
+        <v>1.094</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6">
+      <c r="A576" t="s">
+        <v>12</v>
+      </c>
+      <c r="B576">
+        <v>3</v>
+      </c>
+      <c r="C576" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D576" s="2">
+        <v>32.12</v>
+      </c>
+      <c r="E576" s="2">
+        <v>29.91</v>
+      </c>
+      <c r="F576" s="3">
+        <v>0.964</v>
+      </c>
+    </row>
+    <row r="577" spans="1:6">
+      <c r="A577" t="s">
+        <v>12</v>
+      </c>
+      <c r="B577">
+        <v>4</v>
+      </c>
+      <c r="C577" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D577" s="2">
+        <v>28.01</v>
+      </c>
+      <c r="E577" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="F577" s="3">
+        <v>0.519</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6">
+      <c r="A578" t="s">
+        <v>12</v>
+      </c>
+      <c r="B578">
+        <v>5</v>
+      </c>
+      <c r="C578" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D578" s="2">
+        <v>32.07</v>
+      </c>
+      <c r="E578" s="2">
+        <v>41.68</v>
+      </c>
+      <c r="F578" s="3">
+        <v>1.144</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6">
+      <c r="A579" t="s">
+        <v>9</v>
+      </c>
+      <c r="B579">
+        <v>1</v>
+      </c>
+      <c r="C579" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D579" s="2">
+        <v>24.69</v>
+      </c>
+      <c r="E579" s="2">
+        <v>20.58</v>
+      </c>
+      <c r="F579" s="3">
+        <v>0.784</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6">
+      <c r="A580" t="s">
+        <v>9</v>
+      </c>
+      <c r="B580">
+        <v>2</v>
+      </c>
+      <c r="C580" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D580" s="2">
+        <v>24.13</v>
+      </c>
+      <c r="E580" s="2">
+        <v>1.43</v>
+      </c>
+      <c r="F580" s="3">
+        <v>0.103</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6">
+      <c r="A581" t="s">
+        <v>9</v>
+      </c>
+      <c r="B581" t="s">
+        <v>10</v>
+      </c>
+      <c r="C581" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D581" s="2">
+        <v>23.53</v>
+      </c>
+      <c r="E581" s="2">
+        <v>3.11</v>
+      </c>
+      <c r="F581" s="3">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6">
+      <c r="A582" t="s">
+        <v>9</v>
+      </c>
+      <c r="B582">
+        <v>3</v>
+      </c>
+      <c r="C582" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D582" s="2">
+        <v>24.29</v>
+      </c>
+      <c r="E582" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="F582" s="3">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6">
+      <c r="A583" t="s">
+        <v>9</v>
+      </c>
+      <c r="B583">
+        <v>4</v>
+      </c>
+      <c r="C583" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D583" s="2">
+        <v>24.49</v>
+      </c>
+      <c r="E583" s="2">
+        <v>1.95</v>
+      </c>
+      <c r="F583" s="3">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6">
+      <c r="A584" t="s">
+        <v>9</v>
+      </c>
+      <c r="B584" t="s">
+        <v>11</v>
+      </c>
+      <c r="C584" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D584" s="2">
+        <v>23.58</v>
+      </c>
+      <c r="E584" s="2">
+        <v>1.21</v>
+      </c>
+      <c r="F584" s="3">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6">
+      <c r="A585" t="s">
+        <v>12</v>
+      </c>
+      <c r="B585">
+        <v>1</v>
+      </c>
+      <c r="C585" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D585" s="2">
+        <v>29.59</v>
+      </c>
+      <c r="E585" s="2">
+        <v>0</v>
+      </c>
+      <c r="F585" s="3">
+        <v>0.644</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6">
+      <c r="A586" t="s">
+        <v>12</v>
+      </c>
+      <c r="B586">
+        <v>2</v>
+      </c>
+      <c r="C586" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D586" s="2">
+        <v>26.07</v>
+      </c>
+      <c r="E586" s="2">
+        <v>6.48</v>
+      </c>
+      <c r="F586" s="3">
+        <v>0.694</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6">
+      <c r="A587" t="s">
+        <v>12</v>
+      </c>
+      <c r="B587">
+        <v>3</v>
+      </c>
+      <c r="C587" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D587" s="2">
+        <v>26.69</v>
+      </c>
+      <c r="E587" s="2">
+        <v>27.84</v>
+      </c>
+      <c r="F587" s="3">
+        <v>0.735</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6">
+      <c r="A588" t="s">
+        <v>12</v>
+      </c>
+      <c r="B588">
+        <v>4</v>
+      </c>
+      <c r="C588" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D588" s="2">
+        <v>23</v>
+      </c>
+      <c r="E588" s="2">
+        <v>3.57</v>
+      </c>
+      <c r="F588" s="3">
+        <v>0.646</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6">
+      <c r="A589" t="s">
+        <v>12</v>
+      </c>
+      <c r="B589">
+        <v>5</v>
+      </c>
+      <c r="C589" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D589" s="2">
+        <v>26.63</v>
+      </c>
+      <c r="E589" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F589" s="3">
+        <v>0.662</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6">
+      <c r="A590" t="s">
+        <v>12</v>
+      </c>
+      <c r="B590">
+        <v>1</v>
+      </c>
+      <c r="C590" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D590" s="2">
+        <v>28.47</v>
+      </c>
+      <c r="E590" s="2">
+        <v>1.22</v>
+      </c>
+      <c r="F590" s="3">
+        <v>0.682</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6">
+      <c r="A591" t="s">
+        <v>12</v>
+      </c>
+      <c r="B591">
+        <v>2</v>
+      </c>
+      <c r="C591" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D591" s="2">
+        <v>27.56</v>
+      </c>
+      <c r="E591" s="2">
+        <v>2.98</v>
+      </c>
+      <c r="F591" s="3">
+        <v>0.711</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6">
+      <c r="A592" t="s">
+        <v>12</v>
+      </c>
+      <c r="B592">
+        <v>3</v>
+      </c>
+      <c r="C592" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D592" s="2">
+        <v>28.63</v>
+      </c>
+      <c r="E592" s="2">
+        <v>35.78</v>
+      </c>
+      <c r="F592" s="3">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6">
+      <c r="A593" t="s">
+        <v>12</v>
+      </c>
+      <c r="B593">
+        <v>4</v>
+      </c>
+      <c r="C593" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D593" s="2">
+        <v>25.46</v>
+      </c>
+      <c r="E593" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="F593" s="3">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6">
+      <c r="A594" t="s">
+        <v>12</v>
+      </c>
+      <c r="B594">
+        <v>5</v>
+      </c>
+      <c r="C594" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D594" s="2">
+        <v>28.67</v>
+      </c>
+      <c r="E594" s="2">
+        <v>2.18</v>
+      </c>
+      <c r="F594" s="3">
+        <v>0.747</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6">
+      <c r="A595" t="s">
+        <v>9</v>
+      </c>
+      <c r="B595">
+        <v>1</v>
+      </c>
+      <c r="C595" s="1">
+        <v>46191</v>
+      </c>
+      <c r="D595" s="2">
+        <v>25.07</v>
+      </c>
+      <c r="E595" s="2">
+        <v>0.67</v>
+      </c>
+      <c r="F595" s="3">
+        <v>0.812</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6">
+      <c r="A596" t="s">
+        <v>9</v>
+      </c>
+      <c r="B596">
+        <v>2</v>
+      </c>
+      <c r="C596" s="1">
+        <v>46191</v>
+      </c>
+      <c r="D596" s="2">
+        <v>24.51</v>
+      </c>
+      <c r="E596" s="2">
+        <v>2.51</v>
+      </c>
+      <c r="F596" s="3">
+        <v>0.392</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6">
+      <c r="A597" t="s">
+        <v>9</v>
+      </c>
+      <c r="B597" t="s">
+        <v>10</v>
+      </c>
+      <c r="C597" s="1">
+        <v>46191</v>
+      </c>
+      <c r="D597" s="2">
+        <v>24.11</v>
+      </c>
+      <c r="E597" s="2">
+        <v>12.41</v>
+      </c>
+      <c r="F597" s="3">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6">
+      <c r="A598" t="s">
+        <v>9</v>
+      </c>
+      <c r="B598">
+        <v>3</v>
+      </c>
+      <c r="C598" s="1">
+        <v>46191</v>
+      </c>
+      <c r="D598" s="2">
+        <v>25.12</v>
+      </c>
+      <c r="E598" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="F598" s="3">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6">
+      <c r="A599" t="s">
+        <v>9</v>
+      </c>
+      <c r="B599">
+        <v>4</v>
+      </c>
+      <c r="C599" s="1">
+        <v>46191</v>
+      </c>
+      <c r="D599" s="2">
+        <v>25.05</v>
+      </c>
+      <c r="E599" s="2">
+        <v>7.46</v>
+      </c>
+      <c r="F599" s="3">
+        <v>2.236</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6">
+      <c r="A600" t="s">
+        <v>9</v>
+      </c>
+      <c r="B600" t="s">
+        <v>11</v>
+      </c>
+      <c r="C600" s="1">
+        <v>46191</v>
+      </c>
+      <c r="D600" s="2">
+        <v>24.78</v>
+      </c>
+      <c r="E600" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="F600" s="3">
+        <v>3.158</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6">
+      <c r="A601" t="s">
+        <v>9</v>
+      </c>
+      <c r="B601">
+        <v>1</v>
+      </c>
+      <c r="C601" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D601" s="2">
+        <v>25.16</v>
+      </c>
+      <c r="E601" s="2">
+        <v>0.68</v>
+      </c>
+      <c r="F601" s="3">
+        <v>0.566</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6">
+      <c r="A602" t="s">
+        <v>9</v>
+      </c>
+      <c r="B602">
+        <v>2</v>
+      </c>
+      <c r="C602" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D602" s="2">
+        <v>26.2</v>
+      </c>
+      <c r="E602" s="2">
+        <v>1.79</v>
+      </c>
+      <c r="F602" s="3">
+        <v>2.883</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6">
+      <c r="A603" t="s">
+        <v>9</v>
+      </c>
+      <c r="B603" t="s">
+        <v>10</v>
+      </c>
+      <c r="C603" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D603" s="2">
+        <v>25.73</v>
+      </c>
+      <c r="E603" s="2">
+        <v>14.62</v>
+      </c>
+      <c r="F603" s="3">
+        <v>0.935</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6">
+      <c r="A604" t="s">
+        <v>9</v>
+      </c>
+      <c r="B604">
+        <v>3</v>
+      </c>
+      <c r="C604" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D604" s="2">
+        <v>26.18</v>
+      </c>
+      <c r="E604" s="2">
+        <v>18.25</v>
+      </c>
+      <c r="F604" s="3">
+        <v>0.558</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6">
+      <c r="A605" t="s">
+        <v>9</v>
+      </c>
+      <c r="B605">
+        <v>4</v>
+      </c>
+      <c r="C605" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D605" s="2">
+        <v>26.22</v>
+      </c>
+      <c r="E605" s="2">
+        <v>6.11</v>
+      </c>
+      <c r="F605" s="3">
+        <v>2.549</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6">
+      <c r="A606" t="s">
+        <v>9</v>
+      </c>
+      <c r="B606" t="s">
+        <v>11</v>
+      </c>
+      <c r="C606" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D606" s="2">
+        <v>26.15</v>
+      </c>
+      <c r="E606" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="F606" s="3">
+        <v>2.602</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F606"/>
+  <dimension ref="A1:F697"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -13803,6 +13803,1826 @@
         <v>2.602</v>
       </c>
     </row>
+    <row r="607" spans="1:6">
+      <c r="A607" t="s">
+        <v>12</v>
+      </c>
+      <c r="B607">
+        <v>1</v>
+      </c>
+      <c r="C607" s="1">
+        <v>46194</v>
+      </c>
+      <c r="D607" s="2">
+        <v>29.84</v>
+      </c>
+      <c r="E607" s="2">
+        <v>0</v>
+      </c>
+      <c r="F607" s="3">
+        <v>1.829</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6">
+      <c r="A608" t="s">
+        <v>12</v>
+      </c>
+      <c r="B608">
+        <v>2</v>
+      </c>
+      <c r="C608" s="1">
+        <v>46194</v>
+      </c>
+      <c r="D608" s="2">
+        <v>29.89</v>
+      </c>
+      <c r="E608" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="F608" s="3">
+        <v>1.127</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6">
+      <c r="A609" t="s">
+        <v>12</v>
+      </c>
+      <c r="B609">
+        <v>3</v>
+      </c>
+      <c r="C609" s="1">
+        <v>46194</v>
+      </c>
+      <c r="D609" s="2">
+        <v>29.87</v>
+      </c>
+      <c r="E609" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F609" s="3">
+        <v>1.824</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6">
+      <c r="A610" t="s">
+        <v>12</v>
+      </c>
+      <c r="B610">
+        <v>4</v>
+      </c>
+      <c r="C610" s="1">
+        <v>46194</v>
+      </c>
+      <c r="D610" s="2">
+        <v>29.82</v>
+      </c>
+      <c r="E610" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="F610" s="3">
+        <v>0.964</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6">
+      <c r="A611" t="s">
+        <v>12</v>
+      </c>
+      <c r="B611">
+        <v>5</v>
+      </c>
+      <c r="C611" s="1">
+        <v>46194</v>
+      </c>
+      <c r="D611" s="2">
+        <v>29.85</v>
+      </c>
+      <c r="E611" s="2">
+        <v>21.4</v>
+      </c>
+      <c r="F611" s="3">
+        <v>0.712</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6">
+      <c r="A612" t="s">
+        <v>9</v>
+      </c>
+      <c r="B612">
+        <v>1</v>
+      </c>
+      <c r="C612" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D612" s="2">
+        <v>26.35</v>
+      </c>
+      <c r="E612" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="F612" s="3">
+        <v>1.736</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6">
+      <c r="A613" t="s">
+        <v>9</v>
+      </c>
+      <c r="B613">
+        <v>2</v>
+      </c>
+      <c r="C613" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D613" s="2">
+        <v>26.3</v>
+      </c>
+      <c r="E613" s="2">
+        <v>2.17</v>
+      </c>
+      <c r="F613" s="3">
+        <v>2.672</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6">
+      <c r="A614" t="s">
+        <v>9</v>
+      </c>
+      <c r="B614" t="s">
+        <v>10</v>
+      </c>
+      <c r="C614" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D614" s="2">
+        <v>26.22</v>
+      </c>
+      <c r="E614" s="2">
+        <v>16.12</v>
+      </c>
+      <c r="F614" s="3">
+        <v>1.237</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6">
+      <c r="A615" t="s">
+        <v>9</v>
+      </c>
+      <c r="B615">
+        <v>3</v>
+      </c>
+      <c r="C615" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D615" s="2">
+        <v>26.15</v>
+      </c>
+      <c r="E615" s="2">
+        <v>16.28</v>
+      </c>
+      <c r="F615" s="3">
+        <v>0.616</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6">
+      <c r="A616" t="s">
+        <v>9</v>
+      </c>
+      <c r="B616">
+        <v>4</v>
+      </c>
+      <c r="C616" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D616" s="2">
+        <v>26.18</v>
+      </c>
+      <c r="E616" s="2">
+        <v>8.73</v>
+      </c>
+      <c r="F616" s="3">
+        <v>2.331</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6">
+      <c r="A617" t="s">
+        <v>9</v>
+      </c>
+      <c r="B617" t="s">
+        <v>11</v>
+      </c>
+      <c r="C617" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D617" s="2">
+        <v>26.32</v>
+      </c>
+      <c r="E617" s="2">
+        <v>1.27</v>
+      </c>
+      <c r="F617" s="3">
+        <v>2.011</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6">
+      <c r="A618" t="s">
+        <v>12</v>
+      </c>
+      <c r="B618">
+        <v>1</v>
+      </c>
+      <c r="C618" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D618" s="2">
+        <v>30.57</v>
+      </c>
+      <c r="E618" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="F618" s="3">
+        <v>1.733</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6">
+      <c r="A619" t="s">
+        <v>12</v>
+      </c>
+      <c r="B619">
+        <v>2</v>
+      </c>
+      <c r="C619" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D619" s="2">
+        <v>30.36</v>
+      </c>
+      <c r="E619" s="2">
+        <v>6.86</v>
+      </c>
+      <c r="F619" s="3">
+        <v>1.347</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6">
+      <c r="A620" t="s">
+        <v>12</v>
+      </c>
+      <c r="B620">
+        <v>3</v>
+      </c>
+      <c r="C620" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D620" s="2">
+        <v>29.29</v>
+      </c>
+      <c r="E620" s="2">
+        <v>1.74</v>
+      </c>
+      <c r="F620" s="3">
+        <v>1.637</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6">
+      <c r="A621" t="s">
+        <v>12</v>
+      </c>
+      <c r="B621">
+        <v>4</v>
+      </c>
+      <c r="C621" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D621" s="2">
+        <v>29.84</v>
+      </c>
+      <c r="E621" s="2">
+        <v>6.41</v>
+      </c>
+      <c r="F621" s="3">
+        <v>1.062</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6">
+      <c r="A622" t="s">
+        <v>12</v>
+      </c>
+      <c r="B622">
+        <v>5</v>
+      </c>
+      <c r="C622" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D622" s="2">
+        <v>29.3</v>
+      </c>
+      <c r="E622" s="2">
+        <v>20.11</v>
+      </c>
+      <c r="F622" s="3">
+        <v>0.835</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6">
+      <c r="A623" t="s">
+        <v>9</v>
+      </c>
+      <c r="B623">
+        <v>1</v>
+      </c>
+      <c r="C623" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D623" s="2">
+        <v>27.71</v>
+      </c>
+      <c r="E623" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="F623" s="3">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="624" spans="1:6">
+      <c r="A624" t="s">
+        <v>9</v>
+      </c>
+      <c r="B624">
+        <v>2</v>
+      </c>
+      <c r="C624" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D624" s="2">
+        <v>27.65</v>
+      </c>
+      <c r="E624" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="F624" s="3">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="625" spans="1:6">
+      <c r="A625" t="s">
+        <v>9</v>
+      </c>
+      <c r="B625" t="s">
+        <v>10</v>
+      </c>
+      <c r="C625" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D625" s="2">
+        <v>27.41</v>
+      </c>
+      <c r="E625" s="2">
+        <v>9.12</v>
+      </c>
+      <c r="F625" s="3">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="626" spans="1:6">
+      <c r="A626" t="s">
+        <v>9</v>
+      </c>
+      <c r="B626">
+        <v>3</v>
+      </c>
+      <c r="C626" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D626" s="2">
+        <v>27.63</v>
+      </c>
+      <c r="E626" s="2">
+        <v>17.17</v>
+      </c>
+      <c r="F626" s="3">
+        <v>0.654</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6">
+      <c r="A627" t="s">
+        <v>9</v>
+      </c>
+      <c r="B627">
+        <v>4</v>
+      </c>
+      <c r="C627" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D627" s="2">
+        <v>28.49</v>
+      </c>
+      <c r="E627" s="2">
+        <v>8.62</v>
+      </c>
+      <c r="F627" s="3">
+        <v>1.122</v>
+      </c>
+    </row>
+    <row r="628" spans="1:6">
+      <c r="A628" t="s">
+        <v>9</v>
+      </c>
+      <c r="B628" t="s">
+        <v>11</v>
+      </c>
+      <c r="C628" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D628" s="2">
+        <v>28.49</v>
+      </c>
+      <c r="E628" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="F628" s="3">
+        <v>1.194</v>
+      </c>
+    </row>
+    <row r="629" spans="1:6">
+      <c r="A629" t="s">
+        <v>12</v>
+      </c>
+      <c r="B629">
+        <v>1</v>
+      </c>
+      <c r="C629" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D629" s="2">
+        <v>28.69</v>
+      </c>
+      <c r="E629" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="F629" s="3">
+        <v>1.542</v>
+      </c>
+    </row>
+    <row r="630" spans="1:6">
+      <c r="A630" t="s">
+        <v>12</v>
+      </c>
+      <c r="B630">
+        <v>2</v>
+      </c>
+      <c r="C630" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D630" s="2">
+        <v>31.64</v>
+      </c>
+      <c r="E630" s="2">
+        <v>33.81</v>
+      </c>
+      <c r="F630" s="3">
+        <v>2.424</v>
+      </c>
+    </row>
+    <row r="631" spans="1:6">
+      <c r="A631" t="s">
+        <v>12</v>
+      </c>
+      <c r="B631">
+        <v>3</v>
+      </c>
+      <c r="C631" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D631" s="2">
+        <v>30.83</v>
+      </c>
+      <c r="E631" s="2">
+        <v>2.33</v>
+      </c>
+      <c r="F631" s="3">
+        <v>2.511</v>
+      </c>
+    </row>
+    <row r="632" spans="1:6">
+      <c r="A632" t="s">
+        <v>12</v>
+      </c>
+      <c r="B632">
+        <v>4</v>
+      </c>
+      <c r="C632" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D632" s="2">
+        <v>29.37</v>
+      </c>
+      <c r="E632" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="F632" s="3">
+        <v>2.722</v>
+      </c>
+    </row>
+    <row r="633" spans="1:6">
+      <c r="A633" t="s">
+        <v>12</v>
+      </c>
+      <c r="B633">
+        <v>5</v>
+      </c>
+      <c r="C633" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D633" s="2">
+        <v>30.59</v>
+      </c>
+      <c r="E633" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="F633" s="3">
+        <v>3.154</v>
+      </c>
+    </row>
+    <row r="634" spans="1:6">
+      <c r="A634" t="s">
+        <v>9</v>
+      </c>
+      <c r="B634">
+        <v>1</v>
+      </c>
+      <c r="C634" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D634" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="E634" s="2">
+        <v>27.34</v>
+      </c>
+      <c r="F634" s="3">
+        <v>0.872</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6">
+      <c r="A635" t="s">
+        <v>9</v>
+      </c>
+      <c r="B635">
+        <v>2</v>
+      </c>
+      <c r="C635" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D635" s="2">
+        <v>2.16</v>
+      </c>
+      <c r="E635" s="2">
+        <v>27.62</v>
+      </c>
+      <c r="F635" s="3">
+        <v>2.644</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6">
+      <c r="A636" t="s">
+        <v>9</v>
+      </c>
+      <c r="B636" t="s">
+        <v>10</v>
+      </c>
+      <c r="C636" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D636" s="2">
+        <v>15.27</v>
+      </c>
+      <c r="E636" s="2">
+        <v>27.18</v>
+      </c>
+      <c r="F636" s="3">
+        <v>1.142</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6">
+      <c r="A637" t="s">
+        <v>9</v>
+      </c>
+      <c r="B637">
+        <v>3</v>
+      </c>
+      <c r="C637" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D637" s="2">
+        <v>17.66</v>
+      </c>
+      <c r="E637" s="2">
+        <v>27.22</v>
+      </c>
+      <c r="F637" s="3">
+        <v>0.623</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6">
+      <c r="A638" t="s">
+        <v>9</v>
+      </c>
+      <c r="B638">
+        <v>4</v>
+      </c>
+      <c r="C638" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D638" s="2">
+        <v>8.35</v>
+      </c>
+      <c r="E638" s="2">
+        <v>27.15</v>
+      </c>
+      <c r="F638" s="3">
+        <v>2.327</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6">
+      <c r="A639" t="s">
+        <v>9</v>
+      </c>
+      <c r="B639" t="s">
+        <v>11</v>
+      </c>
+      <c r="C639" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D639" s="2">
+        <v>1.42</v>
+      </c>
+      <c r="E639" s="2">
+        <v>27.42</v>
+      </c>
+      <c r="F639" s="3">
+        <v>2.432</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6">
+      <c r="A640" t="s">
+        <v>12</v>
+      </c>
+      <c r="B640">
+        <v>1</v>
+      </c>
+      <c r="C640" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D640" s="2">
+        <v>28.02</v>
+      </c>
+      <c r="E640" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F640" s="3">
+        <v>3.075</v>
+      </c>
+    </row>
+    <row r="641" spans="1:6">
+      <c r="A641" t="s">
+        <v>12</v>
+      </c>
+      <c r="B641">
+        <v>2</v>
+      </c>
+      <c r="C641" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D641" s="2">
+        <v>30.78</v>
+      </c>
+      <c r="E641" s="2">
+        <v>2.64</v>
+      </c>
+      <c r="F641" s="3">
+        <v>2.248</v>
+      </c>
+    </row>
+    <row r="642" spans="1:6">
+      <c r="A642" t="s">
+        <v>12</v>
+      </c>
+      <c r="B642">
+        <v>3</v>
+      </c>
+      <c r="C642" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D642" s="2">
+        <v>30.52</v>
+      </c>
+      <c r="E642" s="2">
+        <v>29.82</v>
+      </c>
+      <c r="F642" s="3">
+        <v>2.973</v>
+      </c>
+    </row>
+    <row r="643" spans="1:6">
+      <c r="A643" t="s">
+        <v>12</v>
+      </c>
+      <c r="B643">
+        <v>4</v>
+      </c>
+      <c r="C643" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D643" s="2">
+        <v>30.71</v>
+      </c>
+      <c r="E643" s="2">
+        <v>7.45</v>
+      </c>
+      <c r="F643" s="3">
+        <v>1.678</v>
+      </c>
+    </row>
+    <row r="644" spans="1:6">
+      <c r="A644" t="s">
+        <v>12</v>
+      </c>
+      <c r="B644">
+        <v>5</v>
+      </c>
+      <c r="C644" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D644" s="2">
+        <v>29.83</v>
+      </c>
+      <c r="E644" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="F644" s="3">
+        <v>2.397</v>
+      </c>
+    </row>
+    <row r="645" spans="1:6">
+      <c r="A645" t="s">
+        <v>9</v>
+      </c>
+      <c r="B645">
+        <v>1</v>
+      </c>
+      <c r="C645" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D645" s="2">
+        <v>28.05</v>
+      </c>
+      <c r="E645" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="F645" s="3">
+        <v>0.761</v>
+      </c>
+    </row>
+    <row r="646" spans="1:6">
+      <c r="A646" t="s">
+        <v>9</v>
+      </c>
+      <c r="B646">
+        <v>2</v>
+      </c>
+      <c r="C646" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D646" s="2">
+        <v>28.34</v>
+      </c>
+      <c r="E646" s="2">
+        <v>2.82</v>
+      </c>
+      <c r="F646" s="3">
+        <v>1.854</v>
+      </c>
+    </row>
+    <row r="647" spans="1:6">
+      <c r="A647" t="s">
+        <v>9</v>
+      </c>
+      <c r="B647" t="s">
+        <v>10</v>
+      </c>
+      <c r="C647" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D647" s="2">
+        <v>28.41</v>
+      </c>
+      <c r="E647" s="2">
+        <v>13.95</v>
+      </c>
+      <c r="F647" s="3">
+        <v>1.115</v>
+      </c>
+    </row>
+    <row r="648" spans="1:6">
+      <c r="A648" t="s">
+        <v>9</v>
+      </c>
+      <c r="B648">
+        <v>3</v>
+      </c>
+      <c r="C648" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D648" s="2">
+        <v>28.38</v>
+      </c>
+      <c r="E648" s="2">
+        <v>16.92</v>
+      </c>
+      <c r="F648" s="3">
+        <v>0.846</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6">
+      <c r="A649" t="s">
+        <v>9</v>
+      </c>
+      <c r="B649">
+        <v>4</v>
+      </c>
+      <c r="C649" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D649" s="2">
+        <v>28.29</v>
+      </c>
+      <c r="E649" s="2">
+        <v>4.52</v>
+      </c>
+      <c r="F649" s="3">
+        <v>1.967</v>
+      </c>
+    </row>
+    <row r="650" spans="1:6">
+      <c r="A650" t="s">
+        <v>9</v>
+      </c>
+      <c r="B650" t="s">
+        <v>11</v>
+      </c>
+      <c r="C650" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D650" s="2">
+        <v>28.22</v>
+      </c>
+      <c r="E650" s="2">
+        <v>3.18</v>
+      </c>
+      <c r="F650" s="3">
+        <v>2.443</v>
+      </c>
+    </row>
+    <row r="651" spans="1:6">
+      <c r="A651" t="s">
+        <v>12</v>
+      </c>
+      <c r="B651">
+        <v>1</v>
+      </c>
+      <c r="C651" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D651" s="2">
+        <v>28.21</v>
+      </c>
+      <c r="E651" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="F651" s="3">
+        <v>2.873</v>
+      </c>
+    </row>
+    <row r="652" spans="1:6">
+      <c r="A652" t="s">
+        <v>12</v>
+      </c>
+      <c r="B652">
+        <v>2</v>
+      </c>
+      <c r="C652" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D652" s="2">
+        <v>30.49</v>
+      </c>
+      <c r="E652" s="2">
+        <v>3.12</v>
+      </c>
+      <c r="F652" s="3">
+        <v>2.427</v>
+      </c>
+    </row>
+    <row r="653" spans="1:6">
+      <c r="A653" t="s">
+        <v>12</v>
+      </c>
+      <c r="B653">
+        <v>3</v>
+      </c>
+      <c r="C653" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D653" s="2">
+        <v>30.41</v>
+      </c>
+      <c r="E653" s="2">
+        <v>30.21</v>
+      </c>
+      <c r="F653" s="3">
+        <v>3.019</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6">
+      <c r="A654" t="s">
+        <v>12</v>
+      </c>
+      <c r="B654">
+        <v>4</v>
+      </c>
+      <c r="C654" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D654" s="2">
+        <v>30.59</v>
+      </c>
+      <c r="E654" s="2">
+        <v>8.26</v>
+      </c>
+      <c r="F654" s="3">
+        <v>1.782</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6">
+      <c r="A655" t="s">
+        <v>12</v>
+      </c>
+      <c r="B655">
+        <v>5</v>
+      </c>
+      <c r="C655" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D655" s="2">
+        <v>30.24</v>
+      </c>
+      <c r="E655" s="2">
+        <v>1.21</v>
+      </c>
+      <c r="F655" s="3">
+        <v>2.513</v>
+      </c>
+    </row>
+    <row r="656" spans="1:6">
+      <c r="A656" t="s">
+        <v>9</v>
+      </c>
+      <c r="B656">
+        <v>1</v>
+      </c>
+      <c r="C656" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D656" s="2">
+        <v>26.67</v>
+      </c>
+      <c r="E656" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="F656" s="3">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="657" spans="1:6">
+      <c r="A657" t="s">
+        <v>9</v>
+      </c>
+      <c r="B657">
+        <v>2</v>
+      </c>
+      <c r="C657" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D657" s="2">
+        <v>26.97</v>
+      </c>
+      <c r="E657" s="2">
+        <v>3.28</v>
+      </c>
+      <c r="F657" s="3">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="658" spans="1:6">
+      <c r="A658" t="s">
+        <v>9</v>
+      </c>
+      <c r="B658" t="s">
+        <v>10</v>
+      </c>
+      <c r="C658" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D658" s="2">
+        <v>26.36</v>
+      </c>
+      <c r="E658" s="2">
+        <v>6.37</v>
+      </c>
+      <c r="F658" s="3">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="659" spans="1:6">
+      <c r="A659" t="s">
+        <v>9</v>
+      </c>
+      <c r="B659">
+        <v>3</v>
+      </c>
+      <c r="C659" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D659" s="2">
+        <v>26.94</v>
+      </c>
+      <c r="E659" s="2">
+        <v>3.16</v>
+      </c>
+      <c r="F659" s="3">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="660" spans="1:6">
+      <c r="A660" t="s">
+        <v>9</v>
+      </c>
+      <c r="B660">
+        <v>4</v>
+      </c>
+      <c r="C660" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D660" s="2">
+        <v>26.43</v>
+      </c>
+      <c r="E660" s="2">
+        <v>5.21</v>
+      </c>
+      <c r="F660" s="3">
+        <v>0.301</v>
+      </c>
+    </row>
+    <row r="661" spans="1:6">
+      <c r="A661" t="s">
+        <v>9</v>
+      </c>
+      <c r="B661" t="s">
+        <v>11</v>
+      </c>
+      <c r="C661" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D661" s="2">
+        <v>26.42</v>
+      </c>
+      <c r="E661" s="2">
+        <v>4.67</v>
+      </c>
+      <c r="F661" s="3">
+        <v>0.247</v>
+      </c>
+    </row>
+    <row r="662" spans="1:6">
+      <c r="A662" t="s">
+        <v>12</v>
+      </c>
+      <c r="B662">
+        <v>1</v>
+      </c>
+      <c r="C662" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D662" s="2">
+        <v>30.24</v>
+      </c>
+      <c r="E662" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="F662" s="3">
+        <v>2.676</v>
+      </c>
+    </row>
+    <row r="663" spans="1:6">
+      <c r="A663" t="s">
+        <v>12</v>
+      </c>
+      <c r="B663">
+        <v>2</v>
+      </c>
+      <c r="C663" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D663" s="2">
+        <v>30.52</v>
+      </c>
+      <c r="E663" s="2">
+        <v>30.52</v>
+      </c>
+      <c r="F663" s="3">
+        <v>2.478</v>
+      </c>
+    </row>
+    <row r="664" spans="1:6">
+      <c r="A664" t="s">
+        <v>12</v>
+      </c>
+      <c r="B664">
+        <v>3</v>
+      </c>
+      <c r="C664" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D664" s="2">
+        <v>30.55</v>
+      </c>
+      <c r="E664" s="2">
+        <v>6.44</v>
+      </c>
+      <c r="F664" s="3">
+        <v>2.196</v>
+      </c>
+    </row>
+    <row r="665" spans="1:6">
+      <c r="A665" t="s">
+        <v>12</v>
+      </c>
+      <c r="B665">
+        <v>4</v>
+      </c>
+      <c r="C665" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D665" s="2">
+        <v>30.58</v>
+      </c>
+      <c r="E665" s="2">
+        <v>7.26</v>
+      </c>
+      <c r="F665" s="3">
+        <v>1.407</v>
+      </c>
+    </row>
+    <row r="666" spans="1:6">
+      <c r="A666" t="s">
+        <v>12</v>
+      </c>
+      <c r="B666">
+        <v>5</v>
+      </c>
+      <c r="C666" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D666" s="2">
+        <v>30.43</v>
+      </c>
+      <c r="E666" s="2">
+        <v>42.35</v>
+      </c>
+      <c r="F666" s="3">
+        <v>1.335</v>
+      </c>
+    </row>
+    <row r="667" spans="1:6">
+      <c r="A667" t="s">
+        <v>9</v>
+      </c>
+      <c r="B667">
+        <v>1</v>
+      </c>
+      <c r="C667" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D667" s="2">
+        <v>26.13</v>
+      </c>
+      <c r="E667" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="F667" s="3">
+        <v>0.641</v>
+      </c>
+    </row>
+    <row r="668" spans="1:6">
+      <c r="A668" t="s">
+        <v>9</v>
+      </c>
+      <c r="B668">
+        <v>2</v>
+      </c>
+      <c r="C668" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D668" s="2">
+        <v>26.07</v>
+      </c>
+      <c r="E668" s="2">
+        <v>1.87</v>
+      </c>
+      <c r="F668" s="3">
+        <v>2.699</v>
+      </c>
+    </row>
+    <row r="669" spans="1:6">
+      <c r="A669" t="s">
+        <v>9</v>
+      </c>
+      <c r="B669" t="s">
+        <v>10</v>
+      </c>
+      <c r="C669" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D669" s="2">
+        <v>26.67</v>
+      </c>
+      <c r="E669" s="2">
+        <v>15.24</v>
+      </c>
+      <c r="F669" s="3">
+        <v>0.145</v>
+      </c>
+    </row>
+    <row r="670" spans="1:6">
+      <c r="A670" t="s">
+        <v>9</v>
+      </c>
+      <c r="B670">
+        <v>3</v>
+      </c>
+      <c r="C670" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D670" s="2">
+        <v>26.4</v>
+      </c>
+      <c r="E670" s="2">
+        <v>14.32</v>
+      </c>
+      <c r="F670" s="3">
+        <v>0.437</v>
+      </c>
+    </row>
+    <row r="671" spans="1:6">
+      <c r="A671" t="s">
+        <v>9</v>
+      </c>
+      <c r="B671">
+        <v>4</v>
+      </c>
+      <c r="C671" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D671" s="2">
+        <v>26.56</v>
+      </c>
+      <c r="E671" s="2">
+        <v>6.98</v>
+      </c>
+      <c r="F671" s="3">
+        <v>2.672</v>
+      </c>
+    </row>
+    <row r="672" spans="1:6">
+      <c r="A672" t="s">
+        <v>9</v>
+      </c>
+      <c r="B672" t="s">
+        <v>11</v>
+      </c>
+      <c r="C672" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D672" s="2">
+        <v>26.49</v>
+      </c>
+      <c r="E672" s="2">
+        <v>1.24</v>
+      </c>
+      <c r="F672" s="3">
+        <v>2.435</v>
+      </c>
+    </row>
+    <row r="673" spans="1:6">
+      <c r="A673" t="s">
+        <v>12</v>
+      </c>
+      <c r="B673">
+        <v>1</v>
+      </c>
+      <c r="C673" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D673" s="2">
+        <v>30.69</v>
+      </c>
+      <c r="E673" s="2">
+        <v>0.42</v>
+      </c>
+      <c r="F673" s="3">
+        <v>1.049</v>
+      </c>
+    </row>
+    <row r="674" spans="1:6">
+      <c r="A674" t="s">
+        <v>12</v>
+      </c>
+      <c r="B674">
+        <v>2</v>
+      </c>
+      <c r="C674" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D674" s="2">
+        <v>30.57</v>
+      </c>
+      <c r="E674" s="2">
+        <v>5.17</v>
+      </c>
+      <c r="F674" s="3">
+        <v>1.419</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6">
+      <c r="A675" t="s">
+        <v>12</v>
+      </c>
+      <c r="B675">
+        <v>3</v>
+      </c>
+      <c r="C675" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D675" s="2">
+        <v>30.43</v>
+      </c>
+      <c r="E675" s="2">
+        <v>28.29</v>
+      </c>
+      <c r="F675" s="3">
+        <v>1.468</v>
+      </c>
+    </row>
+    <row r="676" spans="1:6">
+      <c r="A676" t="s">
+        <v>12</v>
+      </c>
+      <c r="B676">
+        <v>4</v>
+      </c>
+      <c r="C676" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D676" s="2">
+        <v>30.62</v>
+      </c>
+      <c r="E676" s="2">
+        <v>11.31</v>
+      </c>
+      <c r="F676" s="3">
+        <v>1.044</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6">
+      <c r="A677" t="s">
+        <v>12</v>
+      </c>
+      <c r="B677">
+        <v>5</v>
+      </c>
+      <c r="C677" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D677" s="2">
+        <v>30.67</v>
+      </c>
+      <c r="E677" s="2">
+        <v>32.43</v>
+      </c>
+      <c r="F677" s="3">
+        <v>1.059</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6">
+      <c r="A678" t="s">
+        <v>12</v>
+      </c>
+      <c r="B678">
+        <v>1</v>
+      </c>
+      <c r="C678" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D678" s="2">
+        <v>29.42</v>
+      </c>
+      <c r="E678" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="F678" s="3">
+        <v>1.676</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6">
+      <c r="A679" t="s">
+        <v>12</v>
+      </c>
+      <c r="B679">
+        <v>2</v>
+      </c>
+      <c r="C679" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D679" s="2">
+        <v>29.54</v>
+      </c>
+      <c r="E679" s="2">
+        <v>20.62</v>
+      </c>
+      <c r="F679" s="3">
+        <v>0.878</v>
+      </c>
+    </row>
+    <row r="680" spans="1:6">
+      <c r="A680" t="s">
+        <v>12</v>
+      </c>
+      <c r="B680">
+        <v>3</v>
+      </c>
+      <c r="C680" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D680" s="2">
+        <v>29.33</v>
+      </c>
+      <c r="E680" s="2">
+        <v>3.95</v>
+      </c>
+      <c r="F680" s="3">
+        <v>2.196</v>
+      </c>
+    </row>
+    <row r="681" spans="1:6">
+      <c r="A681" t="s">
+        <v>12</v>
+      </c>
+      <c r="B681">
+        <v>4</v>
+      </c>
+      <c r="C681" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D681" s="2">
+        <v>29.42</v>
+      </c>
+      <c r="E681" s="2">
+        <v>1.26</v>
+      </c>
+      <c r="F681" s="3">
+        <v>0.407</v>
+      </c>
+    </row>
+    <row r="682" spans="1:6">
+      <c r="A682" t="s">
+        <v>12</v>
+      </c>
+      <c r="B682">
+        <v>5</v>
+      </c>
+      <c r="C682" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D682" s="2">
+        <v>29.51</v>
+      </c>
+      <c r="E682" s="2">
+        <v>2.54</v>
+      </c>
+      <c r="F682" s="3">
+        <v>2.335</v>
+      </c>
+    </row>
+    <row r="683" spans="1:6">
+      <c r="A683" t="s">
+        <v>12</v>
+      </c>
+      <c r="B683">
+        <v>1</v>
+      </c>
+      <c r="C683" s="1">
+        <v>46203</v>
+      </c>
+      <c r="D683" s="2">
+        <v>44.45</v>
+      </c>
+      <c r="E683" s="2">
+        <v>0</v>
+      </c>
+      <c r="F683" s="3">
+        <v>0.387</v>
+      </c>
+    </row>
+    <row r="684" spans="1:6">
+      <c r="A684" t="s">
+        <v>12</v>
+      </c>
+      <c r="B684">
+        <v>2</v>
+      </c>
+      <c r="C684" s="1">
+        <v>46203</v>
+      </c>
+      <c r="D684" s="2">
+        <v>44.49</v>
+      </c>
+      <c r="E684" s="2">
+        <v>14.49</v>
+      </c>
+      <c r="F684" s="3">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="685" spans="1:6">
+      <c r="A685" t="s">
+        <v>12</v>
+      </c>
+      <c r="B685">
+        <v>3</v>
+      </c>
+      <c r="C685" s="1">
+        <v>46203</v>
+      </c>
+      <c r="D685" s="2">
+        <v>44.38</v>
+      </c>
+      <c r="E685" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F685" s="3">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="686" spans="1:6">
+      <c r="A686" t="s">
+        <v>12</v>
+      </c>
+      <c r="B686">
+        <v>4</v>
+      </c>
+      <c r="C686" s="1">
+        <v>46203</v>
+      </c>
+      <c r="D686" s="2">
+        <v>44.4</v>
+      </c>
+      <c r="E686" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="F686" s="3">
+        <v>0.546</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6">
+      <c r="A687" t="s">
+        <v>12</v>
+      </c>
+      <c r="B687">
+        <v>5</v>
+      </c>
+      <c r="C687" s="1">
+        <v>46203</v>
+      </c>
+      <c r="D687" s="2">
+        <v>44.52</v>
+      </c>
+      <c r="E687" s="2">
+        <v>25.17</v>
+      </c>
+      <c r="F687" s="3">
+        <v>0.706</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6">
+      <c r="A688" t="s">
+        <v>12</v>
+      </c>
+      <c r="B688">
+        <v>1</v>
+      </c>
+      <c r="C688" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D688" s="2">
+        <v>41.76</v>
+      </c>
+      <c r="E688" s="2">
+        <v>0.44</v>
+      </c>
+      <c r="F688" s="3">
+        <v>0.523</v>
+      </c>
+    </row>
+    <row r="689" spans="1:6">
+      <c r="A689" t="s">
+        <v>12</v>
+      </c>
+      <c r="B689">
+        <v>2</v>
+      </c>
+      <c r="C689" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D689" s="2">
+        <v>41.81</v>
+      </c>
+      <c r="E689" s="2">
+        <v>20.2</v>
+      </c>
+      <c r="F689" s="3">
+        <v>2.143</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6">
+      <c r="A690" t="s">
+        <v>12</v>
+      </c>
+      <c r="B690">
+        <v>3</v>
+      </c>
+      <c r="C690" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D690" s="2">
+        <v>41.78</v>
+      </c>
+      <c r="E690" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="F690" s="3">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6">
+      <c r="A691" t="s">
+        <v>12</v>
+      </c>
+      <c r="B691">
+        <v>4</v>
+      </c>
+      <c r="C691" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D691" s="2">
+        <v>41.86</v>
+      </c>
+      <c r="E691" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="F691" s="3">
+        <v>1.279</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6">
+      <c r="A692" t="s">
+        <v>12</v>
+      </c>
+      <c r="B692">
+        <v>5</v>
+      </c>
+      <c r="C692" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D692" s="2">
+        <v>41.84</v>
+      </c>
+      <c r="E692" s="2">
+        <v>28.6</v>
+      </c>
+      <c r="F692" s="3">
+        <v>1.163</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6">
+      <c r="A693" t="s">
+        <v>12</v>
+      </c>
+      <c r="B693">
+        <v>1</v>
+      </c>
+      <c r="C693" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D693" s="2">
+        <v>41.4</v>
+      </c>
+      <c r="E693" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="F693" s="3">
+        <v>0.527</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6">
+      <c r="A694" t="s">
+        <v>12</v>
+      </c>
+      <c r="B694">
+        <v>2</v>
+      </c>
+      <c r="C694" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D694" s="2">
+        <v>41.48</v>
+      </c>
+      <c r="E694" s="2">
+        <v>30.17</v>
+      </c>
+      <c r="F694" s="3">
+        <v>1.624</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6">
+      <c r="A695" t="s">
+        <v>12</v>
+      </c>
+      <c r="B695">
+        <v>3</v>
+      </c>
+      <c r="C695" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D695" s="2">
+        <v>41.46</v>
+      </c>
+      <c r="E695" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="F695" s="3">
+        <v>2.371</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6">
+      <c r="A696" t="s">
+        <v>12</v>
+      </c>
+      <c r="B696">
+        <v>4</v>
+      </c>
+      <c r="C696" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D696" s="2">
+        <v>41.53</v>
+      </c>
+      <c r="E696" s="2">
+        <v>4.21</v>
+      </c>
+      <c r="F696" s="3">
+        <v>0.521</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6">
+      <c r="A697" t="s">
+        <v>12</v>
+      </c>
+      <c r="B697">
+        <v>5</v>
+      </c>
+      <c r="C697" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D697" s="2">
+        <v>41.55</v>
+      </c>
+      <c r="E697" s="2">
+        <v>26.46</v>
+      </c>
+      <c r="F697" s="3">
+        <v>1.079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12960" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F697"/>
+  <dimension ref="A1:F707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -15623,6 +15623,206 @@
         <v>1.079</v>
       </c>
     </row>
+    <row r="698" spans="1:6">
+      <c r="A698" t="s">
+        <v>12</v>
+      </c>
+      <c r="B698">
+        <v>1</v>
+      </c>
+      <c r="C698" s="1">
+        <v>46207</v>
+      </c>
+      <c r="D698" s="2">
+        <v>38.3</v>
+      </c>
+      <c r="E698" s="2">
+        <v>0.14</v>
+      </c>
+      <c r="F698" s="3">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6">
+      <c r="A699" t="s">
+        <v>12</v>
+      </c>
+      <c r="B699">
+        <v>2</v>
+      </c>
+      <c r="C699" s="1">
+        <v>46207</v>
+      </c>
+      <c r="D699" s="2">
+        <v>42.99</v>
+      </c>
+      <c r="E699" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="F699" s="3">
+        <v>0.402</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6">
+      <c r="A700" t="s">
+        <v>12</v>
+      </c>
+      <c r="B700">
+        <v>3</v>
+      </c>
+      <c r="C700" s="1">
+        <v>46207</v>
+      </c>
+      <c r="D700" s="2">
+        <v>41.91</v>
+      </c>
+      <c r="E700" s="2">
+        <v>1.29</v>
+      </c>
+      <c r="F700" s="3">
+        <v>0.467</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6">
+      <c r="A701" t="s">
+        <v>12</v>
+      </c>
+      <c r="B701">
+        <v>4</v>
+      </c>
+      <c r="C701" s="1">
+        <v>46207</v>
+      </c>
+      <c r="D701" s="2">
+        <v>41.44</v>
+      </c>
+      <c r="E701" s="2">
+        <v>2.38</v>
+      </c>
+      <c r="F701" s="3">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6">
+      <c r="A702" t="s">
+        <v>12</v>
+      </c>
+      <c r="B702">
+        <v>5</v>
+      </c>
+      <c r="C702" s="1">
+        <v>46207</v>
+      </c>
+      <c r="D702" s="2">
+        <v>42.99</v>
+      </c>
+      <c r="E702" s="2">
+        <v>20.2</v>
+      </c>
+      <c r="F702" s="3">
+        <v>0.479</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6">
+      <c r="A703" t="s">
+        <v>12</v>
+      </c>
+      <c r="B703">
+        <v>1</v>
+      </c>
+      <c r="C703" s="1">
+        <v>46208</v>
+      </c>
+      <c r="D703" s="2">
+        <v>42.9</v>
+      </c>
+      <c r="E703" s="2">
+        <v>0</v>
+      </c>
+      <c r="F703" s="3">
+        <v>1.997</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6">
+      <c r="A704" t="s">
+        <v>12</v>
+      </c>
+      <c r="B704">
+        <v>2</v>
+      </c>
+      <c r="C704" s="1">
+        <v>46208</v>
+      </c>
+      <c r="D704" s="2">
+        <v>42.91</v>
+      </c>
+      <c r="E704" s="2">
+        <v>14.93</v>
+      </c>
+      <c r="F704" s="3">
+        <v>1.882</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6">
+      <c r="A705" t="s">
+        <v>12</v>
+      </c>
+      <c r="B705">
+        <v>3</v>
+      </c>
+      <c r="C705" s="1">
+        <v>46208</v>
+      </c>
+      <c r="D705" s="2">
+        <v>42.94</v>
+      </c>
+      <c r="E705" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="F705" s="3">
+        <v>1.903</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6">
+      <c r="A706" t="s">
+        <v>12</v>
+      </c>
+      <c r="B706">
+        <v>4</v>
+      </c>
+      <c r="C706" s="1">
+        <v>46208</v>
+      </c>
+      <c r="D706" s="2">
+        <v>43.01</v>
+      </c>
+      <c r="E706" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="F706" s="3">
+        <v>1.479</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6">
+      <c r="A707" t="s">
+        <v>12</v>
+      </c>
+      <c r="B707">
+        <v>5</v>
+      </c>
+      <c r="C707" s="1">
+        <v>46208</v>
+      </c>
+      <c r="D707" s="2">
+        <v>42.84</v>
+      </c>
+      <c r="E707" s="2">
+        <v>29.52</v>
+      </c>
+      <c r="F707" s="3">
+        <v>1.966</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960" activeTab="1"/>
+    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F707"/>
+  <dimension ref="A1:F712"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -15823,6 +15823,106 @@
         <v>1.966</v>
       </c>
     </row>
+    <row r="708" spans="1:6">
+      <c r="A708" t="s">
+        <v>12</v>
+      </c>
+      <c r="B708">
+        <v>1</v>
+      </c>
+      <c r="C708" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D708" s="2">
+        <v>40.9</v>
+      </c>
+      <c r="E708" s="2">
+        <v>0</v>
+      </c>
+      <c r="F708" s="3">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="709" spans="1:6">
+      <c r="A709" t="s">
+        <v>12</v>
+      </c>
+      <c r="B709">
+        <v>2</v>
+      </c>
+      <c r="C709" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D709" s="2">
+        <v>42.76</v>
+      </c>
+      <c r="E709" s="2">
+        <v>17.16</v>
+      </c>
+      <c r="F709" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6">
+      <c r="A710" t="s">
+        <v>12</v>
+      </c>
+      <c r="B710">
+        <v>3</v>
+      </c>
+      <c r="C710" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D710" s="2">
+        <v>42.57</v>
+      </c>
+      <c r="E710" s="2">
+        <v>1.48</v>
+      </c>
+      <c r="F710" s="3">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6">
+      <c r="A711" t="s">
+        <v>12</v>
+      </c>
+      <c r="B711">
+        <v>4</v>
+      </c>
+      <c r="C711" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D711" s="2">
+        <v>42.55</v>
+      </c>
+      <c r="E711" s="2">
+        <v>3.77</v>
+      </c>
+      <c r="F711" s="3">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6">
+      <c r="A712" t="s">
+        <v>12</v>
+      </c>
+      <c r="B712">
+        <v>5</v>
+      </c>
+      <c r="C712" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D712" s="2">
+        <v>42.84</v>
+      </c>
+      <c r="E712" s="2">
+        <v>25.3</v>
+      </c>
+      <c r="F712" s="3">
+        <v>1.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F712"/>
+  <dimension ref="A1:F717"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -15923,6 +15923,106 @@
         <v>1.72</v>
       </c>
     </row>
+    <row r="713" spans="1:6">
+      <c r="A713" t="s">
+        <v>12</v>
+      </c>
+      <c r="B713">
+        <v>1</v>
+      </c>
+      <c r="C713" s="1">
+        <v>46211</v>
+      </c>
+      <c r="D713" s="2">
+        <v>48.41</v>
+      </c>
+      <c r="E713" s="2">
+        <v>0</v>
+      </c>
+      <c r="F713" s="3">
+        <v>0.816</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6">
+      <c r="A714" t="s">
+        <v>12</v>
+      </c>
+      <c r="B714">
+        <v>2</v>
+      </c>
+      <c r="C714" s="1">
+        <v>46211</v>
+      </c>
+      <c r="D714" s="2">
+        <v>48.77</v>
+      </c>
+      <c r="E714" s="2">
+        <v>13.24</v>
+      </c>
+      <c r="F714" s="3">
+        <v>0.899</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6">
+      <c r="A715" t="s">
+        <v>12</v>
+      </c>
+      <c r="B715">
+        <v>3</v>
+      </c>
+      <c r="C715" s="1">
+        <v>46211</v>
+      </c>
+      <c r="D715" s="2">
+        <v>47.77</v>
+      </c>
+      <c r="E715" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="F715" s="3">
+        <v>0.979</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6">
+      <c r="A716" t="s">
+        <v>12</v>
+      </c>
+      <c r="B716">
+        <v>4</v>
+      </c>
+      <c r="C716" s="1">
+        <v>46211</v>
+      </c>
+      <c r="D716" s="2">
+        <v>47.75</v>
+      </c>
+      <c r="E716" s="2">
+        <v>4.4</v>
+      </c>
+      <c r="F716" s="3">
+        <v>0.628</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6">
+      <c r="A717" t="s">
+        <v>12</v>
+      </c>
+      <c r="B717">
+        <v>5</v>
+      </c>
+      <c r="C717" s="1">
+        <v>46211</v>
+      </c>
+      <c r="D717" s="2">
+        <v>48.23</v>
+      </c>
+      <c r="E717" s="2">
+        <v>22.87</v>
+      </c>
+      <c r="F717" s="3">
+        <v>0.948</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -697,7 +697,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -708,6 +708,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1677,7 +1680,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F717"/>
+  <dimension ref="A1:F727"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -16023,6 +16026,206 @@
         <v>0.948</v>
       </c>
     </row>
+    <row r="718" spans="1:6">
+      <c r="A718" t="s">
+        <v>12</v>
+      </c>
+      <c r="B718">
+        <v>1</v>
+      </c>
+      <c r="C718" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D718" s="2">
+        <v>48.41</v>
+      </c>
+      <c r="E718" s="2">
+        <v>0</v>
+      </c>
+      <c r="F718" s="3">
+        <v>0.816</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6">
+      <c r="A719" t="s">
+        <v>12</v>
+      </c>
+      <c r="B719">
+        <v>2</v>
+      </c>
+      <c r="C719" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D719" s="2">
+        <v>48.77</v>
+      </c>
+      <c r="E719" s="2">
+        <v>13.24</v>
+      </c>
+      <c r="F719" s="3">
+        <v>0.899</v>
+      </c>
+    </row>
+    <row r="720" spans="1:6">
+      <c r="A720" t="s">
+        <v>12</v>
+      </c>
+      <c r="B720">
+        <v>3</v>
+      </c>
+      <c r="C720" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D720" s="2">
+        <v>47.77</v>
+      </c>
+      <c r="E720" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="F720" s="3">
+        <v>0.979</v>
+      </c>
+    </row>
+    <row r="721" spans="1:6">
+      <c r="A721" t="s">
+        <v>12</v>
+      </c>
+      <c r="B721">
+        <v>4</v>
+      </c>
+      <c r="C721" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D721" s="2">
+        <v>47.75</v>
+      </c>
+      <c r="E721" s="2">
+        <v>4.4</v>
+      </c>
+      <c r="F721" s="3">
+        <v>0.628</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6">
+      <c r="A722" t="s">
+        <v>12</v>
+      </c>
+      <c r="B722">
+        <v>5</v>
+      </c>
+      <c r="C722" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D722" s="2">
+        <v>48.23</v>
+      </c>
+      <c r="E722" s="2">
+        <v>22.87</v>
+      </c>
+      <c r="F722" s="3">
+        <v>0.948</v>
+      </c>
+    </row>
+    <row r="723" spans="1:6">
+      <c r="A723" t="s">
+        <v>12</v>
+      </c>
+      <c r="B723">
+        <v>1</v>
+      </c>
+      <c r="C723" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D723" s="2">
+        <v>43.04</v>
+      </c>
+      <c r="E723" s="4">
+        <v>0</v>
+      </c>
+      <c r="F723" s="3">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="724" spans="1:6">
+      <c r="A724" t="s">
+        <v>12</v>
+      </c>
+      <c r="B724">
+        <v>2</v>
+      </c>
+      <c r="C724" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D724" s="2">
+        <v>42.68</v>
+      </c>
+      <c r="E724" s="4">
+        <v>18.69</v>
+      </c>
+      <c r="F724" s="3">
+        <v>0.826</v>
+      </c>
+    </row>
+    <row r="725" spans="1:6">
+      <c r="A725" t="s">
+        <v>12</v>
+      </c>
+      <c r="B725">
+        <v>3</v>
+      </c>
+      <c r="C725" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D725" s="2">
+        <v>42.8</v>
+      </c>
+      <c r="E725" s="4">
+        <v>2.68</v>
+      </c>
+      <c r="F725" s="3">
+        <v>0.851</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6">
+      <c r="A726" t="s">
+        <v>12</v>
+      </c>
+      <c r="B726">
+        <v>4</v>
+      </c>
+      <c r="C726" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D726" s="2">
+        <v>42.48</v>
+      </c>
+      <c r="E726" s="4">
+        <v>0</v>
+      </c>
+      <c r="F726" s="3">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="727" spans="1:6">
+      <c r="A727" t="s">
+        <v>12</v>
+      </c>
+      <c r="B727">
+        <v>5</v>
+      </c>
+      <c r="C727" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D727" s="2">
+        <v>42.81</v>
+      </c>
+      <c r="E727" s="4">
+        <v>36.8</v>
+      </c>
+      <c r="F727" s="3">
+        <v>1.023</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -697,7 +697,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -708,9 +708,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1680,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F727"/>
+  <dimension ref="A1:F732"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -16134,12 +16131,12 @@
         <v>1</v>
       </c>
       <c r="C723" s="1">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="D723" s="2">
         <v>43.04</v>
       </c>
-      <c r="E723" s="4">
+      <c r="E723" s="2">
         <v>0</v>
       </c>
       <c r="F723" s="3">
@@ -16154,12 +16151,12 @@
         <v>2</v>
       </c>
       <c r="C724" s="1">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="D724" s="2">
         <v>42.68</v>
       </c>
-      <c r="E724" s="4">
+      <c r="E724" s="2">
         <v>18.69</v>
       </c>
       <c r="F724" s="3">
@@ -16174,12 +16171,12 @@
         <v>3</v>
       </c>
       <c r="C725" s="1">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="D725" s="2">
         <v>42.8</v>
       </c>
-      <c r="E725" s="4">
+      <c r="E725" s="2">
         <v>2.68</v>
       </c>
       <c r="F725" s="3">
@@ -16194,12 +16191,12 @@
         <v>4</v>
       </c>
       <c r="C726" s="1">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="D726" s="2">
         <v>42.48</v>
       </c>
-      <c r="E726" s="4">
+      <c r="E726" s="2">
         <v>0</v>
       </c>
       <c r="F726" s="3">
@@ -16214,16 +16211,116 @@
         <v>5</v>
       </c>
       <c r="C727" s="1">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="D727" s="2">
         <v>42.81</v>
       </c>
-      <c r="E727" s="4">
+      <c r="E727" s="2">
         <v>36.8</v>
       </c>
       <c r="F727" s="3">
         <v>1.023</v>
+      </c>
+    </row>
+    <row r="728" spans="1:6">
+      <c r="A728" t="s">
+        <v>12</v>
+      </c>
+      <c r="B728">
+        <v>1</v>
+      </c>
+      <c r="C728" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D728" s="2">
+        <v>35.06</v>
+      </c>
+      <c r="E728" s="2">
+        <v>0</v>
+      </c>
+      <c r="F728" s="3">
+        <v>1.232</v>
+      </c>
+    </row>
+    <row r="729" spans="1:6">
+      <c r="A729" t="s">
+        <v>12</v>
+      </c>
+      <c r="B729">
+        <v>2</v>
+      </c>
+      <c r="C729" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D729" s="2">
+        <v>35.14</v>
+      </c>
+      <c r="E729" s="2">
+        <v>10.74</v>
+      </c>
+      <c r="F729" s="3">
+        <v>1.717</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6">
+      <c r="A730" t="s">
+        <v>12</v>
+      </c>
+      <c r="B730">
+        <v>3</v>
+      </c>
+      <c r="C730" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D730" s="2">
+        <v>35.1</v>
+      </c>
+      <c r="E730" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="F730" s="3">
+        <v>1.649</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6">
+      <c r="A731" t="s">
+        <v>12</v>
+      </c>
+      <c r="B731">
+        <v>4</v>
+      </c>
+      <c r="C731" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D731" s="2">
+        <v>35.18</v>
+      </c>
+      <c r="E731" s="2">
+        <v>2.72</v>
+      </c>
+      <c r="F731" s="3">
+        <v>1.401</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6">
+      <c r="A732" t="s">
+        <v>12</v>
+      </c>
+      <c r="B732">
+        <v>5</v>
+      </c>
+      <c r="C732" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D732" s="2">
+        <v>35.05</v>
+      </c>
+      <c r="E732" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="F732" s="3">
+        <v>1.715</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,10 +1677,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F732"/>
+  <dimension ref="A1:F742"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
+    <col min="6" max="6" width="9.375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16321,6 +16322,206 @@
       </c>
       <c r="F732" s="3">
         <v>1.715</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6">
+      <c r="A733" t="s">
+        <v>12</v>
+      </c>
+      <c r="B733">
+        <v>1</v>
+      </c>
+      <c r="C733" s="1">
+        <v>46217</v>
+      </c>
+      <c r="D733" s="2">
+        <v>35.12</v>
+      </c>
+      <c r="E733" s="2">
+        <v>0</v>
+      </c>
+      <c r="F733" s="3">
+        <v>1.227</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6">
+      <c r="A734" t="s">
+        <v>12</v>
+      </c>
+      <c r="B734">
+        <v>2</v>
+      </c>
+      <c r="C734" s="1">
+        <v>46217</v>
+      </c>
+      <c r="D734" s="2">
+        <v>35.16</v>
+      </c>
+      <c r="E734" s="2">
+        <v>14.81</v>
+      </c>
+      <c r="F734" s="3">
+        <v>1.673</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6">
+      <c r="A735" t="s">
+        <v>12</v>
+      </c>
+      <c r="B735">
+        <v>3</v>
+      </c>
+      <c r="C735" s="1">
+        <v>46217</v>
+      </c>
+      <c r="D735" s="2">
+        <v>35.08</v>
+      </c>
+      <c r="E735" s="2">
+        <v>6.12</v>
+      </c>
+      <c r="F735" s="3">
+        <v>1.487</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6">
+      <c r="A736" t="s">
+        <v>12</v>
+      </c>
+      <c r="B736">
+        <v>4</v>
+      </c>
+      <c r="C736" s="1">
+        <v>46217</v>
+      </c>
+      <c r="D736" s="2">
+        <v>35.12</v>
+      </c>
+      <c r="E736" s="2">
+        <v>1.63</v>
+      </c>
+      <c r="F736" s="3">
+        <v>1.323</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6">
+      <c r="A737" t="s">
+        <v>12</v>
+      </c>
+      <c r="B737">
+        <v>5</v>
+      </c>
+      <c r="C737" s="1">
+        <v>46217</v>
+      </c>
+      <c r="D737" s="2">
+        <v>35.06</v>
+      </c>
+      <c r="E737" s="2">
+        <v>13.7</v>
+      </c>
+      <c r="F737" s="3">
+        <v>1.582</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6">
+      <c r="A738" t="s">
+        <v>12</v>
+      </c>
+      <c r="B738">
+        <v>1</v>
+      </c>
+      <c r="C738" s="1">
+        <v>46218</v>
+      </c>
+      <c r="D738" s="2">
+        <v>35.32</v>
+      </c>
+      <c r="E738" s="2">
+        <v>0</v>
+      </c>
+      <c r="F738" s="3">
+        <v>1.317</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6">
+      <c r="A739" t="s">
+        <v>12</v>
+      </c>
+      <c r="B739">
+        <v>2</v>
+      </c>
+      <c r="C739" s="1">
+        <v>46218</v>
+      </c>
+      <c r="D739" s="2">
+        <v>35.24</v>
+      </c>
+      <c r="E739" s="2">
+        <v>16.37</v>
+      </c>
+      <c r="F739" s="3">
+        <v>1.726</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6">
+      <c r="A740" t="s">
+        <v>12</v>
+      </c>
+      <c r="B740">
+        <v>3</v>
+      </c>
+      <c r="C740" s="1">
+        <v>46218</v>
+      </c>
+      <c r="D740" s="2">
+        <v>35.27</v>
+      </c>
+      <c r="E740" s="2">
+        <v>5.24</v>
+      </c>
+      <c r="F740" s="3">
+        <v>1.387</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6">
+      <c r="A741" t="s">
+        <v>12</v>
+      </c>
+      <c r="B741">
+        <v>4</v>
+      </c>
+      <c r="C741" s="1">
+        <v>46218</v>
+      </c>
+      <c r="D741" s="2">
+        <v>34.18</v>
+      </c>
+      <c r="E741" s="2">
+        <v>2.74</v>
+      </c>
+      <c r="F741" s="3">
+        <v>1.421</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6">
+      <c r="A742" t="s">
+        <v>12</v>
+      </c>
+      <c r="B742">
+        <v>5</v>
+      </c>
+      <c r="C742" s="1">
+        <v>46218</v>
+      </c>
+      <c r="D742" s="2">
+        <v>35.36</v>
+      </c>
+      <c r="E742" s="2">
+        <v>17.03</v>
+      </c>
+      <c r="F742" s="3">
+        <v>1.665</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="17">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1677,7 +1677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F742"/>
+  <dimension ref="A1:F762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -16524,6 +16524,406 @@
         <v>1.665</v>
       </c>
     </row>
+    <row r="743" spans="1:6">
+      <c r="A743" t="s">
+        <v>12</v>
+      </c>
+      <c r="B743">
+        <v>1</v>
+      </c>
+      <c r="C743" s="1">
+        <v>46220</v>
+      </c>
+      <c r="D743" s="2">
+        <v>33.19</v>
+      </c>
+      <c r="E743" s="2">
+        <v>0.69</v>
+      </c>
+      <c r="F743" s="3">
+        <v>0.293</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6">
+      <c r="A744" t="s">
+        <v>12</v>
+      </c>
+      <c r="B744">
+        <v>2</v>
+      </c>
+      <c r="C744" s="1">
+        <v>46220</v>
+      </c>
+      <c r="D744" s="2">
+        <v>33.38</v>
+      </c>
+      <c r="E744" s="2">
+        <v>14.34</v>
+      </c>
+      <c r="F744" s="3">
+        <v>0.684</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6">
+      <c r="A745" t="s">
+        <v>12</v>
+      </c>
+      <c r="B745">
+        <v>3</v>
+      </c>
+      <c r="C745" s="1">
+        <v>46220</v>
+      </c>
+      <c r="D745" s="2">
+        <v>33.35</v>
+      </c>
+      <c r="E745" s="2">
+        <v>9.89</v>
+      </c>
+      <c r="F745" s="3">
+        <v>0.669</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6">
+      <c r="A746" t="s">
+        <v>12</v>
+      </c>
+      <c r="B746">
+        <v>4</v>
+      </c>
+      <c r="C746" s="1">
+        <v>46220</v>
+      </c>
+      <c r="D746" s="2">
+        <v>33.32</v>
+      </c>
+      <c r="E746" s="2">
+        <v>0</v>
+      </c>
+      <c r="F746" s="3">
+        <v>0.56</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6">
+      <c r="A747" t="s">
+        <v>12</v>
+      </c>
+      <c r="B747">
+        <v>5</v>
+      </c>
+      <c r="C747" s="1">
+        <v>46220</v>
+      </c>
+      <c r="D747" s="2">
+        <v>33.35</v>
+      </c>
+      <c r="E747" s="2">
+        <v>13.71</v>
+      </c>
+      <c r="F747" s="3">
+        <v>0.789</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6">
+      <c r="A748" t="s">
+        <v>12</v>
+      </c>
+      <c r="B748">
+        <v>1</v>
+      </c>
+      <c r="C748" s="1">
+        <v>46221</v>
+      </c>
+      <c r="D748" s="2">
+        <v>32.83</v>
+      </c>
+      <c r="E748" s="2">
+        <v>0</v>
+      </c>
+      <c r="F748" s="3">
+        <v>0.296</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6">
+      <c r="A749" t="s">
+        <v>12</v>
+      </c>
+      <c r="B749">
+        <v>2</v>
+      </c>
+      <c r="C749" s="1">
+        <v>46221</v>
+      </c>
+      <c r="D749" s="2">
+        <v>32.44</v>
+      </c>
+      <c r="E749" s="2">
+        <v>14.35</v>
+      </c>
+      <c r="F749" s="3">
+        <v>0.733</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6">
+      <c r="A750" t="s">
+        <v>12</v>
+      </c>
+      <c r="B750">
+        <v>3</v>
+      </c>
+      <c r="C750" s="1">
+        <v>46221</v>
+      </c>
+      <c r="D750" s="2">
+        <v>32.4</v>
+      </c>
+      <c r="E750" s="2">
+        <v>11.05</v>
+      </c>
+      <c r="F750" s="3">
+        <v>0.708</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6">
+      <c r="A751" t="s">
+        <v>12</v>
+      </c>
+      <c r="B751">
+        <v>4</v>
+      </c>
+      <c r="C751" s="1">
+        <v>46221</v>
+      </c>
+      <c r="D751" s="2">
+        <v>14.35</v>
+      </c>
+      <c r="E751" s="2">
+        <v>0</v>
+      </c>
+      <c r="F751" s="3">
+        <v>0.607</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6">
+      <c r="A752" t="s">
+        <v>12</v>
+      </c>
+      <c r="B752">
+        <v>5</v>
+      </c>
+      <c r="C752" s="1">
+        <v>46221</v>
+      </c>
+      <c r="D752" s="2">
+        <v>32.46</v>
+      </c>
+      <c r="E752" s="2">
+        <v>13.19</v>
+      </c>
+      <c r="F752" s="3">
+        <v>0.789</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6">
+      <c r="A753" t="s">
+        <v>12</v>
+      </c>
+      <c r="B753">
+        <v>1</v>
+      </c>
+      <c r="C753" s="1">
+        <v>46222</v>
+      </c>
+      <c r="D753" s="2">
+        <v>33.18</v>
+      </c>
+      <c r="E753" s="2">
+        <v>0</v>
+      </c>
+      <c r="F753" s="3">
+        <v>0.311</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6">
+      <c r="A754" t="s">
+        <v>12</v>
+      </c>
+      <c r="B754">
+        <v>2</v>
+      </c>
+      <c r="C754" s="1">
+        <v>46222</v>
+      </c>
+      <c r="D754" s="2">
+        <v>33.17</v>
+      </c>
+      <c r="E754" s="2">
+        <v>12.99</v>
+      </c>
+      <c r="F754" s="3">
+        <v>0.704</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6">
+      <c r="A755" t="s">
+        <v>12</v>
+      </c>
+      <c r="B755">
+        <v>3</v>
+      </c>
+      <c r="C755" s="1">
+        <v>46222</v>
+      </c>
+      <c r="D755" s="2">
+        <v>33.16</v>
+      </c>
+      <c r="E755" s="2">
+        <v>9.58</v>
+      </c>
+      <c r="F755" s="3">
+        <v>0.676</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6">
+      <c r="A756" t="s">
+        <v>12</v>
+      </c>
+      <c r="B756">
+        <v>4</v>
+      </c>
+      <c r="C756" s="1">
+        <v>46222</v>
+      </c>
+      <c r="D756" s="2">
+        <v>33.12</v>
+      </c>
+      <c r="E756" s="2">
+        <v>0</v>
+      </c>
+      <c r="F756" s="3">
+        <v>0.672</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6">
+      <c r="A757" t="s">
+        <v>12</v>
+      </c>
+      <c r="B757">
+        <v>5</v>
+      </c>
+      <c r="C757" s="1">
+        <v>46222</v>
+      </c>
+      <c r="D757" s="2">
+        <v>33.18</v>
+      </c>
+      <c r="E757" s="2">
+        <v>12.61</v>
+      </c>
+      <c r="F757" s="3">
+        <v>0.876</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6">
+      <c r="A758" t="s">
+        <v>12</v>
+      </c>
+      <c r="B758">
+        <v>1</v>
+      </c>
+      <c r="C758" s="1">
+        <v>46223</v>
+      </c>
+      <c r="D758" s="2">
+        <v>33.35</v>
+      </c>
+      <c r="E758" s="2">
+        <v>0</v>
+      </c>
+      <c r="F758" s="3">
+        <v>0.364</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6">
+      <c r="A759" t="s">
+        <v>12</v>
+      </c>
+      <c r="B759">
+        <v>2</v>
+      </c>
+      <c r="C759" s="1">
+        <v>46223</v>
+      </c>
+      <c r="D759" s="2">
+        <v>33.26</v>
+      </c>
+      <c r="E759" s="2">
+        <v>12.68</v>
+      </c>
+      <c r="F759" s="3">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6">
+      <c r="A760" t="s">
+        <v>12</v>
+      </c>
+      <c r="B760">
+        <v>3</v>
+      </c>
+      <c r="C760" s="1">
+        <v>46223</v>
+      </c>
+      <c r="D760" s="2">
+        <v>33.29</v>
+      </c>
+      <c r="E760" s="2">
+        <v>9.98</v>
+      </c>
+      <c r="F760" s="3">
+        <v>0.893</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6">
+      <c r="A761" t="s">
+        <v>12</v>
+      </c>
+      <c r="B761">
+        <v>4</v>
+      </c>
+      <c r="C761" s="1">
+        <v>46223</v>
+      </c>
+      <c r="D761" s="2">
+        <v>33.37</v>
+      </c>
+      <c r="E761" s="2">
+        <v>0</v>
+      </c>
+      <c r="F761" s="3">
+        <v>0.825</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6">
+      <c r="A762" t="s">
+        <v>12</v>
+      </c>
+      <c r="B762">
+        <v>5</v>
+      </c>
+      <c r="C762" s="1">
+        <v>46223</v>
+      </c>
+      <c r="D762" s="2">
+        <v>33.4</v>
+      </c>
+      <c r="E762" s="2">
+        <v>14.36</v>
+      </c>
+      <c r="F762" s="3">
+        <v>0.895</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="14">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1497,7 +1497,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F435"/>
+  <dimension ref="A1:F480"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -10204,6 +10204,906 @@
         <v>0.669</v>
       </c>
     </row>
+    <row r="436" spans="1:6">
+      <c r="A436" t="s">
+        <v>9</v>
+      </c>
+      <c r="B436">
+        <v>1</v>
+      </c>
+      <c r="C436" s="1">
+        <v>46234</v>
+      </c>
+      <c r="D436" s="2">
+        <v>34.05</v>
+      </c>
+      <c r="E436" s="2">
+        <v>2.51</v>
+      </c>
+      <c r="F436" s="3">
+        <v>0.681</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6">
+      <c r="A437" t="s">
+        <v>9</v>
+      </c>
+      <c r="B437">
+        <v>2</v>
+      </c>
+      <c r="C437" s="1">
+        <v>46234</v>
+      </c>
+      <c r="D437" s="2">
+        <v>34.1</v>
+      </c>
+      <c r="E437" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="F437" s="3">
+        <v>0.834</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6">
+      <c r="A438" t="s">
+        <v>9</v>
+      </c>
+      <c r="B438">
+        <v>3</v>
+      </c>
+      <c r="C438" s="1">
+        <v>46234</v>
+      </c>
+      <c r="D438" s="2">
+        <v>34.08</v>
+      </c>
+      <c r="E438" s="2">
+        <v>5.21</v>
+      </c>
+      <c r="F438" s="3">
+        <v>0.417</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6">
+      <c r="A439" t="s">
+        <v>9</v>
+      </c>
+      <c r="B439">
+        <v>4</v>
+      </c>
+      <c r="C439" s="1">
+        <v>46234</v>
+      </c>
+      <c r="D439" s="2">
+        <v>34.02</v>
+      </c>
+      <c r="E439" s="2">
+        <v>3.95</v>
+      </c>
+      <c r="F439" s="3">
+        <v>0.577</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6">
+      <c r="A440" t="s">
+        <v>9</v>
+      </c>
+      <c r="B440">
+        <v>5</v>
+      </c>
+      <c r="C440" s="1">
+        <v>46234</v>
+      </c>
+      <c r="D440" s="2">
+        <v>34.07</v>
+      </c>
+      <c r="E440" s="2">
+        <v>8.53</v>
+      </c>
+      <c r="F440" s="3">
+        <v>0.492</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6">
+      <c r="A441" t="s">
+        <v>9</v>
+      </c>
+      <c r="B441">
+        <v>1</v>
+      </c>
+      <c r="C441" s="1">
+        <v>46235</v>
+      </c>
+      <c r="D441" s="2">
+        <v>34.29</v>
+      </c>
+      <c r="E441" s="2">
+        <v>0</v>
+      </c>
+      <c r="F441" s="3">
+        <v>0.672</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6">
+      <c r="A442" t="s">
+        <v>9</v>
+      </c>
+      <c r="B442">
+        <v>2</v>
+      </c>
+      <c r="C442" s="1">
+        <v>46235</v>
+      </c>
+      <c r="D442" s="2">
+        <v>34.24</v>
+      </c>
+      <c r="E442" s="2">
+        <v>10.82</v>
+      </c>
+      <c r="F442" s="3">
+        <v>8.457</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6">
+      <c r="A443" t="s">
+        <v>9</v>
+      </c>
+      <c r="B443">
+        <v>3</v>
+      </c>
+      <c r="C443" s="1">
+        <v>46235</v>
+      </c>
+      <c r="D443" s="2">
+        <v>34.25</v>
+      </c>
+      <c r="E443" s="2">
+        <v>5.46</v>
+      </c>
+      <c r="F443" s="3">
+        <v>0.525</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6">
+      <c r="A444" t="s">
+        <v>9</v>
+      </c>
+      <c r="B444">
+        <v>4</v>
+      </c>
+      <c r="C444" s="1">
+        <v>46235</v>
+      </c>
+      <c r="D444" s="2">
+        <v>34.22</v>
+      </c>
+      <c r="E444" s="2">
+        <v>4.86</v>
+      </c>
+      <c r="F444" s="3">
+        <v>0.631</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6">
+      <c r="A445" t="s">
+        <v>9</v>
+      </c>
+      <c r="B445">
+        <v>5</v>
+      </c>
+      <c r="C445" s="1">
+        <v>46235</v>
+      </c>
+      <c r="D445" s="2">
+        <v>34.22</v>
+      </c>
+      <c r="E445" s="2">
+        <v>5.62</v>
+      </c>
+      <c r="F445" s="3">
+        <v>0.527</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6">
+      <c r="A446" t="s">
+        <v>9</v>
+      </c>
+      <c r="B446">
+        <v>1</v>
+      </c>
+      <c r="C446" s="1">
+        <v>46236</v>
+      </c>
+      <c r="D446" s="2">
+        <v>34.57</v>
+      </c>
+      <c r="E446" s="2">
+        <v>0</v>
+      </c>
+      <c r="F446" s="3">
+        <v>0.088</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6">
+      <c r="A447" t="s">
+        <v>9</v>
+      </c>
+      <c r="B447">
+        <v>2</v>
+      </c>
+      <c r="C447" s="1">
+        <v>46236</v>
+      </c>
+      <c r="D447" s="2">
+        <v>34.47</v>
+      </c>
+      <c r="E447" s="2">
+        <v>9.87</v>
+      </c>
+      <c r="F447" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6">
+      <c r="A448" t="s">
+        <v>9</v>
+      </c>
+      <c r="B448">
+        <v>3</v>
+      </c>
+      <c r="C448" s="1">
+        <v>46236</v>
+      </c>
+      <c r="D448" s="2">
+        <v>34.44</v>
+      </c>
+      <c r="E448" s="2">
+        <v>0</v>
+      </c>
+      <c r="F448" s="3">
+        <v>0.258</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6">
+      <c r="A449" t="s">
+        <v>9</v>
+      </c>
+      <c r="B449">
+        <v>4</v>
+      </c>
+      <c r="C449" s="1">
+        <v>46236</v>
+      </c>
+      <c r="D449" s="2">
+        <v>34.46</v>
+      </c>
+      <c r="E449" s="2">
+        <v>0</v>
+      </c>
+      <c r="F449" s="3">
+        <v>0.316</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6">
+      <c r="A450" t="s">
+        <v>9</v>
+      </c>
+      <c r="B450">
+        <v>5</v>
+      </c>
+      <c r="C450" s="1">
+        <v>46236</v>
+      </c>
+      <c r="D450" s="2">
+        <v>34.42</v>
+      </c>
+      <c r="E450" s="2">
+        <v>38.94</v>
+      </c>
+      <c r="F450" s="3">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6">
+      <c r="A451" t="s">
+        <v>9</v>
+      </c>
+      <c r="B451">
+        <v>1</v>
+      </c>
+      <c r="C451" s="1">
+        <v>46238</v>
+      </c>
+      <c r="D451" s="2">
+        <v>34.16</v>
+      </c>
+      <c r="E451" s="2">
+        <v>0</v>
+      </c>
+      <c r="F451" s="3">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6">
+      <c r="A452" t="s">
+        <v>9</v>
+      </c>
+      <c r="B452">
+        <v>2</v>
+      </c>
+      <c r="C452" s="1">
+        <v>46238</v>
+      </c>
+      <c r="D452" s="2">
+        <v>34.31</v>
+      </c>
+      <c r="E452" s="2">
+        <v>9.22</v>
+      </c>
+      <c r="F452" s="3">
+        <v>0.831</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6">
+      <c r="A453" t="s">
+        <v>9</v>
+      </c>
+      <c r="B453">
+        <v>3</v>
+      </c>
+      <c r="C453" s="1">
+        <v>46238</v>
+      </c>
+      <c r="D453" s="2">
+        <v>34.33</v>
+      </c>
+      <c r="E453" s="2">
+        <v>0</v>
+      </c>
+      <c r="F453" s="3">
+        <v>0.834</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6">
+      <c r="A454" t="s">
+        <v>9</v>
+      </c>
+      <c r="B454">
+        <v>4</v>
+      </c>
+      <c r="C454" s="1">
+        <v>46238</v>
+      </c>
+      <c r="D454" s="2">
+        <v>34.32</v>
+      </c>
+      <c r="E454" s="2">
+        <v>0</v>
+      </c>
+      <c r="F454" s="3">
+        <v>0.626</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6">
+      <c r="A455" t="s">
+        <v>9</v>
+      </c>
+      <c r="B455">
+        <v>5</v>
+      </c>
+      <c r="C455" s="1">
+        <v>46238</v>
+      </c>
+      <c r="D455" s="2">
+        <v>34.33</v>
+      </c>
+      <c r="E455" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="F455" s="3">
+        <v>0.841</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6">
+      <c r="A456" t="s">
+        <v>9</v>
+      </c>
+      <c r="B456">
+        <v>1</v>
+      </c>
+      <c r="C456" s="1">
+        <v>46239</v>
+      </c>
+      <c r="D456" s="2">
+        <v>31.68</v>
+      </c>
+      <c r="E456" s="2">
+        <v>0</v>
+      </c>
+      <c r="F456" s="3">
+        <v>0.696</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6">
+      <c r="A457" t="s">
+        <v>9</v>
+      </c>
+      <c r="B457">
+        <v>2</v>
+      </c>
+      <c r="C457" s="1">
+        <v>46239</v>
+      </c>
+      <c r="D457" s="2">
+        <v>31.96</v>
+      </c>
+      <c r="E457" s="2">
+        <v>26.29</v>
+      </c>
+      <c r="F457" s="3">
+        <v>0.848</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6">
+      <c r="A458" t="s">
+        <v>9</v>
+      </c>
+      <c r="B458">
+        <v>3</v>
+      </c>
+      <c r="C458" s="1">
+        <v>46239</v>
+      </c>
+      <c r="D458" s="2">
+        <v>31.07</v>
+      </c>
+      <c r="E458" s="2">
+        <v>0</v>
+      </c>
+      <c r="F458" s="3">
+        <v>0.634</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6">
+      <c r="A459" t="s">
+        <v>9</v>
+      </c>
+      <c r="B459">
+        <v>4</v>
+      </c>
+      <c r="C459" s="1">
+        <v>46239</v>
+      </c>
+      <c r="D459" s="2">
+        <v>28.26</v>
+      </c>
+      <c r="E459" s="2">
+        <v>0</v>
+      </c>
+      <c r="F459" s="3">
+        <v>0.659</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6">
+      <c r="A460" t="s">
+        <v>9</v>
+      </c>
+      <c r="B460">
+        <v>5</v>
+      </c>
+      <c r="C460" s="1">
+        <v>46239</v>
+      </c>
+      <c r="D460" s="2">
+        <v>31.38</v>
+      </c>
+      <c r="E460" s="2">
+        <v>16.44</v>
+      </c>
+      <c r="F460" s="3">
+        <v>0.841</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6">
+      <c r="A461" t="s">
+        <v>9</v>
+      </c>
+      <c r="B461">
+        <v>1</v>
+      </c>
+      <c r="C461" s="1">
+        <v>46240</v>
+      </c>
+      <c r="D461" s="2">
+        <v>34.21</v>
+      </c>
+      <c r="E461" s="2">
+        <v>0</v>
+      </c>
+      <c r="F461" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6">
+      <c r="A462" t="s">
+        <v>9</v>
+      </c>
+      <c r="B462">
+        <v>2</v>
+      </c>
+      <c r="C462" s="1">
+        <v>46240</v>
+      </c>
+      <c r="D462" s="2">
+        <v>34.24</v>
+      </c>
+      <c r="E462" s="2">
+        <v>29.99</v>
+      </c>
+      <c r="F462" s="3">
+        <v>0.833</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6">
+      <c r="A463" t="s">
+        <v>9</v>
+      </c>
+      <c r="B463">
+        <v>3</v>
+      </c>
+      <c r="C463" s="1">
+        <v>46240</v>
+      </c>
+      <c r="D463" s="2">
+        <v>34.24</v>
+      </c>
+      <c r="E463" s="2">
+        <v>0</v>
+      </c>
+      <c r="F463" s="3">
+        <v>0.619</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6">
+      <c r="A464" t="s">
+        <v>9</v>
+      </c>
+      <c r="B464">
+        <v>4</v>
+      </c>
+      <c r="C464" s="1">
+        <v>46240</v>
+      </c>
+      <c r="D464" s="2">
+        <v>34.22</v>
+      </c>
+      <c r="E464" s="2">
+        <v>4.37</v>
+      </c>
+      <c r="F464" s="3">
+        <v>0.569</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6">
+      <c r="A465" t="s">
+        <v>9</v>
+      </c>
+      <c r="B465">
+        <v>5</v>
+      </c>
+      <c r="C465" s="1">
+        <v>46240</v>
+      </c>
+      <c r="D465" s="2">
+        <v>34.23</v>
+      </c>
+      <c r="E465" s="2">
+        <v>39.15</v>
+      </c>
+      <c r="F465" s="3">
+        <v>0.654</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6">
+      <c r="A466" t="s">
+        <v>9</v>
+      </c>
+      <c r="B466">
+        <v>1</v>
+      </c>
+      <c r="C466" s="1">
+        <v>46241</v>
+      </c>
+      <c r="D466" s="2">
+        <v>19.09</v>
+      </c>
+      <c r="E466" s="2">
+        <v>0</v>
+      </c>
+      <c r="F466" s="3">
+        <v>0.465</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6">
+      <c r="A467" t="s">
+        <v>9</v>
+      </c>
+      <c r="B467">
+        <v>2</v>
+      </c>
+      <c r="C467" s="1">
+        <v>46241</v>
+      </c>
+      <c r="D467" s="2">
+        <v>19.1</v>
+      </c>
+      <c r="E467" s="2">
+        <v>26.24</v>
+      </c>
+      <c r="F467" s="3">
+        <v>0.629</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6">
+      <c r="A468" t="s">
+        <v>9</v>
+      </c>
+      <c r="B468">
+        <v>3</v>
+      </c>
+      <c r="C468" s="1">
+        <v>46241</v>
+      </c>
+      <c r="D468" s="2">
+        <v>19.1</v>
+      </c>
+      <c r="E468" s="2">
+        <v>0</v>
+      </c>
+      <c r="F468" s="3">
+        <v>0.747</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6">
+      <c r="A469" t="s">
+        <v>9</v>
+      </c>
+      <c r="B469">
+        <v>4</v>
+      </c>
+      <c r="C469" s="1">
+        <v>46241</v>
+      </c>
+      <c r="D469" s="2">
+        <v>19.11</v>
+      </c>
+      <c r="E469" s="2">
+        <v>0</v>
+      </c>
+      <c r="F469" s="3">
+        <v>0.566</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6">
+      <c r="A470" t="s">
+        <v>9</v>
+      </c>
+      <c r="B470">
+        <v>5</v>
+      </c>
+      <c r="C470" s="1">
+        <v>46241</v>
+      </c>
+      <c r="D470" s="2">
+        <v>19.11</v>
+      </c>
+      <c r="E470" s="2">
+        <v>36.57</v>
+      </c>
+      <c r="F470" s="3">
+        <v>0.865</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6">
+      <c r="A471" t="s">
+        <v>9</v>
+      </c>
+      <c r="B471">
+        <v>1</v>
+      </c>
+      <c r="C471" s="1">
+        <v>46242</v>
+      </c>
+      <c r="D471" s="2">
+        <v>32.7</v>
+      </c>
+      <c r="E471" s="2">
+        <v>0</v>
+      </c>
+      <c r="F471" s="3">
+        <v>0.488</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6">
+      <c r="A472" t="s">
+        <v>9</v>
+      </c>
+      <c r="B472">
+        <v>2</v>
+      </c>
+      <c r="C472" s="1">
+        <v>46242</v>
+      </c>
+      <c r="D472" s="2">
+        <v>32.72</v>
+      </c>
+      <c r="E472" s="2">
+        <v>29.79</v>
+      </c>
+      <c r="F472" s="3">
+        <v>0.741</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6">
+      <c r="A473" t="s">
+        <v>9</v>
+      </c>
+      <c r="B473">
+        <v>3</v>
+      </c>
+      <c r="C473" s="1">
+        <v>46242</v>
+      </c>
+      <c r="D473" s="2">
+        <v>32.73</v>
+      </c>
+      <c r="E473" s="2">
+        <v>9.87</v>
+      </c>
+      <c r="F473" s="3">
+        <v>0.856</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6">
+      <c r="A474" t="s">
+        <v>9</v>
+      </c>
+      <c r="B474">
+        <v>4</v>
+      </c>
+      <c r="C474" s="1">
+        <v>46242</v>
+      </c>
+      <c r="D474" s="2">
+        <v>32.75</v>
+      </c>
+      <c r="E474" s="2">
+        <v>0</v>
+      </c>
+      <c r="F474" s="3">
+        <v>0.727</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6">
+      <c r="A475" t="s">
+        <v>9</v>
+      </c>
+      <c r="B475">
+        <v>5</v>
+      </c>
+      <c r="C475" s="1">
+        <v>46242</v>
+      </c>
+      <c r="D475" s="2">
+        <v>32.72</v>
+      </c>
+      <c r="E475" s="2">
+        <v>35.62</v>
+      </c>
+      <c r="F475" s="3">
+        <v>0.738</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6">
+      <c r="A476" t="s">
+        <v>9</v>
+      </c>
+      <c r="B476">
+        <v>1</v>
+      </c>
+      <c r="C476" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D476" s="2">
+        <v>33.24</v>
+      </c>
+      <c r="E476" s="2">
+        <v>0</v>
+      </c>
+      <c r="F476" s="3">
+        <v>0.504</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6">
+      <c r="A477" t="s">
+        <v>9</v>
+      </c>
+      <c r="B477">
+        <v>2</v>
+      </c>
+      <c r="C477" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D477" s="2">
+        <v>33.68</v>
+      </c>
+      <c r="E477" s="2">
+        <v>26.7</v>
+      </c>
+      <c r="F477" s="3">
+        <v>0.585</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6">
+      <c r="A478" t="s">
+        <v>9</v>
+      </c>
+      <c r="B478">
+        <v>3</v>
+      </c>
+      <c r="C478" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D478" s="2">
+        <v>33.25</v>
+      </c>
+      <c r="E478" s="2">
+        <v>3.38</v>
+      </c>
+      <c r="F478" s="3">
+        <v>0.643</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6">
+      <c r="A479" t="s">
+        <v>9</v>
+      </c>
+      <c r="B479">
+        <v>4</v>
+      </c>
+      <c r="C479" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D479" s="2">
+        <v>33.25</v>
+      </c>
+      <c r="E479" s="2">
+        <v>4.19</v>
+      </c>
+      <c r="F479" s="3">
+        <v>0.702</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6">
+      <c r="A480" t="s">
+        <v>9</v>
+      </c>
+      <c r="B480">
+        <v>5</v>
+      </c>
+      <c r="C480" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D480" s="2">
+        <v>33.25</v>
+      </c>
+      <c r="E480" s="2">
+        <v>36.57</v>
+      </c>
+      <c r="F480" s="3">
+        <v>0.822</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="14">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1272,13 +1272,13 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="F2" s="1">
         <v>46052</v>
@@ -1330,7 +1330,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1497,7 +1497,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F480"/>
+  <dimension ref="A1:F485"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5"/>
@@ -11104,6 +11104,106 @@
         <v>0.822</v>
       </c>
     </row>
+    <row r="481" spans="1:6">
+      <c r="A481" t="s">
+        <v>9</v>
+      </c>
+      <c r="B481">
+        <v>1</v>
+      </c>
+      <c r="C481" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D481" s="2">
+        <v>33.73</v>
+      </c>
+      <c r="E481" s="2">
+        <v>0</v>
+      </c>
+      <c r="F481" s="3">
+        <v>1.131</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6">
+      <c r="A482" t="s">
+        <v>9</v>
+      </c>
+      <c r="B482">
+        <v>2</v>
+      </c>
+      <c r="C482" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D482" s="2">
+        <v>33.72</v>
+      </c>
+      <c r="E482" s="2">
+        <v>28.01</v>
+      </c>
+      <c r="F482" s="3">
+        <v>0.645</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6">
+      <c r="A483" t="s">
+        <v>9</v>
+      </c>
+      <c r="B483">
+        <v>3</v>
+      </c>
+      <c r="C483" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D483" s="2">
+        <v>33.74</v>
+      </c>
+      <c r="E483" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="F483" s="3">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6">
+      <c r="A484" t="s">
+        <v>9</v>
+      </c>
+      <c r="B484">
+        <v>4</v>
+      </c>
+      <c r="C484" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D484" s="2">
+        <v>33.73</v>
+      </c>
+      <c r="E484" s="2">
+        <v>2.92</v>
+      </c>
+      <c r="F484" s="3">
+        <v>0.743</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6">
+      <c r="A485" t="s">
+        <v>9</v>
+      </c>
+      <c r="B485">
+        <v>5</v>
+      </c>
+      <c r="C485" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D485" s="2">
+        <v>33.74</v>
+      </c>
+      <c r="E485" s="2">
+        <v>38.57</v>
+      </c>
+      <c r="F485" s="3">
+        <v>0.623</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -10018,7 +10018,7 @@
         <v>33.42</v>
       </c>
       <c r="E426" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F426" s="3">
         <v>0.521</v>
@@ -10341,7 +10341,7 @@
         <v>10.82</v>
       </c>
       <c r="F442" s="3">
-        <v>8.457</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -10421,7 +10421,7 @@
         <v>0</v>
       </c>
       <c r="F446" s="3">
-        <v>0.088</v>
+        <v>0.857</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -10441,7 +10441,7 @@
         <v>9.87</v>
       </c>
       <c r="F447" s="3">
-        <v>6</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="448" spans="1:6">
@@ -11115,7 +11115,7 @@
         <v>46244</v>
       </c>
       <c r="D481" s="2">
-        <v>33.73</v>
+        <v>34.83</v>
       </c>
       <c r="E481" s="2">
         <v>0</v>
@@ -11135,10 +11135,10 @@
         <v>46244</v>
       </c>
       <c r="D482" s="2">
-        <v>33.72</v>
+        <v>34.84</v>
       </c>
       <c r="E482" s="2">
-        <v>28.01</v>
+        <v>28.53</v>
       </c>
       <c r="F482" s="3">
         <v>0.645</v>
@@ -11155,13 +11155,13 @@
         <v>46244</v>
       </c>
       <c r="D483" s="2">
-        <v>33.74</v>
+        <v>34.83</v>
       </c>
       <c r="E483" s="2">
-        <v>0.07</v>
+        <v>0</v>
       </c>
       <c r="F483" s="3">
-        <v>0.537</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="484" spans="1:6">
@@ -11175,13 +11175,13 @@
         <v>46244</v>
       </c>
       <c r="D484" s="2">
-        <v>33.73</v>
+        <v>34.81</v>
       </c>
       <c r="E484" s="2">
-        <v>2.92</v>
+        <v>3.26</v>
       </c>
       <c r="F484" s="3">
-        <v>0.743</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="485" spans="1:6">
@@ -11195,13 +11195,13 @@
         <v>46244</v>
       </c>
       <c r="D485" s="2">
-        <v>33.74</v>
+        <v>34.85</v>
       </c>
       <c r="E485" s="2">
-        <v>38.57</v>
+        <v>39.85</v>
       </c>
       <c r="F485" s="3">
-        <v>0.623</v>
+        <v>0.564</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -10341,7 +10341,7 @@
         <v>10.82</v>
       </c>
       <c r="F442" s="3">
-        <v>0.457</v>
+        <v>8.457</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -10415,13 +10415,13 @@
         <v>46236</v>
       </c>
       <c r="D446" s="2">
-        <v>34.57</v>
+        <v>4.57</v>
       </c>
       <c r="E446" s="2">
         <v>0</v>
       </c>
       <c r="F446" s="3">
-        <v>0.857</v>
+        <v>0.088</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -10441,7 +10441,7 @@
         <v>9.87</v>
       </c>
       <c r="F447" s="3">
-        <v>0.834</v>
+        <v>1.006</v>
       </c>
     </row>
     <row r="448" spans="1:6">
@@ -10455,7 +10455,7 @@
         <v>46236</v>
       </c>
       <c r="D448" s="2">
-        <v>34.44</v>
+        <v>9.44</v>
       </c>
       <c r="E448" s="2">
         <v>0</v>
@@ -10475,7 +10475,7 @@
         <v>46236</v>
       </c>
       <c r="D449" s="2">
-        <v>34.46</v>
+        <v>15.74</v>
       </c>
       <c r="E449" s="2">
         <v>0</v>
@@ -10515,7 +10515,7 @@
         <v>46238</v>
       </c>
       <c r="D451" s="2">
-        <v>34.16</v>
+        <v>4.16</v>
       </c>
       <c r="E451" s="2">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="31">
   <si>
     <t>抽采地点</t>
   </si>
@@ -61,6 +61,57 @@
   </si>
   <si>
     <t>12803回风巷</t>
+  </si>
+  <si>
+    <t>12803回风巷高位钻孔</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>1-7</t>
+  </si>
+  <si>
+    <t>1-8</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>2-6</t>
+  </si>
+  <si>
+    <t>2-7</t>
+  </si>
+  <si>
+    <t>2-8</t>
   </si>
   <si>
     <t>检测日期</t>
@@ -691,7 +742,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -702,6 +753,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1232,6 +1289,7 @@
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
+    <col min="1" max="1" width="20.625" customWidth="1"/>
     <col min="6" max="6" width="11.5"/>
   </cols>
   <sheetData>
@@ -1410,53 +1468,469 @@
         <v>0.468</v>
       </c>
     </row>
-    <row r="7" spans="6:6">
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="6:6">
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="6:6">
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="6:6">
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="6:6">
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="6:6">
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="6:6">
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="6:6">
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="6:6">
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="6:6">
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="6:6">
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="6:6">
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="6:6">
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="6:6">
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="6:6">
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="6:6">
-      <c r="F22" s="1"/>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>65</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>66</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="H7" s="2">
+        <v>40.07</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>115</v>
+      </c>
+      <c r="E8">
+        <v>78</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G8" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="H8" s="2">
+        <v>40.15</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0.252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>62</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H9" s="2">
+        <v>40.02</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.386</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>27</v>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>62</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G10" s="2">
+        <v>4.4</v>
+      </c>
+      <c r="H10" s="2">
+        <v>40.12</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0.219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>78</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>40.11</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0.189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>13</v>
+      </c>
+      <c r="E12">
+        <v>52</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="H12" s="2">
+        <v>40.15</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>61</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H13" s="2">
+        <v>40.13</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>12</v>
+      </c>
+      <c r="E14">
+        <v>58</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="H14" s="2">
+        <v>40.1</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15">
+        <v>65</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>86</v>
+      </c>
+      <c r="F15" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H15" s="2">
+        <v>40.16</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0.359</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16">
+        <v>50</v>
+      </c>
+      <c r="D16">
+        <v>19</v>
+      </c>
+      <c r="E16">
+        <v>64</v>
+      </c>
+      <c r="F16" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G16" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H16" s="2">
+        <v>40.16</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17">
+        <v>37</v>
+      </c>
+      <c r="D17">
+        <v>14</v>
+      </c>
+      <c r="E17">
+        <v>66</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G17" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="H17" s="2">
+        <v>40.2</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18">
+        <v>27</v>
+      </c>
+      <c r="D18">
+        <v>14</v>
+      </c>
+      <c r="E18">
+        <v>86</v>
+      </c>
+      <c r="F18" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G18" s="2">
+        <v>13.4</v>
+      </c>
+      <c r="H18" s="2">
+        <v>40.19</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
+      <c r="D19">
+        <v>17</v>
+      </c>
+      <c r="E19">
+        <v>86</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="2">
+        <v>40.18</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0.294</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20">
+        <v>13</v>
+      </c>
+      <c r="D20">
+        <v>17</v>
+      </c>
+      <c r="E20">
+        <v>84</v>
+      </c>
+      <c r="F20" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G20" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="H20" s="2">
+        <v>40.16</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>8</v>
+      </c>
+      <c r="D21">
+        <v>12</v>
+      </c>
+      <c r="E21">
+        <v>86</v>
+      </c>
+      <c r="F21" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="H21" s="2">
+        <v>40.18</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0.284</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <v>16</v>
+      </c>
+      <c r="E22">
+        <v>26</v>
+      </c>
+      <c r="F22" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G22" s="2">
+        <v>48.6</v>
+      </c>
+      <c r="H22" s="2">
+        <v>40.25</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0.104</v>
+      </c>
     </row>
     <row r="23" spans="6:6">
       <c r="F23" s="1"/>
@@ -1497,9 +1971,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F485"/>
+  <dimension ref="A1:F559"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
+    <col min="1" max="1" width="12.25" customWidth="1"/>
     <col min="3" max="3" width="11.5"/>
     <col min="6" max="6" width="9.375"/>
   </cols>
@@ -1512,16 +1987,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -11108,100 +11583,1568 @@
       <c r="A481" t="s">
         <v>9</v>
       </c>
-      <c r="B481">
-        <v>1</v>
+      <c r="B481" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C481" s="1">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="D481" s="2">
-        <v>34.83</v>
+        <v>3.07</v>
       </c>
       <c r="E481" s="2">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="F481" s="3">
-        <v>1.131</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="482" spans="1:6">
       <c r="A482" t="s">
         <v>9</v>
       </c>
-      <c r="B482">
-        <v>2</v>
+      <c r="B482" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C482" s="1">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="D482" s="2">
-        <v>34.84</v>
+        <v>3.06</v>
       </c>
       <c r="E482" s="2">
-        <v>28.53</v>
+        <v>0</v>
       </c>
       <c r="F482" s="3">
-        <v>0.645</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="483" spans="1:6">
       <c r="A483" t="s">
         <v>9</v>
       </c>
-      <c r="B483">
-        <v>3</v>
+      <c r="B483" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C483" s="1">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="D483" s="2">
-        <v>34.83</v>
+        <v>3.02</v>
       </c>
       <c r="E483" s="2">
         <v>0</v>
       </c>
       <c r="F483" s="3">
-        <v>0.626</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="484" spans="1:6">
       <c r="A484" t="s">
         <v>9</v>
       </c>
-      <c r="B484">
-        <v>4</v>
+      <c r="B484" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C484" s="1">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="D484" s="2">
-        <v>34.81</v>
+        <v>3.09</v>
       </c>
       <c r="E484" s="2">
-        <v>3.26</v>
+        <v>43.67</v>
       </c>
       <c r="F484" s="3">
-        <v>1.042</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="485" spans="1:6">
       <c r="A485" t="s">
         <v>9</v>
       </c>
-      <c r="B485">
+      <c r="B485" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C485" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D485" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="E485" s="2">
+        <v>0</v>
+      </c>
+      <c r="F485" s="3">
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6">
+      <c r="A486" t="s">
+        <v>9</v>
+      </c>
+      <c r="B486" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C486" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D486" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="E486" s="2">
+        <v>0</v>
+      </c>
+      <c r="F486" s="3">
+        <v>0.213</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6">
+      <c r="A487" t="s">
+        <v>9</v>
+      </c>
+      <c r="B487" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C487" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D487" s="2">
+        <v>3.07</v>
+      </c>
+      <c r="E487" s="2">
+        <v>0</v>
+      </c>
+      <c r="F487" s="3">
+        <v>0.243</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6">
+      <c r="A488" t="s">
+        <v>9</v>
+      </c>
+      <c r="B488" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C488" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D488" s="2"/>
+      <c r="E488" s="2"/>
+      <c r="F488" s="3"/>
+    </row>
+    <row r="489" spans="1:6">
+      <c r="A489" t="s">
+        <v>9</v>
+      </c>
+      <c r="B489" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C489" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D489" s="2">
+        <v>3.06</v>
+      </c>
+      <c r="E489" s="2">
+        <v>4.32</v>
+      </c>
+      <c r="F489" s="3">
+        <v>0.242</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6">
+      <c r="A490" t="s">
+        <v>9</v>
+      </c>
+      <c r="B490" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C490" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D490" s="2">
+        <v>3.07</v>
+      </c>
+      <c r="E490" s="2">
+        <v>8.65</v>
+      </c>
+      <c r="F490" s="3">
+        <v>0.281</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6">
+      <c r="A491" t="s">
+        <v>9</v>
+      </c>
+      <c r="B491" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C491" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D491" s="2">
+        <v>3.06</v>
+      </c>
+      <c r="E491" s="2">
+        <v>6.42</v>
+      </c>
+      <c r="F491" s="3">
+        <v>0.269</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6">
+      <c r="A492" t="s">
+        <v>9</v>
+      </c>
+      <c r="B492" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C492" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D492" s="2">
+        <v>3.04</v>
+      </c>
+      <c r="E492" s="2">
+        <v>0</v>
+      </c>
+      <c r="F492" s="3">
+        <v>0.279</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6">
+      <c r="A493" t="s">
+        <v>9</v>
+      </c>
+      <c r="B493" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C493" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D493" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="E493" s="2">
+        <v>0</v>
+      </c>
+      <c r="F493" s="3">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6">
+      <c r="A494" t="s">
+        <v>9</v>
+      </c>
+      <c r="B494" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C494" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D494" s="2">
+        <v>3.01</v>
+      </c>
+      <c r="E494" s="2">
+        <v>0</v>
+      </c>
+      <c r="F494" s="3">
+        <v>0.166</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6">
+      <c r="A495" t="s">
+        <v>9</v>
+      </c>
+      <c r="B495" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C495" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D495" s="2"/>
+      <c r="E495" s="2"/>
+      <c r="F495" s="3"/>
+    </row>
+    <row r="496" spans="1:6">
+      <c r="A496" t="s">
+        <v>9</v>
+      </c>
+      <c r="B496" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C496" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D496" s="2">
+        <v>3.09</v>
+      </c>
+      <c r="E496" s="2">
+        <v>81.12</v>
+      </c>
+      <c r="F496" s="3">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6">
+      <c r="A497" t="s">
+        <v>9</v>
+      </c>
+      <c r="B497">
+        <v>1</v>
+      </c>
+      <c r="C497" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D497" s="2">
+        <v>34.83</v>
+      </c>
+      <c r="E497" s="2">
+        <v>0</v>
+      </c>
+      <c r="F497" s="3">
+        <v>1.131</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6">
+      <c r="A498" t="s">
+        <v>9</v>
+      </c>
+      <c r="B498">
+        <v>2</v>
+      </c>
+      <c r="C498" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D498" s="2">
+        <v>34.84</v>
+      </c>
+      <c r="E498" s="2">
+        <v>28.53</v>
+      </c>
+      <c r="F498" s="3">
+        <v>0.645</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6">
+      <c r="A499" t="s">
+        <v>9</v>
+      </c>
+      <c r="B499">
+        <v>3</v>
+      </c>
+      <c r="C499" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D499" s="2">
+        <v>34.83</v>
+      </c>
+      <c r="E499" s="2">
+        <v>0</v>
+      </c>
+      <c r="F499" s="3">
+        <v>0.626</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6">
+      <c r="A500" t="s">
+        <v>9</v>
+      </c>
+      <c r="B500">
+        <v>4</v>
+      </c>
+      <c r="C500" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D500" s="2">
+        <v>34.81</v>
+      </c>
+      <c r="E500" s="2">
+        <v>3.26</v>
+      </c>
+      <c r="F500" s="3">
+        <v>1.042</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6">
+      <c r="A501" t="s">
+        <v>9</v>
+      </c>
+      <c r="B501">
         <v>5</v>
       </c>
-      <c r="C485" s="1">
+      <c r="C501" s="1">
         <v>46244</v>
       </c>
-      <c r="D485" s="2">
+      <c r="D501" s="2">
         <v>34.85</v>
       </c>
-      <c r="E485" s="2">
+      <c r="E501" s="2">
         <v>39.85</v>
       </c>
-      <c r="F485" s="3">
+      <c r="F501" s="3">
         <v>0.564</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6">
+      <c r="A502" t="s">
+        <v>9</v>
+      </c>
+      <c r="B502" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C502" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D502" s="2">
+        <v>2.92</v>
+      </c>
+      <c r="E502" s="2">
+        <v>7.82</v>
+      </c>
+      <c r="F502" s="3">
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6">
+      <c r="A503" t="s">
+        <v>9</v>
+      </c>
+      <c r="B503" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C503" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D503" s="2">
+        <v>2.99</v>
+      </c>
+      <c r="E503" s="2">
+        <v>0</v>
+      </c>
+      <c r="F503" s="3">
+        <v>0.148</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6">
+      <c r="A504" t="s">
+        <v>9</v>
+      </c>
+      <c r="B504" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C504" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D504" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="E504" s="2">
+        <v>0</v>
+      </c>
+      <c r="F504" s="3">
+        <v>0.082</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6">
+      <c r="A505" t="s">
+        <v>9</v>
+      </c>
+      <c r="B505" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C505" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D505" s="2">
+        <v>2.96</v>
+      </c>
+      <c r="E505" s="2">
+        <v>33.98</v>
+      </c>
+      <c r="F505" s="3">
+        <v>0.082</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6">
+      <c r="A506" t="s">
+        <v>9</v>
+      </c>
+      <c r="B506" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C506" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D506" s="2">
+        <v>2.91</v>
+      </c>
+      <c r="E506" s="2">
+        <v>0</v>
+      </c>
+      <c r="F506" s="3">
+        <v>0.195</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6">
+      <c r="A507" t="s">
+        <v>9</v>
+      </c>
+      <c r="B507" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C507" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D507" s="2">
+        <v>2.84</v>
+      </c>
+      <c r="E507" s="2">
+        <v>0.31</v>
+      </c>
+      <c r="F507" s="3">
+        <v>0.138</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6">
+      <c r="A508" t="s">
+        <v>9</v>
+      </c>
+      <c r="B508" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C508" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D508" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="E508" s="2">
+        <v>0</v>
+      </c>
+      <c r="F508" s="3">
+        <v>0.248</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6">
+      <c r="A509" t="s">
+        <v>9</v>
+      </c>
+      <c r="B509" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C509" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D509" s="2">
+        <v>2.78</v>
+      </c>
+      <c r="E509" s="2">
+        <v>0</v>
+      </c>
+      <c r="F509" s="3">
+        <v>1.534</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6">
+      <c r="A510" t="s">
+        <v>9</v>
+      </c>
+      <c r="B510" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C510" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D510" s="2">
+        <v>2.99</v>
+      </c>
+      <c r="E510" s="2">
+        <v>2.83</v>
+      </c>
+      <c r="F510" s="3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6">
+      <c r="A511" t="s">
+        <v>9</v>
+      </c>
+      <c r="B511" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C511" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D511" s="2">
+        <v>2.85</v>
+      </c>
+      <c r="E511" s="2">
+        <v>6.15</v>
+      </c>
+      <c r="F511" s="3">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6">
+      <c r="A512" t="s">
+        <v>9</v>
+      </c>
+      <c r="B512" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C512" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D512" s="2">
+        <v>2.99</v>
+      </c>
+      <c r="E512" s="2">
+        <v>10.08</v>
+      </c>
+      <c r="F512" s="3">
+        <v>0.171</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6">
+      <c r="A513" t="s">
+        <v>9</v>
+      </c>
+      <c r="B513" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C513" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D513" s="2">
+        <v>2.84</v>
+      </c>
+      <c r="E513" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="F513" s="3">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6">
+      <c r="A514" t="s">
+        <v>9</v>
+      </c>
+      <c r="B514" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C514" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D514" s="2">
+        <v>2.84</v>
+      </c>
+      <c r="E514" s="2">
+        <v>0</v>
+      </c>
+      <c r="F514" s="3">
+        <v>0.143</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6">
+      <c r="A515" t="s">
+        <v>9</v>
+      </c>
+      <c r="B515" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C515" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D515" s="2">
+        <v>2.94</v>
+      </c>
+      <c r="E515" s="2">
+        <v>0</v>
+      </c>
+      <c r="F515" s="3">
+        <v>0.205</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6">
+      <c r="A516" t="s">
+        <v>9</v>
+      </c>
+      <c r="B516" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C516" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D516" s="2">
+        <v>2.99</v>
+      </c>
+      <c r="E516" s="2">
+        <v>0</v>
+      </c>
+      <c r="F516" s="3">
+        <v>0.957</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6">
+      <c r="A517" t="s">
+        <v>9</v>
+      </c>
+      <c r="B517" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C517" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D517" s="2">
+        <v>2.99</v>
+      </c>
+      <c r="E517" s="2">
+        <v>72.46</v>
+      </c>
+      <c r="F517" s="3">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6">
+      <c r="A518" t="s">
+        <v>9</v>
+      </c>
+      <c r="B518">
+        <v>1</v>
+      </c>
+      <c r="C518" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D518" s="2">
+        <v>33.79</v>
+      </c>
+      <c r="E518" s="2">
+        <v>0</v>
+      </c>
+      <c r="F518" s="3">
+        <v>0.548</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6">
+      <c r="A519" t="s">
+        <v>9</v>
+      </c>
+      <c r="B519">
+        <v>2</v>
+      </c>
+      <c r="C519" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D519" s="2">
+        <v>33.78</v>
+      </c>
+      <c r="E519" s="2">
+        <v>33.78</v>
+      </c>
+      <c r="F519" s="3">
+        <v>0.716</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6">
+      <c r="A520" t="s">
+        <v>9</v>
+      </c>
+      <c r="B520">
+        <v>3</v>
+      </c>
+      <c r="C520" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D520" s="2">
+        <v>33.79</v>
+      </c>
+      <c r="E520" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="F520" s="3">
+        <v>0.737</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6">
+      <c r="A521" t="s">
+        <v>9</v>
+      </c>
+      <c r="B521">
+        <v>4</v>
+      </c>
+      <c r="C521" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D521" s="2">
+        <v>33.8</v>
+      </c>
+      <c r="E521" s="2">
+        <v>3.17</v>
+      </c>
+      <c r="F521" s="3">
+        <v>0.813</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6">
+      <c r="A522" t="s">
+        <v>9</v>
+      </c>
+      <c r="B522">
+        <v>5</v>
+      </c>
+      <c r="C522" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D522" s="2">
+        <v>33.82</v>
+      </c>
+      <c r="E522" s="2">
+        <v>39.15</v>
+      </c>
+      <c r="F522" s="3">
+        <v>0.832</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6">
+      <c r="A523" t="s">
+        <v>9</v>
+      </c>
+      <c r="B523" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C523" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D523" s="2">
+        <v>3.04</v>
+      </c>
+      <c r="E523" s="2">
+        <v>13.6</v>
+      </c>
+      <c r="F523" s="3">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6">
+      <c r="A524" t="s">
+        <v>9</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C524" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D524" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="E524" s="2">
+        <v>0</v>
+      </c>
+      <c r="F524" s="3">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6">
+      <c r="A525" t="s">
+        <v>9</v>
+      </c>
+      <c r="B525" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C525" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D525" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="E525" s="2">
+        <v>0</v>
+      </c>
+      <c r="F525" s="3">
+        <v>0.133</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6">
+      <c r="A526" t="s">
+        <v>9</v>
+      </c>
+      <c r="B526" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C526" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D526" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="E526" s="2">
+        <v>34.26</v>
+      </c>
+      <c r="F526" s="3">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6">
+      <c r="A527" t="s">
+        <v>9</v>
+      </c>
+      <c r="B527" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C527" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D527" s="2">
+        <v>3.04</v>
+      </c>
+      <c r="E527" s="2">
+        <v>0</v>
+      </c>
+      <c r="F527" s="3">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6">
+      <c r="A528" t="s">
+        <v>9</v>
+      </c>
+      <c r="B528" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C528" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D528" s="2">
+        <v>3.08</v>
+      </c>
+      <c r="E528" s="2">
+        <v>0</v>
+      </c>
+      <c r="F528" s="3">
+        <v>0.208</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6">
+      <c r="A529" t="s">
+        <v>9</v>
+      </c>
+      <c r="B529" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C529" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D529" s="2">
+        <v>3.09</v>
+      </c>
+      <c r="E529" s="2">
+        <v>0</v>
+      </c>
+      <c r="F529" s="3">
+        <v>0.237</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6">
+      <c r="A530" t="s">
+        <v>9</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C530" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D530" s="2">
+        <v>3.04</v>
+      </c>
+      <c r="E530" s="2">
+        <v>0</v>
+      </c>
+      <c r="F530" s="3">
+        <v>0.178</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6">
+      <c r="A531" t="s">
+        <v>9</v>
+      </c>
+      <c r="B531" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C531" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D531" s="2">
+        <v>3.04</v>
+      </c>
+      <c r="E531" s="2">
+        <v>4.32</v>
+      </c>
+      <c r="F531" s="3">
+        <v>0.251</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6">
+      <c r="A532" t="s">
+        <v>9</v>
+      </c>
+      <c r="B532" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C532" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D532" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="E532" s="2">
+        <v>5.77</v>
+      </c>
+      <c r="F532" s="3">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6">
+      <c r="A533" t="s">
+        <v>9</v>
+      </c>
+      <c r="B533" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C533" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D533" s="2">
+        <v>3.02</v>
+      </c>
+      <c r="E533" s="2">
+        <v>4.37</v>
+      </c>
+      <c r="F533" s="3">
+        <v>0.273</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6">
+      <c r="A534" t="s">
+        <v>9</v>
+      </c>
+      <c r="B534" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C534" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D534" s="2">
+        <v>3.07</v>
+      </c>
+      <c r="E534" s="2">
+        <v>0</v>
+      </c>
+      <c r="F534" s="3">
+        <v>0.285</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6">
+      <c r="A535" t="s">
+        <v>9</v>
+      </c>
+      <c r="B535" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C535" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D535" s="2">
+        <v>3.04</v>
+      </c>
+      <c r="E535" s="2">
+        <v>0</v>
+      </c>
+      <c r="F535" s="3">
+        <v>0.231</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6">
+      <c r="A536" t="s">
+        <v>9</v>
+      </c>
+      <c r="B536" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C536" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D536" s="2">
+        <v>3</v>
+      </c>
+      <c r="E536" s="2">
+        <v>0</v>
+      </c>
+      <c r="F536" s="3">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6">
+      <c r="A537" t="s">
+        <v>9</v>
+      </c>
+      <c r="B537" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C537" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D537" s="2">
+        <v>3.01</v>
+      </c>
+      <c r="E537" s="2">
+        <v>0</v>
+      </c>
+      <c r="F537" s="3">
+        <v>0.166</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6">
+      <c r="A538" t="s">
+        <v>9</v>
+      </c>
+      <c r="B538" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C538" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D538" s="2">
+        <v>3.06</v>
+      </c>
+      <c r="E538" s="2">
+        <v>70.48</v>
+      </c>
+      <c r="F538" s="3">
+        <v>0.137</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6">
+      <c r="A539" t="s">
+        <v>9</v>
+      </c>
+      <c r="B539">
+        <v>1</v>
+      </c>
+      <c r="C539" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D539" s="2">
+        <v>30.76</v>
+      </c>
+      <c r="E539" s="2">
+        <v>0</v>
+      </c>
+      <c r="F539" s="3">
+        <v>1.067</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6">
+      <c r="A540" t="s">
+        <v>9</v>
+      </c>
+      <c r="B540">
+        <v>2</v>
+      </c>
+      <c r="C540" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D540" s="2">
+        <v>30.78</v>
+      </c>
+      <c r="E540" s="2">
+        <v>26.57</v>
+      </c>
+      <c r="F540" s="3">
+        <v>0.555</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6">
+      <c r="A541" t="s">
+        <v>9</v>
+      </c>
+      <c r="B541">
+        <v>3</v>
+      </c>
+      <c r="C541" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D541" s="2">
+        <v>30.76</v>
+      </c>
+      <c r="E541" s="2">
+        <v>0</v>
+      </c>
+      <c r="F541" s="3">
+        <v>0.681</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6">
+      <c r="A542" t="s">
+        <v>9</v>
+      </c>
+      <c r="B542">
+        <v>4</v>
+      </c>
+      <c r="C542" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D542" s="2">
+        <v>30.77</v>
+      </c>
+      <c r="E542" s="2">
+        <v>2.86</v>
+      </c>
+      <c r="F542" s="3">
+        <v>1.066</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6">
+      <c r="A543" t="s">
+        <v>9</v>
+      </c>
+      <c r="B543">
+        <v>5</v>
+      </c>
+      <c r="C543" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D543" s="2">
+        <v>30.77</v>
+      </c>
+      <c r="E543" s="2">
+        <v>33.1</v>
+      </c>
+      <c r="F543" s="3">
+        <v>0.674</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6">
+      <c r="A544" t="s">
+        <v>9</v>
+      </c>
+      <c r="B544" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C544" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D544" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="E544" s="2">
+        <v>80.09</v>
+      </c>
+      <c r="F544" s="3">
+        <v>0.071</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6">
+      <c r="A545" t="s">
+        <v>9</v>
+      </c>
+      <c r="B545" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C545" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D545" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="E545" s="2">
+        <v>0</v>
+      </c>
+      <c r="F545" s="3">
+        <v>0.072</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6">
+      <c r="A546" t="s">
+        <v>9</v>
+      </c>
+      <c r="B546" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C546" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D546" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="E546" s="2">
+        <v>59.77</v>
+      </c>
+      <c r="F546" s="3">
+        <v>0.067</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6">
+      <c r="A547" t="s">
+        <v>9</v>
+      </c>
+      <c r="B547" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C547" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D547" s="2">
+        <v>1.13</v>
+      </c>
+      <c r="E547" s="2">
+        <v>42.78</v>
+      </c>
+      <c r="F547" s="3">
+        <v>0.068</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6">
+      <c r="A548" t="s">
+        <v>9</v>
+      </c>
+      <c r="B548" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C548" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D548" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="E548" s="2">
+        <v>0</v>
+      </c>
+      <c r="F548" s="3">
+        <v>0.086</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6">
+      <c r="A549" t="s">
+        <v>9</v>
+      </c>
+      <c r="B549" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C549" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D549" s="2">
+        <v>1.13</v>
+      </c>
+      <c r="E549" s="2">
+        <v>51.81</v>
+      </c>
+      <c r="F549" s="3">
+        <v>0.068</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6">
+      <c r="A550" t="s">
+        <v>9</v>
+      </c>
+      <c r="B550" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C550" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D550" s="2">
+        <v>1.15</v>
+      </c>
+      <c r="E550" s="2">
+        <v>51.81</v>
+      </c>
+      <c r="F550" s="3">
+        <v>0.069</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6">
+      <c r="A551" t="s">
+        <v>9</v>
+      </c>
+      <c r="B551" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C551" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D551" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="E551" s="2">
+        <v>0</v>
+      </c>
+      <c r="F551" s="3">
+        <v>0.765</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6">
+      <c r="A552" t="s">
+        <v>9</v>
+      </c>
+      <c r="B552" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C552" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D552" s="2">
+        <v>1.09</v>
+      </c>
+      <c r="E552" s="2">
+        <v>0</v>
+      </c>
+      <c r="F552" s="3">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6">
+      <c r="A553" t="s">
+        <v>9</v>
+      </c>
+      <c r="B553" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C553" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D553" s="2">
+        <v>1.09</v>
+      </c>
+      <c r="E553" s="2">
+        <v>61.76</v>
+      </c>
+      <c r="F553" s="3">
+        <v>0.081</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6">
+      <c r="A554" t="s">
+        <v>9</v>
+      </c>
+      <c r="B554" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C554" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D554" s="2">
+        <v>1.11</v>
+      </c>
+      <c r="E554" s="2">
+        <v>0</v>
+      </c>
+      <c r="F554" s="3">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6">
+      <c r="A555" t="s">
+        <v>9</v>
+      </c>
+      <c r="B555" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C555" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D555" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="E555" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="F555" s="3">
+        <v>0.061</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6">
+      <c r="A556" t="s">
+        <v>9</v>
+      </c>
+      <c r="B556" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C556" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D556" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="E556" s="2">
+        <v>0</v>
+      </c>
+      <c r="F556" s="3">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6">
+      <c r="A557" t="s">
+        <v>9</v>
+      </c>
+      <c r="B557" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C557" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D557" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="E557" s="2">
+        <v>0</v>
+      </c>
+      <c r="F557" s="3">
+        <v>0.085</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6">
+      <c r="A558" t="s">
+        <v>9</v>
+      </c>
+      <c r="B558" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C558" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D558" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="E558" s="2">
+        <v>0</v>
+      </c>
+      <c r="F558" s="3">
+        <v>0.076</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6">
+      <c r="A559" t="s">
+        <v>9</v>
+      </c>
+      <c r="B559" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C559" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D559" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="E559" s="2">
+        <v>48.72</v>
+      </c>
+      <c r="F559" s="3">
+        <v>0.059</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="27930" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -11581,7 +11581,7 @@
     </row>
     <row r="481" spans="1:6">
       <c r="A481" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B481" s="4" t="s">
         <v>11</v>
@@ -11601,7 +11601,7 @@
     </row>
     <row r="482" spans="1:6">
       <c r="A482" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B482" s="4" t="s">
         <v>12</v>
@@ -11621,7 +11621,7 @@
     </row>
     <row r="483" spans="1:6">
       <c r="A483" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B483" s="4" t="s">
         <v>13</v>
@@ -11641,7 +11641,7 @@
     </row>
     <row r="484" spans="1:6">
       <c r="A484" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B484" s="4" t="s">
         <v>14</v>
@@ -11661,7 +11661,7 @@
     </row>
     <row r="485" spans="1:6">
       <c r="A485" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B485" s="4" t="s">
         <v>15</v>
@@ -11681,7 +11681,7 @@
     </row>
     <row r="486" spans="1:6">
       <c r="A486" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B486" s="4" t="s">
         <v>16</v>
@@ -11701,7 +11701,7 @@
     </row>
     <row r="487" spans="1:6">
       <c r="A487" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B487" s="4" t="s">
         <v>17</v>
@@ -11721,7 +11721,7 @@
     </row>
     <row r="488" spans="1:6">
       <c r="A488" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B488" s="4" t="s">
         <v>18</v>
@@ -11735,7 +11735,7 @@
     </row>
     <row r="489" spans="1:6">
       <c r="A489" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B489" s="4" t="s">
         <v>19</v>
@@ -11755,7 +11755,7 @@
     </row>
     <row r="490" spans="1:6">
       <c r="A490" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B490" s="4" t="s">
         <v>20</v>
@@ -11775,7 +11775,7 @@
     </row>
     <row r="491" spans="1:6">
       <c r="A491" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B491" s="4" t="s">
         <v>21</v>
@@ -11795,7 +11795,7 @@
     </row>
     <row r="492" spans="1:6">
       <c r="A492" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B492" s="4" t="s">
         <v>22</v>
@@ -11815,7 +11815,7 @@
     </row>
     <row r="493" spans="1:6">
       <c r="A493" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B493" s="4" t="s">
         <v>23</v>
@@ -11835,7 +11835,7 @@
     </row>
     <row r="494" spans="1:6">
       <c r="A494" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B494" s="4" t="s">
         <v>24</v>
@@ -11855,7 +11855,7 @@
     </row>
     <row r="495" spans="1:6">
       <c r="A495" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B495" s="4" t="s">
         <v>25</v>
@@ -11869,7 +11869,7 @@
     </row>
     <row r="496" spans="1:6">
       <c r="A496" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B496" s="4" t="s">
         <v>26</v>
@@ -11989,7 +11989,7 @@
     </row>
     <row r="502" spans="1:6">
       <c r="A502" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B502" s="4" t="s">
         <v>11</v>
@@ -12009,7 +12009,7 @@
     </row>
     <row r="503" spans="1:6">
       <c r="A503" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B503" s="4" t="s">
         <v>12</v>
@@ -12029,7 +12029,7 @@
     </row>
     <row r="504" spans="1:6">
       <c r="A504" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B504" s="4" t="s">
         <v>13</v>
@@ -12049,7 +12049,7 @@
     </row>
     <row r="505" spans="1:6">
       <c r="A505" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B505" s="4" t="s">
         <v>14</v>
@@ -12069,7 +12069,7 @@
     </row>
     <row r="506" spans="1:6">
       <c r="A506" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B506" s="4" t="s">
         <v>15</v>
@@ -12089,7 +12089,7 @@
     </row>
     <row r="507" spans="1:6">
       <c r="A507" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B507" s="4" t="s">
         <v>16</v>
@@ -12109,7 +12109,7 @@
     </row>
     <row r="508" spans="1:6">
       <c r="A508" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B508" s="4" t="s">
         <v>17</v>
@@ -12129,7 +12129,7 @@
     </row>
     <row r="509" spans="1:6">
       <c r="A509" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B509" s="4" t="s">
         <v>18</v>
@@ -12149,7 +12149,7 @@
     </row>
     <row r="510" spans="1:6">
       <c r="A510" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B510" s="4" t="s">
         <v>19</v>
@@ -12169,7 +12169,7 @@
     </row>
     <row r="511" spans="1:6">
       <c r="A511" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B511" s="4" t="s">
         <v>20</v>
@@ -12189,7 +12189,7 @@
     </row>
     <row r="512" spans="1:6">
       <c r="A512" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B512" s="4" t="s">
         <v>21</v>
@@ -12209,7 +12209,7 @@
     </row>
     <row r="513" spans="1:6">
       <c r="A513" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B513" s="4" t="s">
         <v>22</v>
@@ -12229,7 +12229,7 @@
     </row>
     <row r="514" spans="1:6">
       <c r="A514" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B514" s="4" t="s">
         <v>23</v>
@@ -12249,7 +12249,7 @@
     </row>
     <row r="515" spans="1:6">
       <c r="A515" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B515" s="4" t="s">
         <v>24</v>
@@ -12269,7 +12269,7 @@
     </row>
     <row r="516" spans="1:6">
       <c r="A516" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B516" s="4" t="s">
         <v>25</v>
@@ -12289,7 +12289,7 @@
     </row>
     <row r="517" spans="1:6">
       <c r="A517" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B517" s="4" t="s">
         <v>26</v>
@@ -12409,7 +12409,7 @@
     </row>
     <row r="523" spans="1:6">
       <c r="A523" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B523" s="4" t="s">
         <v>11</v>
@@ -12429,7 +12429,7 @@
     </row>
     <row r="524" spans="1:6">
       <c r="A524" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B524" s="4" t="s">
         <v>12</v>
@@ -12449,7 +12449,7 @@
     </row>
     <row r="525" spans="1:6">
       <c r="A525" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B525" s="4" t="s">
         <v>13</v>
@@ -12469,7 +12469,7 @@
     </row>
     <row r="526" spans="1:6">
       <c r="A526" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B526" s="4" t="s">
         <v>14</v>
@@ -12489,7 +12489,7 @@
     </row>
     <row r="527" spans="1:6">
       <c r="A527" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B527" s="4" t="s">
         <v>15</v>
@@ -12509,7 +12509,7 @@
     </row>
     <row r="528" spans="1:6">
       <c r="A528" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B528" s="4" t="s">
         <v>16</v>
@@ -12529,7 +12529,7 @@
     </row>
     <row r="529" spans="1:6">
       <c r="A529" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B529" s="4" t="s">
         <v>17</v>
@@ -12549,7 +12549,7 @@
     </row>
     <row r="530" spans="1:6">
       <c r="A530" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B530" s="4" t="s">
         <v>18</v>
@@ -12569,7 +12569,7 @@
     </row>
     <row r="531" spans="1:6">
       <c r="A531" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B531" s="4" t="s">
         <v>19</v>
@@ -12589,7 +12589,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B532" s="4" t="s">
         <v>20</v>
@@ -12609,7 +12609,7 @@
     </row>
     <row r="533" spans="1:6">
       <c r="A533" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B533" s="4" t="s">
         <v>21</v>
@@ -12629,7 +12629,7 @@
     </row>
     <row r="534" spans="1:6">
       <c r="A534" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B534" s="4" t="s">
         <v>22</v>
@@ -12649,7 +12649,7 @@
     </row>
     <row r="535" spans="1:6">
       <c r="A535" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B535" s="4" t="s">
         <v>23</v>
@@ -12669,7 +12669,7 @@
     </row>
     <row r="536" spans="1:6">
       <c r="A536" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B536" s="4" t="s">
         <v>24</v>
@@ -12689,7 +12689,7 @@
     </row>
     <row r="537" spans="1:6">
       <c r="A537" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B537" s="4" t="s">
         <v>25</v>
@@ -12709,7 +12709,7 @@
     </row>
     <row r="538" spans="1:6">
       <c r="A538" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B538" s="4" t="s">
         <v>26</v>
@@ -12829,7 +12829,7 @@
     </row>
     <row r="544" spans="1:6">
       <c r="A544" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B544" s="4" t="s">
         <v>11</v>
@@ -12849,7 +12849,7 @@
     </row>
     <row r="545" spans="1:6">
       <c r="A545" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B545" s="4" t="s">
         <v>12</v>
@@ -12869,7 +12869,7 @@
     </row>
     <row r="546" spans="1:6">
       <c r="A546" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B546" s="4" t="s">
         <v>13</v>
@@ -12889,7 +12889,7 @@
     </row>
     <row r="547" spans="1:6">
       <c r="A547" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B547" s="4" t="s">
         <v>14</v>
@@ -12909,7 +12909,7 @@
     </row>
     <row r="548" spans="1:6">
       <c r="A548" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B548" s="4" t="s">
         <v>15</v>
@@ -12929,7 +12929,7 @@
     </row>
     <row r="549" spans="1:6">
       <c r="A549" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B549" s="4" t="s">
         <v>16</v>
@@ -12949,7 +12949,7 @@
     </row>
     <row r="550" spans="1:6">
       <c r="A550" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B550" s="4" t="s">
         <v>17</v>
@@ -12969,7 +12969,7 @@
     </row>
     <row r="551" spans="1:6">
       <c r="A551" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B551" s="4" t="s">
         <v>18</v>
@@ -12989,7 +12989,7 @@
     </row>
     <row r="552" spans="1:6">
       <c r="A552" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B552" s="4" t="s">
         <v>19</v>
@@ -13009,7 +13009,7 @@
     </row>
     <row r="553" spans="1:6">
       <c r="A553" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B553" s="4" t="s">
         <v>20</v>
@@ -13029,7 +13029,7 @@
     </row>
     <row r="554" spans="1:6">
       <c r="A554" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B554" s="4" t="s">
         <v>21</v>
@@ -13049,7 +13049,7 @@
     </row>
     <row r="555" spans="1:6">
       <c r="A555" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B555" s="4" t="s">
         <v>22</v>
@@ -13069,7 +13069,7 @@
     </row>
     <row r="556" spans="1:6">
       <c r="A556" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B556" s="4" t="s">
         <v>23</v>
@@ -13089,7 +13089,7 @@
     </row>
     <row r="557" spans="1:6">
       <c r="A557" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B557" s="4" t="s">
         <v>24</v>
@@ -13109,7 +13109,7 @@
     </row>
     <row r="558" spans="1:6">
       <c r="A558" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B558" s="4" t="s">
         <v>25</v>
@@ -13129,7 +13129,7 @@
     </row>
     <row r="559" spans="1:6">
       <c r="A559" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B559" s="4" t="s">
         <v>26</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="14">
   <si>
     <t>抽采地点</t>
   </si>
@@ -61,57 +61,6 @@
   </si>
   <si>
     <t>12803回风巷</t>
-  </si>
-  <si>
-    <t>12803回风巷高位钻孔</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>1-6</t>
-  </si>
-  <si>
-    <t>1-7</t>
-  </si>
-  <si>
-    <t>1-8</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>2-5</t>
-  </si>
-  <si>
-    <t>2-6</t>
-  </si>
-  <si>
-    <t>2-7</t>
-  </si>
-  <si>
-    <t>2-8</t>
   </si>
   <si>
     <t>检测日期</t>
@@ -742,7 +691,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -753,12 +702,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1286,7 +1229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.625" customWidth="1"/>
@@ -1468,499 +1411,35 @@
         <v>0.468</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>65</v>
-      </c>
-      <c r="D7">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>66</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G7" s="2">
-        <v>4.2</v>
-      </c>
-      <c r="H7" s="2">
-        <v>40.07</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0.142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-      <c r="D8">
-        <v>115</v>
-      </c>
-      <c r="E8">
-        <v>78</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G8" s="2">
-        <v>2.2</v>
-      </c>
-      <c r="H8" s="2">
-        <v>40.15</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0.252</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>37</v>
-      </c>
-      <c r="D9">
-        <v>14</v>
-      </c>
-      <c r="E9">
-        <v>62</v>
-      </c>
-      <c r="F9" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H9" s="2">
-        <v>40.02</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0.386</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
-        <v>27</v>
-      </c>
-      <c r="D10">
-        <v>14</v>
-      </c>
-      <c r="E10">
-        <v>62</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G10" s="2">
-        <v>4.4</v>
-      </c>
-      <c r="H10" s="2">
-        <v>40.12</v>
-      </c>
-      <c r="I10" s="5">
-        <v>0.219</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>19</v>
-      </c>
-      <c r="D11">
-        <v>13</v>
-      </c>
-      <c r="E11">
-        <v>78</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G11" s="2">
-        <v>2.6</v>
-      </c>
-      <c r="H11" s="2">
-        <v>40.11</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0.189</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
-        <v>13</v>
-      </c>
-      <c r="D12">
-        <v>13</v>
-      </c>
-      <c r="E12">
-        <v>52</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="H12" s="2">
-        <v>40.15</v>
-      </c>
-      <c r="I12" s="5">
-        <v>0.152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13">
-        <v>8</v>
-      </c>
-      <c r="D13">
-        <v>12</v>
-      </c>
-      <c r="E13">
-        <v>61</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H13" s="2">
-        <v>40.13</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0.327</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>12</v>
-      </c>
-      <c r="E14">
-        <v>58</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="H14" s="2">
-        <v>40.1</v>
-      </c>
-      <c r="I14" s="5">
-        <v>0.203</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15">
-        <v>65</v>
-      </c>
-      <c r="D15">
-        <v>20</v>
-      </c>
-      <c r="E15">
-        <v>86</v>
-      </c>
-      <c r="F15" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H15" s="2">
-        <v>40.16</v>
-      </c>
-      <c r="I15" s="5">
-        <v>0.359</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16">
-        <v>50</v>
-      </c>
-      <c r="D16">
-        <v>19</v>
-      </c>
-      <c r="E16">
-        <v>64</v>
-      </c>
-      <c r="F16" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G16" s="2">
-        <v>4.6</v>
-      </c>
-      <c r="H16" s="2">
-        <v>40.16</v>
-      </c>
-      <c r="I16" s="5">
-        <v>0.157</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17">
-        <v>37</v>
-      </c>
-      <c r="D17">
-        <v>14</v>
-      </c>
-      <c r="E17">
-        <v>66</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G17" s="2">
-        <v>2.8</v>
-      </c>
-      <c r="H17" s="2">
-        <v>40.2</v>
-      </c>
-      <c r="I17" s="5">
-        <v>0.172</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18">
-        <v>27</v>
-      </c>
-      <c r="D18">
-        <v>14</v>
-      </c>
-      <c r="E18">
-        <v>86</v>
-      </c>
-      <c r="F18" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G18" s="2">
-        <v>13.4</v>
-      </c>
-      <c r="H18" s="2">
-        <v>40.19</v>
-      </c>
-      <c r="I18" s="5">
-        <v>0.202</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19">
-        <v>18</v>
-      </c>
-      <c r="D19">
-        <v>17</v>
-      </c>
-      <c r="E19">
-        <v>86</v>
-      </c>
-      <c r="F19" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H19" s="2">
-        <v>40.18</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0.294</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20">
-        <v>13</v>
-      </c>
-      <c r="D20">
-        <v>17</v>
-      </c>
-      <c r="E20">
-        <v>84</v>
-      </c>
-      <c r="F20" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G20" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="H20" s="2">
-        <v>40.16</v>
-      </c>
-      <c r="I20" s="5">
-        <v>0.162</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21">
-        <v>8</v>
-      </c>
-      <c r="D21">
-        <v>12</v>
-      </c>
-      <c r="E21">
-        <v>86</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="H21" s="2">
-        <v>40.18</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0.284</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22">
-        <v>16</v>
-      </c>
-      <c r="E22">
-        <v>26</v>
-      </c>
-      <c r="F22" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G22" s="2">
-        <v>48.6</v>
-      </c>
-      <c r="H22" s="2">
-        <v>40.25</v>
-      </c>
-      <c r="I22" s="5">
-        <v>0.104</v>
-      </c>
-    </row>
-    <row r="23" spans="6:6">
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="6:6">
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="6:6">
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="6:6">
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="6:6">
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="6:6">
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="6:6">
-      <c r="F29" s="1"/>
-    </row>
-    <row r="30" spans="6:6">
-      <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="6:6">
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="6:6">
-      <c r="F32" s="1"/>
+    <row r="7" spans="6:6">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="6:6">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="6:6">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="6:6">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="6:6">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="6:6">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="6:6">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="6:6">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="6:6">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="6:6">
+      <c r="F16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1971,7 +1450,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F559"/>
+  <dimension ref="A1:F575"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1987,16 +1466,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -11581,310 +11060,322 @@
     </row>
     <row r="481" spans="1:6">
       <c r="A481" t="s">
-        <v>10</v>
-      </c>
-      <c r="B481" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="B481">
+        <v>1</v>
       </c>
       <c r="C481" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D481" s="2">
-        <v>3.07</v>
+        <v>34.83</v>
       </c>
       <c r="E481" s="2">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="F481" s="3">
-        <v>0.114</v>
+        <v>1.131</v>
       </c>
     </row>
     <row r="482" spans="1:6">
       <c r="A482" t="s">
-        <v>10</v>
-      </c>
-      <c r="B482" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="B482">
+        <v>2</v>
       </c>
       <c r="C482" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D482" s="2">
-        <v>3.06</v>
+        <v>34.84</v>
       </c>
       <c r="E482" s="2">
-        <v>0</v>
+        <v>28.53</v>
       </c>
       <c r="F482" s="3">
-        <v>0.142</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="483" spans="1:6">
       <c r="A483" t="s">
-        <v>10</v>
-      </c>
-      <c r="B483" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="B483">
+        <v>3</v>
       </c>
       <c r="C483" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D483" s="2">
-        <v>3.02</v>
+        <v>34.83</v>
       </c>
       <c r="E483" s="2">
         <v>0</v>
       </c>
       <c r="F483" s="3">
-        <v>0.127</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="484" spans="1:6">
       <c r="A484" t="s">
-        <v>10</v>
-      </c>
-      <c r="B484" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="B484">
+        <v>4</v>
       </c>
       <c r="C484" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D484" s="2">
-        <v>3.09</v>
+        <v>34.81</v>
       </c>
       <c r="E484" s="2">
-        <v>43.67</v>
+        <v>3.26</v>
       </c>
       <c r="F484" s="3">
-        <v>0.136</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="485" spans="1:6">
       <c r="A485" t="s">
-        <v>10</v>
-      </c>
-      <c r="B485" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="B485">
+        <v>5</v>
       </c>
       <c r="C485" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D485" s="2">
-        <v>3.05</v>
+        <v>34.85</v>
       </c>
       <c r="E485" s="2">
-        <v>0</v>
+        <v>39.85</v>
       </c>
       <c r="F485" s="3">
-        <v>0.182</v>
+        <v>0.564</v>
       </c>
     </row>
     <row r="486" spans="1:6">
       <c r="A486" t="s">
-        <v>10</v>
-      </c>
-      <c r="B486" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="B486">
+        <v>1</v>
       </c>
       <c r="C486" s="1">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="D486" s="2">
-        <v>3.05</v>
+        <v>33.79</v>
       </c>
       <c r="E486" s="2">
         <v>0</v>
       </c>
       <c r="F486" s="3">
-        <v>0.213</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="487" spans="1:6">
       <c r="A487" t="s">
-        <v>10</v>
-      </c>
-      <c r="B487" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="B487">
+        <v>2</v>
       </c>
       <c r="C487" s="1">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="D487" s="2">
-        <v>3.07</v>
+        <v>33.78</v>
       </c>
       <c r="E487" s="2">
-        <v>0</v>
+        <v>33.78</v>
       </c>
       <c r="F487" s="3">
-        <v>0.243</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="488" spans="1:6">
       <c r="A488" t="s">
-        <v>10</v>
-      </c>
-      <c r="B488" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="B488">
+        <v>3</v>
       </c>
       <c r="C488" s="1">
-        <v>46243</v>
-      </c>
-      <c r="D488" s="2"/>
-      <c r="E488" s="2"/>
-      <c r="F488" s="3"/>
+        <v>46245</v>
+      </c>
+      <c r="D488" s="2">
+        <v>33.79</v>
+      </c>
+      <c r="E488" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="F488" s="3">
+        <v>0.737</v>
+      </c>
     </row>
     <row r="489" spans="1:6">
       <c r="A489" t="s">
-        <v>10</v>
-      </c>
-      <c r="B489" s="4" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="B489">
+        <v>4</v>
       </c>
       <c r="C489" s="1">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="D489" s="2">
-        <v>3.06</v>
+        <v>33.8</v>
       </c>
       <c r="E489" s="2">
-        <v>4.32</v>
+        <v>3.17</v>
       </c>
       <c r="F489" s="3">
-        <v>0.242</v>
+        <v>0.813</v>
       </c>
     </row>
     <row r="490" spans="1:6">
       <c r="A490" t="s">
-        <v>10</v>
-      </c>
-      <c r="B490" s="4" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="B490">
+        <v>5</v>
       </c>
       <c r="C490" s="1">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="D490" s="2">
-        <v>3.07</v>
+        <v>33.82</v>
       </c>
       <c r="E490" s="2">
-        <v>8.65</v>
+        <v>39.15</v>
       </c>
       <c r="F490" s="3">
-        <v>0.281</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="491" spans="1:6">
       <c r="A491" t="s">
-        <v>10</v>
-      </c>
-      <c r="B491" s="4" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B491">
+        <v>1</v>
       </c>
       <c r="C491" s="1">
-        <v>46243</v>
+        <v>46246</v>
       </c>
       <c r="D491" s="2">
-        <v>3.06</v>
+        <v>30.76</v>
       </c>
       <c r="E491" s="2">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="F491" s="3">
-        <v>0.269</v>
+        <v>1.067</v>
       </c>
     </row>
     <row r="492" spans="1:6">
       <c r="A492" t="s">
-        <v>10</v>
-      </c>
-      <c r="B492" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="B492">
+        <v>2</v>
       </c>
       <c r="C492" s="1">
-        <v>46243</v>
+        <v>46246</v>
       </c>
       <c r="D492" s="2">
-        <v>3.04</v>
+        <v>30.78</v>
       </c>
       <c r="E492" s="2">
-        <v>0</v>
+        <v>26.57</v>
       </c>
       <c r="F492" s="3">
-        <v>0.279</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="493" spans="1:6">
       <c r="A493" t="s">
-        <v>10</v>
-      </c>
-      <c r="B493" s="4" t="s">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="B493">
+        <v>3</v>
       </c>
       <c r="C493" s="1">
-        <v>46243</v>
+        <v>46246</v>
       </c>
       <c r="D493" s="2">
-        <v>3.05</v>
+        <v>30.76</v>
       </c>
       <c r="E493" s="2">
         <v>0</v>
       </c>
       <c r="F493" s="3">
-        <v>0.224</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="494" spans="1:6">
       <c r="A494" t="s">
-        <v>10</v>
-      </c>
-      <c r="B494" s="4" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+      <c r="B494">
+        <v>4</v>
       </c>
       <c r="C494" s="1">
-        <v>46243</v>
+        <v>46246</v>
       </c>
       <c r="D494" s="2">
-        <v>3.01</v>
+        <v>30.77</v>
       </c>
       <c r="E494" s="2">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="F494" s="3">
-        <v>0.166</v>
+        <v>1.066</v>
       </c>
     </row>
     <row r="495" spans="1:6">
       <c r="A495" t="s">
-        <v>10</v>
-      </c>
-      <c r="B495" s="4" t="s">
-        <v>25</v>
+        <v>9</v>
+      </c>
+      <c r="B495">
+        <v>5</v>
       </c>
       <c r="C495" s="1">
-        <v>46243</v>
-      </c>
-      <c r="D495" s="2"/>
-      <c r="E495" s="2"/>
-      <c r="F495" s="3"/>
+        <v>46246</v>
+      </c>
+      <c r="D495" s="2">
+        <v>30.77</v>
+      </c>
+      <c r="E495" s="2">
+        <v>33.1</v>
+      </c>
+      <c r="F495" s="3">
+        <v>0.674</v>
+      </c>
     </row>
     <row r="496" spans="1:6">
       <c r="A496" t="s">
-        <v>10</v>
-      </c>
-      <c r="B496" s="4" t="s">
-        <v>26</v>
+        <v>9</v>
+      </c>
+      <c r="B496">
+        <v>1</v>
       </c>
       <c r="C496" s="1">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="D496" s="2">
-        <v>3.09</v>
+        <v>34.22</v>
       </c>
       <c r="E496" s="2">
-        <v>81.12</v>
+        <v>0</v>
       </c>
       <c r="F496" s="3">
-        <v>0.154</v>
+        <v>1.646</v>
       </c>
     </row>
     <row r="497" spans="1:6">
@@ -11892,19 +11383,19 @@
         <v>9</v>
       </c>
       <c r="B497">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C497" s="1">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="D497" s="2">
-        <v>34.83</v>
+        <v>34.19</v>
       </c>
       <c r="E497" s="2">
-        <v>0</v>
+        <v>30.38</v>
       </c>
       <c r="F497" s="3">
-        <v>1.131</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="498" spans="1:6">
@@ -11912,19 +11403,19 @@
         <v>9</v>
       </c>
       <c r="B498">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C498" s="1">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="D498" s="2">
-        <v>34.84</v>
+        <v>34.16</v>
       </c>
       <c r="E498" s="2">
-        <v>28.53</v>
+        <v>0.89</v>
       </c>
       <c r="F498" s="3">
-        <v>0.645</v>
+        <v>0.807</v>
       </c>
     </row>
     <row r="499" spans="1:6">
@@ -11932,19 +11423,19 @@
         <v>9</v>
       </c>
       <c r="B499">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C499" s="1">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="D499" s="2">
-        <v>34.83</v>
+        <v>34.22</v>
       </c>
       <c r="E499" s="2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="F499" s="3">
-        <v>0.626</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="500" spans="1:6">
@@ -11952,19 +11443,19 @@
         <v>9</v>
       </c>
       <c r="B500">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C500" s="1">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="D500" s="2">
-        <v>34.81</v>
+        <v>34.2</v>
       </c>
       <c r="E500" s="2">
-        <v>3.26</v>
+        <v>40.74</v>
       </c>
       <c r="F500" s="3">
-        <v>1.042</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="501" spans="1:6">
@@ -11972,339 +11463,339 @@
         <v>9</v>
       </c>
       <c r="B501">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C501" s="1">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="D501" s="2">
-        <v>34.85</v>
+        <v>43.24</v>
       </c>
       <c r="E501" s="2">
-        <v>39.85</v>
+        <v>0</v>
       </c>
       <c r="F501" s="3">
-        <v>0.564</v>
+        <v>1.128</v>
       </c>
     </row>
     <row r="502" spans="1:6">
       <c r="A502" t="s">
-        <v>10</v>
-      </c>
-      <c r="B502" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="B502">
+        <v>2</v>
       </c>
       <c r="C502" s="1">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="D502" s="2">
-        <v>2.92</v>
+        <v>43.68</v>
       </c>
       <c r="E502" s="2">
-        <v>7.82</v>
+        <v>31.27</v>
       </c>
       <c r="F502" s="3">
-        <v>0.245</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="503" spans="1:6">
       <c r="A503" t="s">
-        <v>10</v>
-      </c>
-      <c r="B503" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="B503">
+        <v>3</v>
       </c>
       <c r="C503" s="1">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="D503" s="2">
-        <v>2.99</v>
+        <v>43.25</v>
       </c>
       <c r="E503" s="2">
         <v>0</v>
       </c>
       <c r="F503" s="3">
-        <v>0.148</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="504" spans="1:6">
       <c r="A504" t="s">
-        <v>10</v>
-      </c>
-      <c r="B504" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="B504">
+        <v>4</v>
       </c>
       <c r="C504" s="1">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="D504" s="2">
-        <v>2.8</v>
+        <v>43.25</v>
       </c>
       <c r="E504" s="2">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="F504" s="3">
-        <v>0.082</v>
+        <v>0.811</v>
       </c>
     </row>
     <row r="505" spans="1:6">
       <c r="A505" t="s">
-        <v>10</v>
-      </c>
-      <c r="B505" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="B505">
+        <v>5</v>
       </c>
       <c r="C505" s="1">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="D505" s="2">
-        <v>2.96</v>
+        <v>43.25</v>
       </c>
       <c r="E505" s="2">
-        <v>33.98</v>
+        <v>33.57</v>
       </c>
       <c r="F505" s="3">
-        <v>0.082</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="506" spans="1:6">
       <c r="A506" t="s">
-        <v>10</v>
-      </c>
-      <c r="B506" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="B506">
+        <v>1</v>
       </c>
       <c r="C506" s="1">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="D506" s="2">
-        <v>2.91</v>
+        <v>44.96</v>
       </c>
       <c r="E506" s="2">
         <v>0</v>
       </c>
       <c r="F506" s="3">
-        <v>0.195</v>
+        <v>1.085</v>
       </c>
     </row>
     <row r="507" spans="1:6">
       <c r="A507" t="s">
-        <v>10</v>
-      </c>
-      <c r="B507" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="B507">
+        <v>2</v>
       </c>
       <c r="C507" s="1">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="D507" s="2">
-        <v>2.84</v>
+        <v>44.97</v>
       </c>
       <c r="E507" s="2">
-        <v>0.31</v>
+        <v>20.8</v>
       </c>
       <c r="F507" s="3">
-        <v>0.138</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="508" spans="1:6">
       <c r="A508" t="s">
-        <v>10</v>
-      </c>
-      <c r="B508" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="B508">
+        <v>3</v>
       </c>
       <c r="C508" s="1">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="D508" s="2">
-        <v>2.93</v>
+        <v>44.94</v>
       </c>
       <c r="E508" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F508" s="3">
-        <v>0.248</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="509" spans="1:6">
       <c r="A509" t="s">
-        <v>10</v>
-      </c>
-      <c r="B509" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="B509">
+        <v>4</v>
       </c>
       <c r="C509" s="1">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="D509" s="2">
-        <v>2.78</v>
+        <v>44.92</v>
       </c>
       <c r="E509" s="2">
         <v>0</v>
       </c>
       <c r="F509" s="3">
-        <v>1.534</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="510" spans="1:6">
       <c r="A510" t="s">
-        <v>10</v>
-      </c>
-      <c r="B510" s="4" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="B510">
+        <v>5</v>
       </c>
       <c r="C510" s="1">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="D510" s="2">
-        <v>2.99</v>
+        <v>44.96</v>
       </c>
       <c r="E510" s="2">
-        <v>2.83</v>
+        <v>16.4</v>
       </c>
       <c r="F510" s="3">
-        <v>0.27</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="511" spans="1:6">
       <c r="A511" t="s">
-        <v>10</v>
-      </c>
-      <c r="B511" s="4" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="B511">
+        <v>1</v>
       </c>
       <c r="C511" s="1">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="D511" s="2">
-        <v>2.85</v>
+        <v>42.86</v>
       </c>
       <c r="E511" s="2">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="F511" s="3">
-        <v>0.152</v>
+        <v>1.146</v>
       </c>
     </row>
     <row r="512" spans="1:6">
       <c r="A512" t="s">
-        <v>10</v>
-      </c>
-      <c r="B512" s="4" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B512">
+        <v>2</v>
       </c>
       <c r="C512" s="1">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="D512" s="2">
-        <v>2.99</v>
+        <v>42.87</v>
       </c>
       <c r="E512" s="2">
-        <v>10.08</v>
+        <v>26.44</v>
       </c>
       <c r="F512" s="3">
-        <v>0.171</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="513" spans="1:6">
       <c r="A513" t="s">
-        <v>10</v>
-      </c>
-      <c r="B513" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="B513">
+        <v>3</v>
       </c>
       <c r="C513" s="1">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="D513" s="2">
-        <v>2.84</v>
+        <v>42.82</v>
       </c>
       <c r="E513" s="2">
-        <v>0.62</v>
+        <v>0.43</v>
       </c>
       <c r="F513" s="3">
-        <v>0.125</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="514" spans="1:6">
       <c r="A514" t="s">
-        <v>10</v>
-      </c>
-      <c r="B514" s="4" t="s">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="B514">
+        <v>4</v>
       </c>
       <c r="C514" s="1">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="D514" s="2">
-        <v>2.84</v>
+        <v>42.81</v>
       </c>
       <c r="E514" s="2">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="F514" s="3">
-        <v>0.143</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="515" spans="1:6">
       <c r="A515" t="s">
-        <v>10</v>
-      </c>
-      <c r="B515" s="4" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+      <c r="B515">
+        <v>5</v>
       </c>
       <c r="C515" s="1">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="D515" s="2">
-        <v>2.94</v>
+        <v>42.83</v>
       </c>
       <c r="E515" s="2">
-        <v>0</v>
+        <v>20.63</v>
       </c>
       <c r="F515" s="3">
-        <v>0.205</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="516" spans="1:6">
       <c r="A516" t="s">
-        <v>10</v>
-      </c>
-      <c r="B516" s="4" t="s">
-        <v>25</v>
+        <v>9</v>
+      </c>
+      <c r="B516">
+        <v>1</v>
       </c>
       <c r="C516" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="D516" s="2">
-        <v>2.99</v>
+        <v>48.27</v>
       </c>
       <c r="E516" s="2">
         <v>0</v>
       </c>
       <c r="F516" s="3">
-        <v>0.957</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="517" spans="1:6">
       <c r="A517" t="s">
-        <v>10</v>
-      </c>
-      <c r="B517" s="4" t="s">
-        <v>26</v>
+        <v>9</v>
+      </c>
+      <c r="B517">
+        <v>2</v>
       </c>
       <c r="C517" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="D517" s="2">
-        <v>2.99</v>
+        <v>48.25</v>
       </c>
       <c r="E517" s="2">
-        <v>72.46</v>
+        <v>18.2</v>
       </c>
       <c r="F517" s="3">
-        <v>0.571</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="518" spans="1:6">
@@ -12312,19 +11803,19 @@
         <v>9</v>
       </c>
       <c r="B518">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C518" s="1">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="D518" s="2">
-        <v>33.79</v>
+        <v>48.27</v>
       </c>
       <c r="E518" s="2">
         <v>0</v>
       </c>
       <c r="F518" s="3">
-        <v>0.548</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="519" spans="1:6">
@@ -12332,19 +11823,19 @@
         <v>9</v>
       </c>
       <c r="B519">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C519" s="1">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="D519" s="2">
-        <v>33.78</v>
+        <v>48.24</v>
       </c>
       <c r="E519" s="2">
-        <v>33.78</v>
+        <v>0</v>
       </c>
       <c r="F519" s="3">
-        <v>0.716</v>
+        <v>0.937</v>
       </c>
     </row>
     <row r="520" spans="1:6">
@@ -12352,19 +11843,19 @@
         <v>9</v>
       </c>
       <c r="B520">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C520" s="1">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="D520" s="2">
-        <v>33.79</v>
+        <v>48.22</v>
       </c>
       <c r="E520" s="2">
-        <v>0.18</v>
+        <v>23.4</v>
       </c>
       <c r="F520" s="3">
-        <v>0.737</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="521" spans="1:6">
@@ -12372,19 +11863,19 @@
         <v>9</v>
       </c>
       <c r="B521">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C521" s="1">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="D521" s="2">
-        <v>33.8</v>
+        <v>56.18</v>
       </c>
       <c r="E521" s="2">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="F521" s="3">
-        <v>0.813</v>
+        <v>1.136</v>
       </c>
     </row>
     <row r="522" spans="1:6">
@@ -12392,339 +11883,339 @@
         <v>9</v>
       </c>
       <c r="B522">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C522" s="1">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="D522" s="2">
-        <v>33.82</v>
+        <v>56.15</v>
       </c>
       <c r="E522" s="2">
-        <v>39.15</v>
+        <v>26.36</v>
       </c>
       <c r="F522" s="3">
-        <v>0.832</v>
+        <v>0.764</v>
       </c>
     </row>
     <row r="523" spans="1:6">
       <c r="A523" t="s">
-        <v>10</v>
-      </c>
-      <c r="B523" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="B523">
+        <v>3</v>
       </c>
       <c r="C523" s="1">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="D523" s="2">
-        <v>3.04</v>
+        <v>56.17</v>
       </c>
       <c r="E523" s="2">
-        <v>13.6</v>
+        <v>0.83</v>
       </c>
       <c r="F523" s="3">
-        <v>0.126</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="524" spans="1:6">
       <c r="A524" t="s">
-        <v>10</v>
-      </c>
-      <c r="B524" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="B524">
+        <v>4</v>
       </c>
       <c r="C524" s="1">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="D524" s="2">
-        <v>3.05</v>
+        <v>56.14</v>
       </c>
       <c r="E524" s="2">
-        <v>0</v>
+        <v>9.46</v>
       </c>
       <c r="F524" s="3">
-        <v>0.125</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="525" spans="1:6">
       <c r="A525" t="s">
-        <v>10</v>
-      </c>
-      <c r="B525" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="B525">
+        <v>5</v>
       </c>
       <c r="C525" s="1">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="D525" s="2">
-        <v>3.05</v>
+        <v>56.12</v>
       </c>
       <c r="E525" s="2">
-        <v>0</v>
+        <v>34.46</v>
       </c>
       <c r="F525" s="3">
-        <v>0.133</v>
+        <v>0.688</v>
       </c>
     </row>
     <row r="526" spans="1:6">
       <c r="A526" t="s">
-        <v>10</v>
-      </c>
-      <c r="B526" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="B526">
+        <v>1</v>
       </c>
       <c r="C526" s="1">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="D526" s="2">
-        <v>3.05</v>
+        <v>27.94</v>
       </c>
       <c r="E526" s="2">
-        <v>34.26</v>
+        <v>0</v>
       </c>
       <c r="F526" s="3">
-        <v>0.144</v>
+        <v>1.184</v>
       </c>
     </row>
     <row r="527" spans="1:6">
       <c r="A527" t="s">
-        <v>10</v>
-      </c>
-      <c r="B527" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="B527">
+        <v>2</v>
       </c>
       <c r="C527" s="1">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="D527" s="2">
-        <v>3.04</v>
+        <v>27.95</v>
       </c>
       <c r="E527" s="2">
-        <v>0</v>
+        <v>20.43</v>
       </c>
       <c r="F527" s="3">
-        <v>0.175</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="528" spans="1:6">
       <c r="A528" t="s">
-        <v>10</v>
-      </c>
-      <c r="B528" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="B528">
+        <v>3</v>
       </c>
       <c r="C528" s="1">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="D528" s="2">
-        <v>3.08</v>
+        <v>27.94</v>
       </c>
       <c r="E528" s="2">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="F528" s="3">
-        <v>0.208</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="529" spans="1:6">
       <c r="A529" t="s">
-        <v>10</v>
-      </c>
-      <c r="B529" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="B529">
+        <v>4</v>
       </c>
       <c r="C529" s="1">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="D529" s="2">
-        <v>3.09</v>
+        <v>27.98</v>
       </c>
       <c r="E529" s="2">
-        <v>0</v>
+        <v>7.68</v>
       </c>
       <c r="F529" s="3">
-        <v>0.237</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="530" spans="1:6">
       <c r="A530" t="s">
-        <v>10</v>
-      </c>
-      <c r="B530" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="B530">
+        <v>5</v>
       </c>
       <c r="C530" s="1">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="D530" s="2">
-        <v>3.04</v>
+        <v>27.96</v>
       </c>
       <c r="E530" s="2">
-        <v>0</v>
+        <v>30.56</v>
       </c>
       <c r="F530" s="3">
-        <v>0.178</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="531" spans="1:6">
       <c r="A531" t="s">
-        <v>10</v>
-      </c>
-      <c r="B531" s="4" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="B531">
+        <v>1</v>
       </c>
       <c r="C531" s="1">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="D531" s="2">
-        <v>3.04</v>
+        <v>27.94</v>
       </c>
       <c r="E531" s="2">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="F531" s="3">
-        <v>0.251</v>
+        <v>1.184</v>
       </c>
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>10</v>
-      </c>
-      <c r="B532" s="4" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="B532">
+        <v>2</v>
       </c>
       <c r="C532" s="1">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="D532" s="2">
-        <v>3.05</v>
+        <v>27.95</v>
       </c>
       <c r="E532" s="2">
-        <v>5.77</v>
+        <v>20.43</v>
       </c>
       <c r="F532" s="3">
-        <v>0.233</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="533" spans="1:6">
       <c r="A533" t="s">
-        <v>10</v>
-      </c>
-      <c r="B533" s="4" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B533">
+        <v>3</v>
       </c>
       <c r="C533" s="1">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="D533" s="2">
-        <v>3.02</v>
+        <v>27.94</v>
       </c>
       <c r="E533" s="2">
-        <v>4.37</v>
+        <v>0.84</v>
       </c>
       <c r="F533" s="3">
-        <v>0.273</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="534" spans="1:6">
       <c r="A534" t="s">
-        <v>10</v>
-      </c>
-      <c r="B534" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="B534">
+        <v>4</v>
       </c>
       <c r="C534" s="1">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="D534" s="2">
-        <v>3.07</v>
+        <v>27.98</v>
       </c>
       <c r="E534" s="2">
-        <v>0</v>
+        <v>7.68</v>
       </c>
       <c r="F534" s="3">
-        <v>0.285</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="535" spans="1:6">
       <c r="A535" t="s">
-        <v>10</v>
-      </c>
-      <c r="B535" s="4" t="s">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="B535">
+        <v>5</v>
       </c>
       <c r="C535" s="1">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="D535" s="2">
-        <v>3.04</v>
+        <v>27.96</v>
       </c>
       <c r="E535" s="2">
-        <v>0</v>
+        <v>30.56</v>
       </c>
       <c r="F535" s="3">
-        <v>0.231</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="536" spans="1:6">
       <c r="A536" t="s">
-        <v>10</v>
-      </c>
-      <c r="B536" s="4" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+      <c r="B536">
+        <v>1</v>
       </c>
       <c r="C536" s="1">
-        <v>46245</v>
+        <v>46256</v>
       </c>
       <c r="D536" s="2">
-        <v>3</v>
+        <v>67.78</v>
       </c>
       <c r="E536" s="2">
         <v>0</v>
       </c>
       <c r="F536" s="3">
-        <v>0.158</v>
+        <v>1.321</v>
       </c>
     </row>
     <row r="537" spans="1:6">
       <c r="A537" t="s">
-        <v>10</v>
-      </c>
-      <c r="B537" s="4" t="s">
-        <v>25</v>
+        <v>9</v>
+      </c>
+      <c r="B537">
+        <v>2</v>
       </c>
       <c r="C537" s="1">
-        <v>46245</v>
+        <v>46256</v>
       </c>
       <c r="D537" s="2">
-        <v>3.01</v>
+        <v>67.79</v>
       </c>
       <c r="E537" s="2">
-        <v>0</v>
+        <v>23.15</v>
       </c>
       <c r="F537" s="3">
-        <v>0.166</v>
+        <v>0.813</v>
       </c>
     </row>
     <row r="538" spans="1:6">
       <c r="A538" t="s">
-        <v>10</v>
-      </c>
-      <c r="B538" s="4" t="s">
-        <v>26</v>
+        <v>9</v>
+      </c>
+      <c r="B538">
+        <v>3</v>
       </c>
       <c r="C538" s="1">
-        <v>46245</v>
+        <v>46256</v>
       </c>
       <c r="D538" s="2">
-        <v>3.06</v>
+        <v>68.06</v>
       </c>
       <c r="E538" s="2">
-        <v>70.48</v>
+        <v>4.14</v>
       </c>
       <c r="F538" s="3">
-        <v>0.137</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="539" spans="1:6">
@@ -12732,19 +12223,19 @@
         <v>9</v>
       </c>
       <c r="B539">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C539" s="1">
-        <v>46246</v>
+        <v>46256</v>
       </c>
       <c r="D539" s="2">
-        <v>30.76</v>
+        <v>68.02</v>
       </c>
       <c r="E539" s="2">
-        <v>0</v>
+        <v>8.44</v>
       </c>
       <c r="F539" s="3">
-        <v>1.067</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="540" spans="1:6">
@@ -12752,19 +12243,19 @@
         <v>9</v>
       </c>
       <c r="B540">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C540" s="1">
-        <v>46246</v>
+        <v>46256</v>
       </c>
       <c r="D540" s="2">
-        <v>30.78</v>
+        <v>67.76</v>
       </c>
       <c r="E540" s="2">
-        <v>26.57</v>
+        <v>33.61</v>
       </c>
       <c r="F540" s="3">
-        <v>0.555</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="541" spans="1:6">
@@ -12772,19 +12263,19 @@
         <v>9</v>
       </c>
       <c r="B541">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C541" s="1">
-        <v>46246</v>
+        <v>46257</v>
       </c>
       <c r="D541" s="2">
-        <v>30.76</v>
+        <v>67.78</v>
       </c>
       <c r="E541" s="2">
         <v>0</v>
       </c>
       <c r="F541" s="3">
-        <v>0.681</v>
+        <v>1.321</v>
       </c>
     </row>
     <row r="542" spans="1:6">
@@ -12792,19 +12283,19 @@
         <v>9</v>
       </c>
       <c r="B542">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C542" s="1">
-        <v>46246</v>
+        <v>46257</v>
       </c>
       <c r="D542" s="2">
-        <v>30.77</v>
+        <v>67.79</v>
       </c>
       <c r="E542" s="2">
-        <v>2.86</v>
+        <v>23.15</v>
       </c>
       <c r="F542" s="3">
-        <v>1.066</v>
+        <v>0.813</v>
       </c>
     </row>
     <row r="543" spans="1:6">
@@ -12812,339 +12303,659 @@
         <v>9</v>
       </c>
       <c r="B543">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C543" s="1">
-        <v>46246</v>
+        <v>46257</v>
       </c>
       <c r="D543" s="2">
-        <v>30.77</v>
+        <v>68.06</v>
       </c>
       <c r="E543" s="2">
-        <v>33.1</v>
+        <v>4.14</v>
       </c>
       <c r="F543" s="3">
-        <v>0.674</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="544" spans="1:6">
       <c r="A544" t="s">
-        <v>10</v>
-      </c>
-      <c r="B544" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="B544">
+        <v>4</v>
       </c>
       <c r="C544" s="1">
-        <v>46246</v>
+        <v>46257</v>
       </c>
       <c r="D544" s="2">
-        <v>1.12</v>
+        <v>68.02</v>
       </c>
       <c r="E544" s="2">
-        <v>80.09</v>
+        <v>8.44</v>
       </c>
       <c r="F544" s="3">
-        <v>0.071</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="545" spans="1:6">
       <c r="A545" t="s">
-        <v>10</v>
-      </c>
-      <c r="B545" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="B545">
+        <v>5</v>
       </c>
       <c r="C545" s="1">
-        <v>46246</v>
+        <v>46257</v>
       </c>
       <c r="D545" s="2">
-        <v>1.12</v>
+        <v>67.76</v>
       </c>
       <c r="E545" s="2">
-        <v>0</v>
+        <v>33.61</v>
       </c>
       <c r="F545" s="3">
-        <v>0.072</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="546" spans="1:6">
       <c r="A546" t="s">
-        <v>10</v>
-      </c>
-      <c r="B546" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="B546">
+        <v>1</v>
       </c>
       <c r="C546" s="1">
-        <v>46246</v>
+        <v>46258</v>
       </c>
       <c r="D546" s="2">
-        <v>1.12</v>
+        <v>51.12</v>
       </c>
       <c r="E546" s="2">
-        <v>59.77</v>
+        <v>0</v>
       </c>
       <c r="F546" s="3">
-        <v>0.067</v>
+        <v>2.542</v>
       </c>
     </row>
     <row r="547" spans="1:6">
       <c r="A547" t="s">
-        <v>10</v>
-      </c>
-      <c r="B547" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="B547">
+        <v>2</v>
       </c>
       <c r="C547" s="1">
-        <v>46246</v>
+        <v>46258</v>
       </c>
       <c r="D547" s="2">
-        <v>1.13</v>
+        <v>54.52</v>
       </c>
       <c r="E547" s="2">
-        <v>42.78</v>
+        <v>13.19</v>
       </c>
       <c r="F547" s="3">
-        <v>0.068</v>
+        <v>1.439</v>
       </c>
     </row>
     <row r="548" spans="1:6">
       <c r="A548" t="s">
-        <v>10</v>
-      </c>
-      <c r="B548" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="B548">
+        <v>3</v>
       </c>
       <c r="C548" s="1">
-        <v>46246</v>
+        <v>46258</v>
       </c>
       <c r="D548" s="2">
-        <v>1.12</v>
+        <v>55.37</v>
       </c>
       <c r="E548" s="2">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="F548" s="3">
-        <v>0.086</v>
+        <v>1.861</v>
       </c>
     </row>
     <row r="549" spans="1:6">
       <c r="A549" t="s">
-        <v>10</v>
-      </c>
-      <c r="B549" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="B549">
+        <v>4</v>
       </c>
       <c r="C549" s="1">
-        <v>46246</v>
+        <v>46258</v>
       </c>
       <c r="D549" s="2">
-        <v>1.13</v>
+        <v>53.75</v>
       </c>
       <c r="E549" s="2">
-        <v>51.81</v>
+        <v>3.59</v>
       </c>
       <c r="F549" s="3">
-        <v>0.068</v>
+        <v>2.264</v>
       </c>
     </row>
     <row r="550" spans="1:6">
       <c r="A550" t="s">
-        <v>10</v>
-      </c>
-      <c r="B550" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="B550">
+        <v>5</v>
       </c>
       <c r="C550" s="1">
-        <v>46246</v>
+        <v>46258</v>
       </c>
       <c r="D550" s="2">
-        <v>1.15</v>
+        <v>55.72</v>
       </c>
       <c r="E550" s="2">
-        <v>51.81</v>
+        <v>17.08</v>
       </c>
       <c r="F550" s="3">
-        <v>0.069</v>
+        <v>2.029</v>
       </c>
     </row>
     <row r="551" spans="1:6">
       <c r="A551" t="s">
-        <v>10</v>
-      </c>
-      <c r="B551" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="B551">
+        <v>1</v>
       </c>
       <c r="C551" s="1">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="D551" s="2">
-        <v>1.12</v>
+        <v>33.35</v>
       </c>
       <c r="E551" s="2">
         <v>0</v>
       </c>
       <c r="F551" s="3">
-        <v>0.765</v>
+        <v>1.971</v>
       </c>
     </row>
     <row r="552" spans="1:6">
       <c r="A552" t="s">
-        <v>10</v>
-      </c>
-      <c r="B552" s="4" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="B552">
+        <v>2</v>
       </c>
       <c r="C552" s="1">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="D552" s="2">
-        <v>1.09</v>
+        <v>54.42</v>
       </c>
       <c r="E552" s="2">
-        <v>0</v>
+        <v>16.27</v>
       </c>
       <c r="F552" s="3">
-        <v>0.058</v>
+        <v>1.734</v>
       </c>
     </row>
     <row r="553" spans="1:6">
       <c r="A553" t="s">
-        <v>10</v>
-      </c>
-      <c r="B553" s="4" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="B553">
+        <v>3</v>
       </c>
       <c r="C553" s="1">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="D553" s="2">
-        <v>1.09</v>
+        <v>54.52</v>
       </c>
       <c r="E553" s="2">
-        <v>61.76</v>
+        <v>0.65</v>
       </c>
       <c r="F553" s="3">
-        <v>0.081</v>
+        <v>1.595</v>
       </c>
     </row>
     <row r="554" spans="1:6">
       <c r="A554" t="s">
-        <v>10</v>
-      </c>
-      <c r="B554" s="4" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B554">
+        <v>4</v>
       </c>
       <c r="C554" s="1">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="D554" s="2">
-        <v>1.11</v>
+        <v>52.34</v>
       </c>
       <c r="E554" s="2">
-        <v>0</v>
+        <v>8.48</v>
       </c>
       <c r="F554" s="3">
-        <v>0.041</v>
+        <v>2.796</v>
       </c>
     </row>
     <row r="555" spans="1:6">
       <c r="A555" t="s">
-        <v>10</v>
-      </c>
-      <c r="B555" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="B555">
+        <v>5</v>
       </c>
       <c r="C555" s="1">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="D555" s="2">
-        <v>1.12</v>
+        <v>54.28</v>
       </c>
       <c r="E555" s="2">
-        <v>31.5</v>
+        <v>17.47</v>
       </c>
       <c r="F555" s="3">
-        <v>0.061</v>
+        <v>1.953</v>
       </c>
     </row>
     <row r="556" spans="1:6">
       <c r="A556" t="s">
-        <v>10</v>
-      </c>
-      <c r="B556" s="4" t="s">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="B556">
+        <v>1</v>
       </c>
       <c r="C556" s="1">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="D556" s="2">
-        <v>1.1</v>
+        <v>41.92</v>
       </c>
       <c r="E556" s="2">
         <v>0</v>
       </c>
       <c r="F556" s="3">
-        <v>0.065</v>
+        <v>2.894</v>
       </c>
     </row>
     <row r="557" spans="1:6">
       <c r="A557" t="s">
-        <v>10</v>
-      </c>
-      <c r="B557" s="4" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+      <c r="B557">
+        <v>2</v>
       </c>
       <c r="C557" s="1">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="D557" s="2">
-        <v>1.1</v>
+        <v>41.99</v>
       </c>
       <c r="E557" s="2">
-        <v>0</v>
+        <v>28.86</v>
       </c>
       <c r="F557" s="3">
-        <v>0.085</v>
+        <v>1.665</v>
       </c>
     </row>
     <row r="558" spans="1:6">
       <c r="A558" t="s">
-        <v>10</v>
-      </c>
-      <c r="B558" s="4" t="s">
-        <v>25</v>
+        <v>9</v>
+      </c>
+      <c r="B558">
+        <v>3</v>
       </c>
       <c r="C558" s="1">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="D558" s="2">
-        <v>1.12</v>
+        <v>41.72</v>
       </c>
       <c r="E558" s="2">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="F558" s="3">
-        <v>0.076</v>
+        <v>1.541</v>
       </c>
     </row>
     <row r="559" spans="1:6">
       <c r="A559" t="s">
-        <v>10</v>
-      </c>
-      <c r="B559" s="4" t="s">
-        <v>26</v>
+        <v>9</v>
+      </c>
+      <c r="B559">
+        <v>4</v>
       </c>
       <c r="C559" s="1">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="D559" s="2">
-        <v>1.12</v>
+        <v>41.84</v>
       </c>
       <c r="E559" s="2">
-        <v>48.72</v>
+        <v>5.21</v>
       </c>
       <c r="F559" s="3">
-        <v>0.059</v>
+        <v>1.967</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6">
+      <c r="A560" t="s">
+        <v>9</v>
+      </c>
+      <c r="B560">
+        <v>5</v>
+      </c>
+      <c r="C560" s="1">
+        <v>46260</v>
+      </c>
+      <c r="D560" s="2">
+        <v>41.58</v>
+      </c>
+      <c r="E560" s="2">
+        <v>33.9</v>
+      </c>
+      <c r="F560" s="3">
+        <v>1.667</v>
+      </c>
+    </row>
+    <row r="561" spans="1:6">
+      <c r="A561" t="s">
+        <v>9</v>
+      </c>
+      <c r="B561">
+        <v>1</v>
+      </c>
+      <c r="C561" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D561" s="2">
+        <v>43.53</v>
+      </c>
+      <c r="E561" s="2">
+        <v>0</v>
+      </c>
+      <c r="F561" s="3">
+        <v>1.997</v>
+      </c>
+    </row>
+    <row r="562" spans="1:6">
+      <c r="A562" t="s">
+        <v>9</v>
+      </c>
+      <c r="B562">
+        <v>2</v>
+      </c>
+      <c r="C562" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D562" s="2">
+        <v>45.07</v>
+      </c>
+      <c r="E562" s="2">
+        <v>30.83</v>
+      </c>
+      <c r="F562" s="3">
+        <v>1.117</v>
+      </c>
+    </row>
+    <row r="563" spans="1:6">
+      <c r="A563" t="s">
+        <v>9</v>
+      </c>
+      <c r="B563">
+        <v>3</v>
+      </c>
+      <c r="C563" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D563" s="2">
+        <v>45.08</v>
+      </c>
+      <c r="E563" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="F563" s="3">
+        <v>1.263</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6">
+      <c r="A564" t="s">
+        <v>9</v>
+      </c>
+      <c r="B564">
+        <v>4</v>
+      </c>
+      <c r="C564" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D564" s="2">
+        <v>45.08</v>
+      </c>
+      <c r="E564" s="2">
+        <v>11.62</v>
+      </c>
+      <c r="F564" s="3">
+        <v>1.768</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6">
+      <c r="A565" t="s">
+        <v>9</v>
+      </c>
+      <c r="B565">
+        <v>5</v>
+      </c>
+      <c r="C565" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D565" s="2">
+        <v>45.08</v>
+      </c>
+      <c r="E565" s="2">
+        <v>38.72</v>
+      </c>
+      <c r="F565" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6">
+      <c r="A566" t="s">
+        <v>9</v>
+      </c>
+      <c r="B566">
+        <v>1</v>
+      </c>
+      <c r="C566" s="1">
+        <v>46262</v>
+      </c>
+      <c r="D566" s="2">
+        <v>41.33</v>
+      </c>
+      <c r="E566" s="2">
+        <v>0</v>
+      </c>
+      <c r="F566" s="3">
+        <v>2.905</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6">
+      <c r="A567" t="s">
+        <v>9</v>
+      </c>
+      <c r="B567">
+        <v>2</v>
+      </c>
+      <c r="C567" s="1">
+        <v>46262</v>
+      </c>
+      <c r="D567" s="2">
+        <v>42.52</v>
+      </c>
+      <c r="E567" s="2">
+        <v>34.85</v>
+      </c>
+      <c r="F567" s="3">
+        <v>1.114</v>
+      </c>
+    </row>
+    <row r="568" spans="1:6">
+      <c r="A568" t="s">
+        <v>9</v>
+      </c>
+      <c r="B568">
+        <v>3</v>
+      </c>
+      <c r="C568" s="1">
+        <v>46262</v>
+      </c>
+      <c r="D568" s="2">
+        <v>42.53</v>
+      </c>
+      <c r="E568" s="2">
+        <v>1.72</v>
+      </c>
+      <c r="F568" s="3">
+        <v>1.313</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6">
+      <c r="A569" t="s">
+        <v>9</v>
+      </c>
+      <c r="B569">
+        <v>4</v>
+      </c>
+      <c r="C569" s="1">
+        <v>46262</v>
+      </c>
+      <c r="D569" s="2">
+        <v>42.56</v>
+      </c>
+      <c r="E569" s="2">
+        <v>13.71</v>
+      </c>
+      <c r="F569" s="3">
+        <v>1.613</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6">
+      <c r="A570" t="s">
+        <v>9</v>
+      </c>
+      <c r="B570">
+        <v>5</v>
+      </c>
+      <c r="C570" s="1">
+        <v>46262</v>
+      </c>
+      <c r="D570" s="2">
+        <v>42.52</v>
+      </c>
+      <c r="E570" s="2">
+        <v>41.23</v>
+      </c>
+      <c r="F570" s="3">
+        <v>1.081</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6">
+      <c r="A571" t="s">
+        <v>9</v>
+      </c>
+      <c r="B571">
+        <v>1</v>
+      </c>
+      <c r="C571" s="1">
+        <v>46263</v>
+      </c>
+      <c r="D571" s="2">
+        <v>37.37</v>
+      </c>
+      <c r="E571" s="2">
+        <v>0</v>
+      </c>
+      <c r="F571" s="3">
+        <v>1.191</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6">
+      <c r="A572" t="s">
+        <v>9</v>
+      </c>
+      <c r="B572">
+        <v>2</v>
+      </c>
+      <c r="C572" s="1">
+        <v>46263</v>
+      </c>
+      <c r="D572" s="2">
+        <v>37.34</v>
+      </c>
+      <c r="E572" s="2">
+        <v>37.17</v>
+      </c>
+      <c r="F572" s="3">
+        <v>1.141</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6">
+      <c r="A573" t="s">
+        <v>9</v>
+      </c>
+      <c r="B573">
+        <v>3</v>
+      </c>
+      <c r="C573" s="1">
+        <v>46263</v>
+      </c>
+      <c r="D573" s="2">
+        <v>37.24</v>
+      </c>
+      <c r="E573" s="2">
+        <v>0</v>
+      </c>
+      <c r="F573" s="3">
+        <v>1.333</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6">
+      <c r="A574" t="s">
+        <v>9</v>
+      </c>
+      <c r="B574">
+        <v>4</v>
+      </c>
+      <c r="C574" s="1">
+        <v>46263</v>
+      </c>
+      <c r="D574" s="2">
+        <v>37.18</v>
+      </c>
+      <c r="E574" s="2">
+        <v>9.28</v>
+      </c>
+      <c r="F574" s="3">
+        <v>1.934</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6">
+      <c r="A575" t="s">
+        <v>9</v>
+      </c>
+      <c r="B575">
+        <v>5</v>
+      </c>
+      <c r="C575" s="1">
+        <v>46263</v>
+      </c>
+      <c r="D575" s="2">
+        <v>37.23</v>
+      </c>
+      <c r="E575" s="2">
+        <v>38.46</v>
+      </c>
+      <c r="F575" s="3">
+        <v>0.862</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12975" activeTab="1"/>
+    <workbookView windowWidth="27930" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drills" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="14">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1450,7 +1450,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F575"/>
+  <dimension ref="A1:F585"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -12958,6 +12958,206 @@
         <v>0.862</v>
       </c>
     </row>
+    <row r="576" spans="1:6">
+      <c r="A576" t="s">
+        <v>9</v>
+      </c>
+      <c r="B576">
+        <v>1</v>
+      </c>
+      <c r="C576" s="1">
+        <v>46264</v>
+      </c>
+      <c r="D576" s="2">
+        <v>35.52</v>
+      </c>
+      <c r="E576" s="2">
+        <v>0</v>
+      </c>
+      <c r="F576" s="3">
+        <v>1.543</v>
+      </c>
+    </row>
+    <row r="577" spans="1:6">
+      <c r="A577" t="s">
+        <v>9</v>
+      </c>
+      <c r="B577">
+        <v>2</v>
+      </c>
+      <c r="C577" s="1">
+        <v>46264</v>
+      </c>
+      <c r="D577" s="2">
+        <v>36.44</v>
+      </c>
+      <c r="E577" s="2">
+        <v>29.37</v>
+      </c>
+      <c r="F577" s="3">
+        <v>1.686</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6">
+      <c r="A578" t="s">
+        <v>9</v>
+      </c>
+      <c r="B578">
+        <v>3</v>
+      </c>
+      <c r="C578" s="1">
+        <v>46264</v>
+      </c>
+      <c r="D578" s="2">
+        <v>35.19</v>
+      </c>
+      <c r="E578" s="2">
+        <v>0</v>
+      </c>
+      <c r="F578" s="3">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6">
+      <c r="A579" t="s">
+        <v>9</v>
+      </c>
+      <c r="B579">
+        <v>4</v>
+      </c>
+      <c r="C579" s="1">
+        <v>46264</v>
+      </c>
+      <c r="D579" s="2">
+        <v>34.98</v>
+      </c>
+      <c r="E579" s="2">
+        <v>4.42</v>
+      </c>
+      <c r="F579" s="3">
+        <v>2.292</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6">
+      <c r="A580" t="s">
+        <v>9</v>
+      </c>
+      <c r="B580">
+        <v>5</v>
+      </c>
+      <c r="C580" s="1">
+        <v>46264</v>
+      </c>
+      <c r="D580" s="2">
+        <v>34.98</v>
+      </c>
+      <c r="E580" s="2">
+        <v>25.11</v>
+      </c>
+      <c r="F580" s="3">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6">
+      <c r="A581" t="s">
+        <v>9</v>
+      </c>
+      <c r="B581">
+        <v>1</v>
+      </c>
+      <c r="C581" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D581" s="2">
+        <v>31.69</v>
+      </c>
+      <c r="E581" s="2">
+        <v>0</v>
+      </c>
+      <c r="F581" s="3">
+        <v>1.687</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6">
+      <c r="A582" t="s">
+        <v>9</v>
+      </c>
+      <c r="B582">
+        <v>2</v>
+      </c>
+      <c r="C582" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D582" s="2">
+        <v>27.83</v>
+      </c>
+      <c r="E582" s="2">
+        <v>29.71</v>
+      </c>
+      <c r="F582" s="3">
+        <v>1.069</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6">
+      <c r="A583" t="s">
+        <v>9</v>
+      </c>
+      <c r="B583">
+        <v>3</v>
+      </c>
+      <c r="C583" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D583" s="2">
+        <v>29.81</v>
+      </c>
+      <c r="E583" s="2">
+        <v>9.42</v>
+      </c>
+      <c r="F583" s="3">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6">
+      <c r="A584" t="s">
+        <v>9</v>
+      </c>
+      <c r="B584">
+        <v>4</v>
+      </c>
+      <c r="C584" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D584" s="2">
+        <v>31.42</v>
+      </c>
+      <c r="E584" s="2">
+        <v>65.08</v>
+      </c>
+      <c r="F584" s="3">
+        <v>4.321</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6">
+      <c r="A585" t="s">
+        <v>9</v>
+      </c>
+      <c r="B585">
+        <v>5</v>
+      </c>
+      <c r="C585" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D585" s="2">
+        <v>32.56</v>
+      </c>
+      <c r="E585" s="2">
+        <v>34.21</v>
+      </c>
+      <c r="F585" s="3">
+        <v>1.755</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="14">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1450,7 +1450,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F585"/>
+  <dimension ref="A1:F595"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -13158,6 +13158,206 @@
         <v>1.755</v>
       </c>
     </row>
+    <row r="586" spans="1:6">
+      <c r="A586" t="s">
+        <v>9</v>
+      </c>
+      <c r="B586">
+        <v>1</v>
+      </c>
+      <c r="C586" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D586" s="2">
+        <v>36.48</v>
+      </c>
+      <c r="E586" s="2">
+        <v>0</v>
+      </c>
+      <c r="F586" s="3">
+        <v>1.876</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6">
+      <c r="A587" t="s">
+        <v>9</v>
+      </c>
+      <c r="B587">
+        <v>2</v>
+      </c>
+      <c r="C587" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D587" s="2">
+        <v>36.1</v>
+      </c>
+      <c r="E587" s="2">
+        <v>40.6</v>
+      </c>
+      <c r="F587" s="3">
+        <v>1.742</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6">
+      <c r="A588" t="s">
+        <v>9</v>
+      </c>
+      <c r="B588">
+        <v>3</v>
+      </c>
+      <c r="C588" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D588" s="2">
+        <v>36.2</v>
+      </c>
+      <c r="E588" s="2">
+        <v>9.8</v>
+      </c>
+      <c r="F588" s="3">
+        <v>1.641</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6">
+      <c r="A589" t="s">
+        <v>9</v>
+      </c>
+      <c r="B589">
+        <v>4</v>
+      </c>
+      <c r="C589" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D589" s="2">
+        <v>36.37</v>
+      </c>
+      <c r="E589" s="2">
+        <v>61.2</v>
+      </c>
+      <c r="F589" s="3">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6">
+      <c r="A590" t="s">
+        <v>9</v>
+      </c>
+      <c r="B590">
+        <v>5</v>
+      </c>
+      <c r="C590" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D590" s="2">
+        <v>36.62</v>
+      </c>
+      <c r="E590" s="2">
+        <v>35</v>
+      </c>
+      <c r="F590" s="3">
+        <v>1.275</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6">
+      <c r="A591" t="s">
+        <v>9</v>
+      </c>
+      <c r="B591">
+        <v>1</v>
+      </c>
+      <c r="C591" s="1">
+        <v>46267</v>
+      </c>
+      <c r="D591" s="2">
+        <v>39.15</v>
+      </c>
+      <c r="E591" s="2">
+        <v>0</v>
+      </c>
+      <c r="F591" s="3">
+        <v>1.809</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6">
+      <c r="A592" t="s">
+        <v>9</v>
+      </c>
+      <c r="B592">
+        <v>2</v>
+      </c>
+      <c r="C592" s="1">
+        <v>46267</v>
+      </c>
+      <c r="D592" s="2">
+        <v>38.35</v>
+      </c>
+      <c r="E592" s="2">
+        <v>45.65</v>
+      </c>
+      <c r="F592" s="3">
+        <v>1.787</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6">
+      <c r="A593" t="s">
+        <v>9</v>
+      </c>
+      <c r="B593">
+        <v>3</v>
+      </c>
+      <c r="C593" s="1">
+        <v>46267</v>
+      </c>
+      <c r="D593" s="2">
+        <v>39.6</v>
+      </c>
+      <c r="E593" s="2">
+        <v>6.15</v>
+      </c>
+      <c r="F593" s="3">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6">
+      <c r="A594" t="s">
+        <v>9</v>
+      </c>
+      <c r="B594">
+        <v>4</v>
+      </c>
+      <c r="C594" s="1">
+        <v>46267</v>
+      </c>
+      <c r="D594" s="2">
+        <v>40.16</v>
+      </c>
+      <c r="E594" s="2">
+        <v>47.12</v>
+      </c>
+      <c r="F594" s="3">
+        <v>7.931</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6">
+      <c r="A595" t="s">
+        <v>9</v>
+      </c>
+      <c r="B595">
+        <v>5</v>
+      </c>
+      <c r="C595" s="1">
+        <v>46267</v>
+      </c>
+      <c r="D595" s="2">
+        <v>41.38</v>
+      </c>
+      <c r="E595" s="2">
+        <v>36.43</v>
+      </c>
+      <c r="F595" s="3">
+        <v>2.989</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="14">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1450,7 +1450,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F595"/>
+  <dimension ref="A1:F600"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -13358,6 +13358,106 @@
         <v>2.989</v>
       </c>
     </row>
+    <row r="596" spans="1:6">
+      <c r="A596" t="s">
+        <v>9</v>
+      </c>
+      <c r="B596">
+        <v>1</v>
+      </c>
+      <c r="C596" s="1">
+        <v>46268</v>
+      </c>
+      <c r="D596" s="2">
+        <v>42.43</v>
+      </c>
+      <c r="E596" s="2">
+        <v>0</v>
+      </c>
+      <c r="F596" s="3">
+        <v>1.935</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6">
+      <c r="A597" t="s">
+        <v>9</v>
+      </c>
+      <c r="B597">
+        <v>2</v>
+      </c>
+      <c r="C597" s="1">
+        <v>46268</v>
+      </c>
+      <c r="D597" s="2">
+        <v>44.26</v>
+      </c>
+      <c r="E597" s="2">
+        <v>38.97</v>
+      </c>
+      <c r="F597" s="3">
+        <v>1.112</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6">
+      <c r="A598" t="s">
+        <v>9</v>
+      </c>
+      <c r="B598">
+        <v>3</v>
+      </c>
+      <c r="C598" s="1">
+        <v>46268</v>
+      </c>
+      <c r="D598" s="2">
+        <v>44.36</v>
+      </c>
+      <c r="E598" s="2">
+        <v>14.97</v>
+      </c>
+      <c r="F598" s="3">
+        <v>1.362</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6">
+      <c r="A599" t="s">
+        <v>9</v>
+      </c>
+      <c r="B599">
+        <v>4</v>
+      </c>
+      <c r="C599" s="1">
+        <v>46268</v>
+      </c>
+      <c r="D599" s="2">
+        <v>44.28</v>
+      </c>
+      <c r="E599" s="2">
+        <v>68.46</v>
+      </c>
+      <c r="F599" s="3">
+        <v>7.615</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6">
+      <c r="A600" t="s">
+        <v>9</v>
+      </c>
+      <c r="B600">
+        <v>5</v>
+      </c>
+      <c r="C600" s="1">
+        <v>46268</v>
+      </c>
+      <c r="D600" s="2">
+        <v>44.62</v>
+      </c>
+      <c r="E600" s="2">
+        <v>47.43</v>
+      </c>
+      <c r="F600" s="3">
+        <v>1.244</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="14">
   <si>
     <t>抽采地点</t>
   </si>
@@ -1450,7 +1450,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F600"/>
+  <dimension ref="A1:F610"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -13458,6 +13458,206 @@
         <v>1.244</v>
       </c>
     </row>
+    <row r="601" spans="1:6">
+      <c r="A601" t="s">
+        <v>9</v>
+      </c>
+      <c r="B601">
+        <v>1</v>
+      </c>
+      <c r="C601" s="1">
+        <v>46269</v>
+      </c>
+      <c r="D601" s="2">
+        <v>27.17</v>
+      </c>
+      <c r="E601" s="2">
+        <v>0</v>
+      </c>
+      <c r="F601" s="3">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6">
+      <c r="A602" t="s">
+        <v>9</v>
+      </c>
+      <c r="B602">
+        <v>2</v>
+      </c>
+      <c r="C602" s="1">
+        <v>46269</v>
+      </c>
+      <c r="D602" s="2">
+        <v>27.94</v>
+      </c>
+      <c r="E602" s="2">
+        <v>33.12</v>
+      </c>
+      <c r="F602" s="3">
+        <v>1.179</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6">
+      <c r="A603" t="s">
+        <v>9</v>
+      </c>
+      <c r="B603">
+        <v>3</v>
+      </c>
+      <c r="C603" s="1">
+        <v>46269</v>
+      </c>
+      <c r="D603" s="2">
+        <v>27.97</v>
+      </c>
+      <c r="E603" s="2">
+        <v>0</v>
+      </c>
+      <c r="F603" s="3">
+        <v>0.938</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6">
+      <c r="A604" t="s">
+        <v>9</v>
+      </c>
+      <c r="B604">
+        <v>4</v>
+      </c>
+      <c r="C604" s="1">
+        <v>46269</v>
+      </c>
+      <c r="D604" s="2">
+        <v>27.9</v>
+      </c>
+      <c r="E604" s="2">
+        <v>39.42</v>
+      </c>
+      <c r="F604" s="3">
+        <v>5.268</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6">
+      <c r="A605" t="s">
+        <v>9</v>
+      </c>
+      <c r="B605">
+        <v>5</v>
+      </c>
+      <c r="C605" s="1">
+        <v>46269</v>
+      </c>
+      <c r="D605" s="2">
+        <v>27.98</v>
+      </c>
+      <c r="E605" s="2">
+        <v>45.09</v>
+      </c>
+      <c r="F605" s="3">
+        <v>0.738</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6">
+      <c r="A606" t="s">
+        <v>9</v>
+      </c>
+      <c r="B606">
+        <v>1</v>
+      </c>
+      <c r="C606" s="1">
+        <v>46270</v>
+      </c>
+      <c r="D606" s="2">
+        <v>26.22</v>
+      </c>
+      <c r="E606" s="2">
+        <v>0</v>
+      </c>
+      <c r="F606" s="3">
+        <v>1.426</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6">
+      <c r="A607" t="s">
+        <v>9</v>
+      </c>
+      <c r="B607">
+        <v>2</v>
+      </c>
+      <c r="C607" s="1">
+        <v>46270</v>
+      </c>
+      <c r="D607" s="2">
+        <v>26.86</v>
+      </c>
+      <c r="E607" s="2">
+        <v>74.89</v>
+      </c>
+      <c r="F607" s="3">
+        <v>1.276</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6">
+      <c r="A608" t="s">
+        <v>9</v>
+      </c>
+      <c r="B608">
+        <v>3</v>
+      </c>
+      <c r="C608" s="1">
+        <v>46270</v>
+      </c>
+      <c r="D608" s="2">
+        <v>26.86</v>
+      </c>
+      <c r="E608" s="2">
+        <v>0</v>
+      </c>
+      <c r="F608" s="3">
+        <v>0.858</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6">
+      <c r="A609" t="s">
+        <v>9</v>
+      </c>
+      <c r="B609">
+        <v>4</v>
+      </c>
+      <c r="C609" s="1">
+        <v>46270</v>
+      </c>
+      <c r="D609" s="2">
+        <v>26.88</v>
+      </c>
+      <c r="E609" s="2">
+        <v>54.25</v>
+      </c>
+      <c r="F609" s="3">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6">
+      <c r="A610" t="s">
+        <v>9</v>
+      </c>
+      <c r="B610">
+        <v>5</v>
+      </c>
+      <c r="C610" s="1">
+        <v>46270</v>
+      </c>
+      <c r="D610" s="2">
+        <v>26.93</v>
+      </c>
+      <c r="E610" s="2">
+        <v>45.95</v>
+      </c>
+      <c r="F610" s="3">
+        <v>0.775</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
